--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -1158,7 +1158,11 @@
           <t>Reheat Beef Stroganoff (Sun Dinner)</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F17" s="14" t="inlineStr"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1204,7 +1208,11 @@
           <t>Reheat Vegan Mushroom Stroganoff (Sun Dinner — Veg)</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr"/>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
       <c r="F18" s="14" t="inlineStr"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
@@ -1311,7 +1319,11 @@
           <t>HOT Beef Stroganoff → Dinner</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr"/>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F21" s="16" t="inlineStr"/>
       <c r="G21" s="16" t="inlineStr">
         <is>
@@ -1367,7 +1379,11 @@
           <t>HOT Falafels → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -1416,7 +1432,11 @@
           <t>Heat Falafel (frozen → oven) (Mon Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr"/>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>40 pcs</t>
+        </is>
+      </c>
       <c r="F26" s="14" t="inlineStr"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1761,7 +1781,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr"/>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F35" s="16" t="inlineStr"/>
       <c r="G35" s="16" t="inlineStr">
         <is>
@@ -1803,7 +1827,11 @@
           <t>HOT Jerk Chicken → Dinner</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr"/>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>1.5 hotels</t>
+        </is>
+      </c>
       <c r="F36" s="16" t="inlineStr"/>
       <c r="G36" s="16" t="inlineStr">
         <is>
@@ -1909,7 +1937,11 @@
           <t>HOT Beef Nacho Mix → Lunch</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F40" s="6" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr">
         <is>
@@ -1951,7 +1983,11 @@
           <t>HOT Vegan Nacho Mix → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F41" s="6" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
@@ -2054,7 +2090,11 @@
           <t>Reheat Vegan Nacho Mix (Tue Lunch)</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr"/>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
       <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2503,7 +2543,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>150 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
@@ -2561,7 +2601,7 @@
       </c>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>150 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
@@ -2653,7 +2693,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr"/>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F58" s="16" t="inlineStr"/>
       <c r="G58" s="16" t="inlineStr">
         <is>
@@ -2695,7 +2739,11 @@
           <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr"/>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
           <t>5 oz</t>
@@ -2813,7 +2861,11 @@
           <t>HOT Crispy Chicken Tenders → Lunch</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr"/>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F63" s="6" t="inlineStr"/>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -2855,7 +2907,11 @@
           <t>HOT Vegan Tenders → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr"/>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F64" s="6" t="inlineStr"/>
       <c r="G64" s="6" t="inlineStr">
         <is>
@@ -2897,7 +2953,11 @@
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr"/>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F65" s="6" t="inlineStr"/>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -2950,7 +3010,11 @@
           <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
         </is>
       </c>
-      <c r="E67" s="14" t="inlineStr"/>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>4.5 hotels</t>
+        </is>
+      </c>
       <c r="F67" s="14" t="inlineStr"/>
       <c r="G67" s="14" t="inlineStr">
         <is>
@@ -3003,7 +3067,11 @@
           <t>Cook Adobo Pork/Chicken</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>40 lbs/32 lbs cooked</t>
+        </is>
+      </c>
       <c r="F69" s="9" t="inlineStr"/>
       <c r="G69" s="9" t="inlineStr">
         <is>
@@ -3375,7 +3443,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E78" s="16" t="inlineStr"/>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F78" s="16" t="inlineStr"/>
       <c r="G78" s="16" t="inlineStr">
         <is>
@@ -3756,7 +3828,7 @@
       <c r="I89" s="9" t="inlineStr"/>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>3 min</t>
+          <t>240 min</t>
         </is>
       </c>
       <c r="K89" s="10" t="inlineStr">
@@ -4071,7 +4143,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E97" s="16" t="inlineStr"/>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F97" s="16" t="inlineStr"/>
       <c r="G97" s="16" t="inlineStr">
         <is>
@@ -4498,7 +4574,7 @@
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="15" t="inlineStr">
         <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 9 HOTELS (hot)</t>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4595,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E109" s="16" t="inlineStr"/>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F109" s="16" t="inlineStr"/>
       <c r="G109" s="16" t="inlineStr">
         <is>
@@ -4651,7 +4731,7 @@
       </c>
       <c r="E112" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F112" s="16" t="inlineStr"/>
@@ -4688,7 +4768,7 @@
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 3 HOTELS (hot)</t>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4841,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>0.5 hotel</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
@@ -4816,7 +4896,11 @@
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E118" s="14" t="inlineStr"/>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs + 15 lbs</t>
+        </is>
+      </c>
       <c r="F118" s="14" t="inlineStr"/>
       <c r="G118" s="14" t="inlineStr">
         <is>
@@ -5242,7 +5326,11 @@
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr"/>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F128" s="9" t="inlineStr"/>
       <c r="G128" s="9" t="inlineStr"/>
       <c r="H128" s="9" t="inlineStr">
@@ -5328,7 +5416,7 @@
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="15" t="inlineStr">
         <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 7 HOTELS (hot)</t>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5437,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E131" s="16" t="inlineStr"/>
+      <c r="E131" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F131" s="16" t="inlineStr"/>
       <c r="G131" s="16" t="inlineStr">
         <is>
@@ -5499,7 +5591,11 @@
           <t>HOT Carrot Cabbage Fry → Dinner side</t>
         </is>
       </c>
-      <c r="E134" s="16" t="inlineStr"/>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F134" s="16" t="inlineStr"/>
       <c r="G134" s="16" t="inlineStr">
         <is>
@@ -5545,7 +5641,11 @@
           <t>HOT Rice → Dinner</t>
         </is>
       </c>
-      <c r="E135" s="16" t="inlineStr"/>
+      <c r="E135" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F135" s="16" t="inlineStr"/>
       <c r="G135" s="16" t="inlineStr"/>
       <c r="H135" s="16" t="inlineStr">
@@ -6355,7 +6455,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr"/>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F20" s="16" t="inlineStr"/>
       <c r="G20" s="16" t="inlineStr">
         <is>
@@ -7249,7 +7353,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr"/>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F42" s="16" t="inlineStr"/>
       <c r="G42" s="16" t="inlineStr">
         <is>
@@ -7399,7 +7507,11 @@
           <t>HOT Rice → Dinner</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr"/>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F45" s="16" t="inlineStr"/>
       <c r="G45" s="16" t="inlineStr">
         <is>
@@ -7441,7 +7553,11 @@
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr"/>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F46" s="16" t="inlineStr"/>
       <c r="G46" s="16" t="inlineStr">
         <is>
@@ -8054,7 +8170,11 @@
           <t>Steam Broccoli (Tue Dinner side)</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F62" s="9" t="inlineStr"/>
       <c r="G62" s="9" t="inlineStr">
         <is>
@@ -8157,7 +8277,11 @@
           <t>HOT Steamed Rice → Dinner</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr"/>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F65" s="16" t="inlineStr"/>
       <c r="G65" s="16" t="inlineStr">
         <is>
@@ -8199,7 +8323,11 @@
           <t>HOT Broccoli → Dinner side</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr"/>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F66" s="16" t="inlineStr"/>
       <c r="G66" s="16" t="inlineStr">
         <is>
@@ -8924,7 +9052,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E84" s="16" t="inlineStr"/>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F84" s="16" t="inlineStr"/>
       <c r="G84" s="16" t="inlineStr">
         <is>
@@ -9074,7 +9206,11 @@
           <t>HOT Coconut Rice &amp; Peas → Dinner</t>
         </is>
       </c>
-      <c r="E87" s="16" t="inlineStr"/>
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F87" s="16" t="inlineStr"/>
       <c r="G87" s="16" t="inlineStr">
         <is>
@@ -9116,7 +9252,11 @@
           <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr"/>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F88" s="16" t="inlineStr"/>
       <c r="G88" s="16" t="inlineStr">
         <is>
@@ -12330,7 +12470,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 1 HOTELS (hot)</t>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -12403,7 +12543,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>50 pcs</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
@@ -12800,7 +12940,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr"/>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F37" s="16" t="inlineStr"/>
       <c r="G37" s="16" t="inlineStr">
         <is>
@@ -13886,7 +14030,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E63" s="16" t="inlineStr"/>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F63" s="16" t="inlineStr"/>
       <c r="G63" s="16" t="inlineStr">
         <is>
@@ -14133,7 +14281,7 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 5 HOTELS (hot)</t>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 5.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -14156,7 +14304,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>155 pcs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -14250,7 +14398,11 @@
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F72" s="6" t="inlineStr"/>
       <c r="G72" s="6" t="inlineStr">
         <is>
@@ -14690,7 +14842,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E84" s="16" t="inlineStr"/>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F84" s="16" t="inlineStr"/>
       <c r="G84" s="16" t="inlineStr">
         <is>
@@ -15267,7 +15423,7 @@
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>180 min</t>
+          <t>240 min</t>
         </is>
       </c>
       <c r="K99" s="10" t="inlineStr">
@@ -15582,7 +15738,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E107" s="16" t="inlineStr"/>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F107" s="16" t="inlineStr"/>
       <c r="G107" s="16" t="inlineStr">
         <is>
@@ -15626,7 +15786,7 @@
       </c>
       <c r="E108" s="16" t="inlineStr">
         <is>
-          <t>2.5 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F108" s="16" t="inlineStr">
@@ -15732,7 +15892,11 @@
           <t>HOT Chakalaka → Dinner side</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr"/>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F110" s="16" t="inlineStr"/>
       <c r="G110" s="16" t="inlineStr">
         <is>
@@ -15842,7 +16006,11 @@
           <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr"/>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>100 lbs</t>
+        </is>
+      </c>
       <c r="F114" s="9" t="inlineStr"/>
       <c r="G114" s="9" t="inlineStr">
         <is>
@@ -16310,7 +16478,11 @@
           <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E125" s="16" t="inlineStr"/>
+      <c r="E125" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F125" s="16" t="inlineStr"/>
       <c r="G125" s="16" t="inlineStr"/>
       <c r="H125" s="16" t="inlineStr">
@@ -16352,7 +16524,11 @@
           <t>HOT Spring Rolls → Dinner side</t>
         </is>
       </c>
-      <c r="E126" s="16" t="inlineStr"/>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F126" s="16" t="inlineStr"/>
       <c r="G126" s="16" t="inlineStr"/>
       <c r="H126" s="16" t="inlineStr">
@@ -17014,7 +17190,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E144" s="16" t="inlineStr"/>
+      <c r="E144" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F144" s="16" t="inlineStr"/>
       <c r="G144" s="16" t="inlineStr">
         <is>
@@ -17056,7 +17236,11 @@
           <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
-      <c r="E145" s="16" t="inlineStr"/>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F145" s="16" t="inlineStr"/>
       <c r="G145" s="16" t="inlineStr">
         <is>
@@ -17152,7 +17336,11 @@
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="E147" s="16" t="inlineStr"/>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F147" s="16" t="inlineStr">
         <is>
           <t>6 oz</t>
@@ -17342,7 +17530,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 3 HOTELS (hot)</t>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -17866,7 +18054,11 @@
           <t>Reheat White Chilli Chicken Pasta (Sun Dinner)</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr"/>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
       <c r="F18" s="14" t="inlineStr"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
@@ -18193,7 +18385,11 @@
           <t>HOT Pasta + Broccoli &amp; Carrot → Dinner</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>9 hotels</t>
+        </is>
+      </c>
       <c r="F25" s="16" t="inlineStr"/>
       <c r="G25" s="16" t="inlineStr">
         <is>
@@ -18379,7 +18575,7 @@
       <c r="I31" s="9" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>200 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
@@ -18890,7 +19086,11 @@
           <t>HOT Curry Fish → Dinner</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr"/>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F43" s="16" t="inlineStr"/>
       <c r="G43" s="16" t="inlineStr"/>
       <c r="H43" s="16" t="inlineStr">
@@ -18932,7 +19132,11 @@
           <t>HOT Curry Spiced Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr"/>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F44" s="16" t="inlineStr"/>
       <c r="G44" s="16" t="inlineStr"/>
       <c r="H44" s="16" t="inlineStr">
@@ -18974,7 +19178,11 @@
           <t>HOT Green Curry Sauce → Dinner</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr"/>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F45" s="16" t="inlineStr"/>
       <c r="G45" s="16" t="inlineStr"/>
       <c r="H45" s="16" t="inlineStr">
@@ -19016,7 +19224,11 @@
           <t>HOT Rice + Green Beans → Dinner</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr"/>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>7 hotels</t>
+        </is>
+      </c>
       <c r="F46" s="16" t="inlineStr"/>
       <c r="G46" s="16" t="inlineStr">
         <is>
@@ -20186,7 +20398,11 @@
           <t>HOT BBQ Chicken Legs → Dinner</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr"/>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="F74" s="16" t="inlineStr"/>
       <c r="G74" s="16" t="inlineStr"/>
       <c r="H74" s="16" t="inlineStr">
@@ -20228,7 +20444,11 @@
           <t>HOT BBQ Vegan Tenders → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E75" s="16" t="inlineStr"/>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F75" s="16" t="inlineStr"/>
       <c r="G75" s="16" t="inlineStr"/>
       <c r="H75" s="16" t="inlineStr">
@@ -20270,7 +20490,11 @@
           <t>HOT Herb Garlic Potatoes → Dinner</t>
         </is>
       </c>
-      <c r="E76" s="16" t="inlineStr"/>
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F76" s="16" t="inlineStr"/>
       <c r="G76" s="16" t="inlineStr"/>
       <c r="H76" s="16" t="inlineStr">
@@ -20312,7 +20536,11 @@
           <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
-      <c r="E77" s="16" t="inlineStr"/>
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F77" s="16" t="inlineStr"/>
       <c r="G77" s="16" t="inlineStr"/>
       <c r="H77" s="16" t="inlineStr">
@@ -21014,7 +21242,11 @@
           <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
-      <c r="E94" s="16" t="inlineStr"/>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="F94" s="16" t="inlineStr"/>
       <c r="G94" s="16" t="inlineStr">
         <is>
@@ -21056,7 +21288,11 @@
           <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
         </is>
       </c>
-      <c r="E95" s="16" t="inlineStr"/>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F95" s="16" t="inlineStr"/>
       <c r="G95" s="16" t="inlineStr"/>
       <c r="H95" s="16" t="inlineStr">
@@ -21154,7 +21390,11 @@
           <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr"/>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F99" s="6" t="inlineStr"/>
       <c r="G99" s="6" t="inlineStr">
         <is>
@@ -21761,7 +22001,7 @@
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="15" t="inlineStr">
         <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 17.5 HOTELS (hot)</t>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 24.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -21832,7 +22072,11 @@
           <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
-      <c r="E116" s="16" t="inlineStr"/>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>8 hotels</t>
+        </is>
+      </c>
       <c r="F116" s="16" t="inlineStr"/>
       <c r="G116" s="16" t="inlineStr">
         <is>
@@ -22030,7 +22274,7 @@
       </c>
       <c r="E120" s="16" t="inlineStr">
         <is>
-          <t>0.5 unit</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F120" s="16" t="inlineStr"/>
@@ -22038,7 +22282,7 @@
       <c r="H120" s="16" t="inlineStr"/>
       <c r="I120" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
         </is>
       </c>
       <c r="J120" s="16" t="inlineStr"/>
@@ -22616,7 +22860,11 @@
           <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E137" s="16" t="inlineStr"/>
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F137" s="16" t="inlineStr"/>
       <c r="G137" s="16" t="inlineStr"/>
       <c r="H137" s="16" t="inlineStr">
@@ -22658,7 +22906,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E138" s="16" t="inlineStr"/>
+      <c r="E138" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="F138" s="16" t="inlineStr"/>
       <c r="G138" s="16" t="inlineStr"/>
       <c r="H138" s="16" t="inlineStr"/>
@@ -23182,7 +23434,11 @@
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E152" s="9" t="inlineStr"/>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F152" s="9" t="inlineStr"/>
       <c r="G152" s="9" t="inlineStr">
         <is>
@@ -23235,7 +23491,11 @@
           <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
-      <c r="E154" s="16" t="inlineStr"/>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F154" s="16" t="inlineStr"/>
       <c r="G154" s="16" t="inlineStr"/>
       <c r="H154" s="16" t="inlineStr">
@@ -23277,7 +23537,11 @@
           <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E155" s="16" t="inlineStr"/>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="F155" s="16" t="inlineStr"/>
       <c r="G155" s="16" t="inlineStr"/>
       <c r="H155" s="16" t="inlineStr">
@@ -23319,7 +23583,11 @@
           <t>HOT Rice → Dinner side</t>
         </is>
       </c>
-      <c r="E156" s="16" t="inlineStr"/>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="F156" s="16" t="inlineStr"/>
       <c r="G156" s="16" t="inlineStr">
         <is>
@@ -23361,7 +23629,11 @@
           <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
         </is>
       </c>
-      <c r="E157" s="16" t="inlineStr"/>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="F157" s="16" t="inlineStr"/>
       <c r="G157" s="16" t="inlineStr"/>
       <c r="H157" s="16" t="inlineStr">

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -4354,7 +4354,7 @@
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+          <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr"/>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>No AM run — Tuna Rex + Chickpea Rex Salad pre-sent Fri PM</t>
+          <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr"/>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+          <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr"/>
@@ -21320,7 +21320,7 @@
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr"/>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -2553,7 +2553,7 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thu/Fri Production (prev. cycle)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thu/Fri Production (prev. cycle)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="L59" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thu/Fri Production (prev. cycle)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -17997,7 +17997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L168"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22468,35 +22468,43 @@
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
+          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr"/>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H114" s="12" t="inlineStr"/>
-      <c r="I114" s="12" t="inlineStr"/>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I114" s="12" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
+        </is>
+      </c>
       <c r="J114" s="12" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K114" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K114" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L114" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+          <t>Serves: Wk.4 Saturday Lunch</t>
         </is>
       </c>
     </row>
@@ -22514,12 +22522,12 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
+          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>1 cs</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr"/>
@@ -22530,287 +22538,283 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I115" s="12" t="inlineStr"/>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
+        </is>
+      </c>
       <c r="J115" s="12" t="inlineStr">
         <is>
-          <t>10 min</t>
-        </is>
-      </c>
-      <c r="K115" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K115" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="12" t="inlineStr">
+          <t>Serves: Wk.4 Saturday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr"/>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F116" s="12" t="inlineStr"/>
-      <c r="G116" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H116" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I116" s="12" t="inlineStr"/>
-      <c r="J116" s="12" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr"/>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr"/>
+      <c r="G117" s="9" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>Combi roast</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K117" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr"/>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr"/>
+      <c r="G118" s="9" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K116" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L116" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="12" t="inlineStr">
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 24.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr"/>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F117" s="12" t="inlineStr"/>
-      <c r="G117" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I117" s="12" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
-        </is>
-      </c>
-      <c r="J117" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K117" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L117" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Saturday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="12" t="inlineStr">
+      <c r="B120" s="16" t="inlineStr"/>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>215 pcs</t>
+        </is>
+      </c>
+      <c r="F120" s="16" t="inlineStr"/>
+      <c r="G120" s="16" t="inlineStr">
+        <is>
+          <t>hotel/vac</t>
+        </is>
+      </c>
+      <c r="H120" s="16" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J120" s="16" t="inlineStr"/>
+      <c r="K120" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L120" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr"/>
-      <c r="C118" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D118" s="12" t="inlineStr">
-        <is>
-          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="F118" s="12" t="inlineStr"/>
-      <c r="G118" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H118" s="12" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="I118" s="12" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
-        </is>
-      </c>
-      <c r="J118" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K118" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L118" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Saturday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="B121" s="16" t="inlineStr"/>
+      <c r="C121" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D121" s="16" t="inlineStr">
+        <is>
+          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
+        </is>
+      </c>
+      <c r="E121" s="16" t="inlineStr">
+        <is>
+          <t>8 hotels</t>
+        </is>
+      </c>
+      <c r="F121" s="16" t="inlineStr"/>
+      <c r="G121" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H121" s="16" t="inlineStr">
+        <is>
+          <t>8 hotels</t>
+        </is>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J121" s="16" t="inlineStr"/>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L121" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr"/>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr"/>
-      <c r="G120" s="9" t="inlineStr"/>
-      <c r="H120" s="9" t="inlineStr"/>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>Combi roast</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K120" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L120" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr"/>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr"/>
-      <c r="G121" s="9" t="inlineStr"/>
-      <c r="H121" s="9" t="inlineStr"/>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K121" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L121" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 24.5 HOTELS (hot)</t>
+      <c r="B122" s="16" t="inlineStr"/>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>Cold Beef Nacho Mix → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F122" s="16" t="inlineStr"/>
+      <c r="G122" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H122" s="16" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
+        </is>
+      </c>
+      <c r="J122" s="16" t="inlineStr"/>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L122" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -22828,28 +22832,28 @@
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
+          <t>Cold Vegan Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E123" s="16" t="inlineStr">
         <is>
-          <t>215 pcs</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F123" s="16" t="inlineStr"/>
       <c r="G123" s="16" t="inlineStr">
         <is>
-          <t>hotel/vac</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="H123" s="16" t="inlineStr">
         <is>
-          <t>6 hotels</t>
+          <t>0.5u</t>
         </is>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
         </is>
       </c>
       <c r="J123" s="16" t="inlineStr"/>
@@ -22860,7 +22864,7 @@
       </c>
       <c r="L123" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
+          <t>Produced: Wk. 4 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -22878,39 +22882,39 @@
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
         </is>
       </c>
       <c r="E124" s="16" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F124" s="16" t="inlineStr"/>
       <c r="G124" s="16" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>bus bin</t>
         </is>
       </c>
       <c r="H124" s="16" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J124" s="16" t="inlineStr"/>
-      <c r="K124" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K124" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L124" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk.4 Wed Production (LAN)</t>
         </is>
       </c>
     </row>
@@ -22928,359 +22932,355 @@
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>Cold Beef Nacho Mix → Rex fridge</t>
+          <t>Cold Slaw → Fri Lunch side</t>
         </is>
       </c>
       <c r="E125" s="16" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F125" s="16" t="inlineStr"/>
-      <c r="G125" s="16" t="inlineStr">
+      <c r="G125" s="16" t="inlineStr"/>
+      <c r="H125" s="16" t="inlineStr"/>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J125" s="16" t="inlineStr"/>
+      <c r="K125" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L125" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Wed Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>◆  FRIDAY  —  Jun 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 0.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr"/>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>HOT Crispy Falafel → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Fri Lunch (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="inlineStr"/>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>30 pcs</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="inlineStr"/>
+      <c r="G130" s="14" t="inlineStr"/>
+      <c r="H130" s="14" t="inlineStr"/>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>Purchased frozen; heat day-of at Bloor</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K130" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L130" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Friday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr"/>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>Vegan Carnitas</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr"/>
+      <c r="G132" s="9" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H125" s="16" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
-      <c r="J125" s="16" t="inlineStr"/>
-      <c r="K125" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L125" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B126" s="16" t="inlineStr"/>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D126" s="16" t="inlineStr">
-        <is>
-          <t>Cold Vegan Nacho Mix → Rex fridge</t>
-        </is>
-      </c>
-      <c r="E126" s="16" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F126" s="16" t="inlineStr"/>
-      <c r="G126" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H126" s="16" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
-      <c r="J126" s="16" t="inlineStr"/>
-      <c r="K126" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L126" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="inlineStr"/>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D127" s="16" t="inlineStr">
-        <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
-        </is>
-      </c>
-      <c r="E127" s="16" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F127" s="16" t="inlineStr"/>
-      <c r="G127" s="16" t="inlineStr">
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>Stove</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K132" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L132" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr"/>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Broccoli Prep (Saturday Lunch)</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr"/>
+      <c r="G133" s="12" t="inlineStr">
         <is>
           <t>bus bin</t>
         </is>
       </c>
-      <c r="H127" s="16" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J127" s="16" t="inlineStr"/>
-      <c r="K127" s="17" t="inlineStr">
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="I133" s="12" t="inlineStr"/>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K133" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L127" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk.4 Wed Production (LAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr"/>
-      <c r="C128" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>Cold Slaw → Fri Lunch side</t>
-        </is>
-      </c>
-      <c r="E128" s="16" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F128" s="16" t="inlineStr"/>
-      <c r="G128" s="16" t="inlineStr"/>
-      <c r="H128" s="16" t="inlineStr"/>
-      <c r="I128" s="16" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J128" s="16" t="inlineStr"/>
-      <c r="K128" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L128" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk.4 Wed Production (LAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>◆  FRIDAY  —  Jun 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 0.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Saturday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr"/>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>HOT Crispy Falafel → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="F131" s="6" t="inlineStr"/>
-      <c r="G131" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H131" s="6" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J131" s="6" t="inlineStr"/>
-      <c r="K131" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L131" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk.4 Fri Lunch (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="14" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr"/>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>4 hotels veg</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="inlineStr"/>
+      <c r="G134" s="12" t="inlineStr"/>
+      <c r="H134" s="12" t="inlineStr"/>
+      <c r="I134" s="12" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
+        </is>
+      </c>
+      <c r="J134" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K134" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L134" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B133" s="14" t="inlineStr"/>
-      <c r="C133" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D133" s="14" t="inlineStr">
-        <is>
-          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E133" s="14" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="F133" s="14" t="inlineStr"/>
-      <c r="G133" s="14" t="inlineStr"/>
-      <c r="H133" s="14" t="inlineStr"/>
-      <c r="I133" s="14" t="inlineStr">
-        <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
-        </is>
-      </c>
-      <c r="J133" s="14" t="inlineStr">
+      <c r="B135" s="12" t="inlineStr"/>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Jerk Marinade</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="inlineStr"/>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>cambro/bag</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="inlineStr">
+        <is>
+          <t>1 bag/8 qt</t>
+        </is>
+      </c>
+      <c r="I135" s="12" t="inlineStr"/>
+      <c r="J135" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K133" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L133" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Friday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr"/>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>Vegan Carnitas</t>
-        </is>
-      </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr"/>
-      <c r="G135" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H135" s="9" t="inlineStr">
-        <is>
-          <t>1/2 hotel</t>
-        </is>
-      </c>
-      <c r="I135" s="9" t="inlineStr">
-        <is>
-          <t>Stove</t>
-        </is>
-      </c>
-      <c r="J135" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="L135" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+      <c r="L135" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Monday Dinner</t>
         </is>
       </c>
     </row>
@@ -23298,12 +23298,12 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>Broccoli Prep (Saturday Lunch)</t>
+          <t>Jerk Cauliflower</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>15 pcs</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr"/>
@@ -23314,23 +23314,23 @@
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>1/2 hotel</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr"/>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K136" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K136" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L136" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Saturday Lunch</t>
+          <t>Serves: Wk. 1 Monday Dinner</t>
         </is>
       </c>
     </row>
@@ -23348,22 +23348,22 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
+          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>4 hotels veg</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr"/>
-      <c r="G137" s="12" t="inlineStr"/>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
       <c r="H137" s="12" t="inlineStr"/>
-      <c r="I137" s="12" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
-        </is>
-      </c>
+      <c r="I137" s="12" t="inlineStr"/>
       <c r="J137" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
@@ -23376,7 +23376,7 @@
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
         </is>
       </c>
     </row>
@@ -23394,29 +23394,29 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>Jerk Marinade</t>
+          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr"/>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>cambro/bag</t>
+          <t>bus bin</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>1 bag/8 qt</t>
+          <t>1 bin</t>
         </is>
       </c>
       <c r="I138" s="12" t="inlineStr"/>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>10 min</t>
         </is>
       </c>
       <c r="K138" s="10" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="L138" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
         </is>
       </c>
     </row>
@@ -23444,12 +23444,12 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Jerk Cauliflower</t>
+          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>15 pcs</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr"/>
@@ -23460,13 +23460,13 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>1/2 hotel</t>
+          <t>1 bin</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr"/>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="K139" s="10" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
         </is>
       </c>
     </row>
@@ -24140,321 +24140,337 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="13" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="inlineStr"/>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>Cook Carnitas Pork (→ NC Wk1 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr"/>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K159" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L159" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr"/>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>Cook Carnitas Chicken (→ NC Wk1 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr"/>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K160" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L160" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="20" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B160" s="20" t="inlineStr"/>
-      <c r="C160" s="20" t="inlineStr">
+      <c r="B162" s="20" t="inlineStr"/>
+      <c r="C162" s="20" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="D160" s="20" t="inlineStr">
+      <c r="D162" s="20" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E160" s="20" t="inlineStr">
+      <c r="E162" s="20" t="inlineStr">
         <is>
           <t>3 pcs</t>
         </is>
       </c>
-      <c r="F160" s="20" t="inlineStr">
+      <c r="F162" s="20" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="G160" s="20" t="inlineStr">
+      <c r="G162" s="20" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H160" s="20" t="inlineStr"/>
-      <c r="I160" s="20" t="inlineStr">
+      <c r="H162" s="20" t="inlineStr"/>
+      <c r="I162" s="20" t="inlineStr">
         <is>
           <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
         </is>
       </c>
-      <c r="J160" s="20" t="inlineStr">
+      <c r="J162" s="20" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K160" s="14" t="inlineStr">
+      <c r="K162" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L160" s="20" t="inlineStr">
+      <c r="L162" s="20" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="14" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B161" s="14" t="inlineStr"/>
-      <c r="C161" s="14" t="inlineStr">
+      <c r="B163" s="14" t="inlineStr"/>
+      <c r="C163" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D161" s="14" t="inlineStr">
+      <c r="D163" s="14" t="inlineStr">
         <is>
           <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E161" s="14" t="inlineStr">
+      <c r="E163" s="14" t="inlineStr">
         <is>
           <t>110 lbs</t>
         </is>
       </c>
-      <c r="F161" s="14" t="inlineStr"/>
-      <c r="G161" s="14" t="inlineStr">
+      <c r="F163" s="14" t="inlineStr"/>
+      <c r="G163" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H161" s="14" t="inlineStr">
+      <c r="H163" s="14" t="inlineStr">
         <is>
           <t>3u</t>
         </is>
       </c>
-      <c r="I161" s="14" t="inlineStr">
+      <c r="I163" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J161" s="14" t="inlineStr">
+      <c r="J163" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K161" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L161" s="14" t="inlineStr">
+      <c r="K163" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L163" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="14" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B162" s="14" t="inlineStr"/>
-      <c r="C162" s="14" t="inlineStr">
+      <c r="B164" s="14" t="inlineStr"/>
+      <c r="C164" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D162" s="14" t="inlineStr">
+      <c r="D164" s="14" t="inlineStr">
         <is>
           <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
         </is>
       </c>
-      <c r="E162" s="14" t="inlineStr">
+      <c r="E164" s="14" t="inlineStr">
         <is>
           <t>15 lbs</t>
         </is>
       </c>
-      <c r="F162" s="14" t="inlineStr"/>
-      <c r="G162" s="14" t="inlineStr">
+      <c r="F164" s="14" t="inlineStr"/>
+      <c r="G164" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H162" s="14" t="inlineStr">
+      <c r="H164" s="14" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="I162" s="14" t="inlineStr">
+      <c r="I164" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J162" s="14" t="inlineStr">
+      <c r="J164" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K162" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L162" s="14" t="inlineStr">
+      <c r="K164" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L164" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="9" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B163" s="9" t="inlineStr"/>
-      <c r="C163" s="9" t="inlineStr">
+      <c r="B165" s="9" t="inlineStr"/>
+      <c r="C165" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D163" s="9" t="inlineStr">
+      <c r="D165" s="9" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E163" s="9" t="inlineStr">
+      <c r="E165" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F163" s="9" t="inlineStr"/>
-      <c r="G163" s="9" t="inlineStr">
+      <c r="F165" s="9" t="inlineStr"/>
+      <c r="G165" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H163" s="9" t="inlineStr">
+      <c r="H165" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I163" s="9" t="inlineStr"/>
-      <c r="J163" s="9" t="inlineStr">
+      <c r="I165" s="9" t="inlineStr"/>
+      <c r="J165" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K163" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L163" s="9" t="inlineStr">
+      <c r="K165" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L165" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="15" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B165" s="16" t="inlineStr"/>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D165" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef Massaman Curry → Dinner</t>
-        </is>
-      </c>
-      <c r="E165" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F165" s="16" t="inlineStr"/>
-      <c r="G165" s="16" t="inlineStr"/>
-      <c r="H165" s="16" t="inlineStr">
-        <is>
-          <t>3u</t>
-        </is>
-      </c>
-      <c r="I165" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J165" s="16" t="inlineStr"/>
-      <c r="K165" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L165" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B166" s="16" t="inlineStr"/>
-      <c r="C166" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D166" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E166" s="16" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F166" s="16" t="inlineStr"/>
-      <c r="G166" s="16" t="inlineStr"/>
-      <c r="H166" s="16" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J166" s="16" t="inlineStr"/>
-      <c r="K166" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L166" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -24472,21 +24488,21 @@
       </c>
       <c r="D167" s="16" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner side</t>
+          <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
       <c r="E167" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F167" s="16" t="inlineStr"/>
-      <c r="G167" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H167" s="16" t="inlineStr"/>
+      <c r="G167" s="16" t="inlineStr"/>
+      <c r="H167" s="16" t="inlineStr">
+        <is>
+          <t>3u</t>
+        </is>
+      </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -24500,7 +24516,7 @@
       </c>
       <c r="L167" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -24518,24 +24534,24 @@
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E168" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F168" s="16" t="inlineStr"/>
       <c r="G168" s="16" t="inlineStr"/>
       <c r="H168" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>0.5u</t>
         </is>
       </c>
       <c r="I168" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex fridge</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J168" s="16" t="inlineStr"/>
@@ -24545,6 +24561,98 @@
         </is>
       </c>
       <c r="L168" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr"/>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D169" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F169" s="16" t="inlineStr"/>
+      <c r="G169" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H169" s="16" t="inlineStr"/>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J169" s="16" t="inlineStr"/>
+      <c r="K169" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L169" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr"/>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F170" s="16" t="inlineStr"/>
+      <c r="G170" s="16" t="inlineStr"/>
+      <c r="H170" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex fridge</t>
+        </is>
+      </c>
+      <c r="J170" s="16" t="inlineStr"/>
+      <c r="K170" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L170" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production</t>
         </is>
@@ -24553,7 +24661,6 @@
   </sheetData>
   <mergeCells count="44">
     <mergeCell ref="A99:L99"/>
-    <mergeCell ref="A164:L164"/>
     <mergeCell ref="A149:L149"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="A154:L154"/>
@@ -24571,27 +24678,28 @@
     <mergeCell ref="A129:L129"/>
     <mergeCell ref="A85:L85"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A159:L159"/>
+    <mergeCell ref="A116:L116"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="A150:L150"/>
+    <mergeCell ref="A126:L126"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A144:L144"/>
-    <mergeCell ref="A122:L122"/>
     <mergeCell ref="A140:L140"/>
+    <mergeCell ref="A131:L131"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A134:L134"/>
+    <mergeCell ref="A161:L161"/>
     <mergeCell ref="A152:L152"/>
+    <mergeCell ref="A127:L127"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A130:L130"/>
     <mergeCell ref="A39:L39"/>
     <mergeCell ref="A83:L83"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A166:L166"/>
     <mergeCell ref="A51:L51"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A132:L132"/>
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A119:L119"/>
     <mergeCell ref="A110:L110"/>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4476,321 +4476,345 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="13" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr"/>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr"/>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="inlineStr"/>
+      <c r="I108" s="12" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
+        </is>
+      </c>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K108" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L108" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr"/>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr"/>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K109" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr"/>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr"/>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K110" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="14" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B109" s="14" t="inlineStr"/>
-      <c r="C109" s="14" t="inlineStr">
+      <c r="B112" s="14" t="inlineStr"/>
+      <c r="C112" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
+      <c r="D112" s="14" t="inlineStr">
         <is>
           <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
-      <c r="E109" s="14" t="inlineStr">
+      <c r="E112" s="14" t="inlineStr">
         <is>
           <t>60 lbs</t>
         </is>
       </c>
-      <c r="F109" s="14" t="inlineStr">
+      <c r="F112" s="14" t="inlineStr">
         <is>
           <t>10 oz</t>
         </is>
       </c>
-      <c r="G109" s="14" t="inlineStr">
+      <c r="G112" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H109" s="14" t="inlineStr">
+      <c r="H112" s="14" t="inlineStr">
         <is>
           <t>2 hotels + Vegan</t>
         </is>
       </c>
-      <c r="I109" s="14" t="inlineStr"/>
-      <c r="J109" s="14" t="inlineStr">
+      <c r="I112" s="14" t="inlineStr"/>
+      <c r="J112" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K109" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L109" s="14" t="inlineStr">
+      <c r="K112" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L112" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr"/>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="B113" s="9" t="inlineStr"/>
+      <c r="C113" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>Pineapple Rice (Fri Dinner)</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="E113" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F113" s="9" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="G110" s="9" t="inlineStr">
+      <c r="G113" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H110" s="9" t="inlineStr">
+      <c r="H113" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I110" s="9" t="inlineStr">
+      <c r="I113" s="9" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Oven rice</t>
         </is>
       </c>
-      <c r="J110" s="9" t="inlineStr">
+      <c r="J113" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K110" s="14" t="inlineStr">
+      <c r="K113" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L110" s="9" t="inlineStr">
+      <c r="L113" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="B114" s="9" t="inlineStr"/>
+      <c r="C114" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
         <is>
           <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E114" s="9" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F114" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G111" s="9" t="inlineStr">
+      <c r="G114" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H111" s="9" t="inlineStr">
+      <c r="H114" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I111" s="9" t="inlineStr">
+      <c r="I114" s="9" t="inlineStr">
         <is>
           <t>Frozen; steam at Bloor</t>
         </is>
       </c>
-      <c r="J111" s="9" t="inlineStr">
+      <c r="J114" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K111" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L111" s="9" t="inlineStr">
+      <c r="K114" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="15" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B113" s="16" t="inlineStr"/>
-      <c r="C113" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D113" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E113" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F113" s="16" t="inlineStr"/>
-      <c r="G113" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H113" s="16" t="inlineStr"/>
-      <c r="I113" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J113" s="16" t="inlineStr"/>
-      <c r="K113" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L113" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="inlineStr"/>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F114" s="16" t="inlineStr"/>
-      <c r="G114" s="16" t="inlineStr"/>
-      <c r="H114" s="16" t="inlineStr"/>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J114" s="16" t="inlineStr"/>
-      <c r="K114" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L114" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="inlineStr"/>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D115" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
-        </is>
-      </c>
-      <c r="E115" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F115" s="16" t="inlineStr"/>
-      <c r="G115" s="16" t="inlineStr"/>
-      <c r="H115" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J115" s="16" t="inlineStr"/>
-      <c r="K115" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L115" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -4808,363 +4832,347 @@
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F116" s="16" t="inlineStr"/>
+      <c r="G116" s="16" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H116" s="16" t="inlineStr"/>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="J116" s="16" t="inlineStr"/>
+      <c r="K116" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L116" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr"/>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr"/>
+      <c r="G117" s="16" t="inlineStr"/>
+      <c r="H117" s="16" t="inlineStr"/>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J117" s="16" t="inlineStr"/>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L117" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="inlineStr"/>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pineapple Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F118" s="16" t="inlineStr"/>
+      <c r="G118" s="16" t="inlineStr"/>
+      <c r="H118" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J118" s="16" t="inlineStr"/>
+      <c r="K118" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L118" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr"/>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D119" s="16" t="inlineStr">
+        <is>
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="E116" s="16" t="inlineStr">
+      <c r="E119" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F116" s="16" t="inlineStr"/>
-      <c r="G116" s="16" t="inlineStr"/>
-      <c r="H116" s="16" t="inlineStr">
+      <c r="F119" s="16" t="inlineStr"/>
+      <c r="G119" s="16" t="inlineStr"/>
+      <c r="H119" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I116" s="16" t="inlineStr">
+      <c r="I119" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J116" s="16" t="inlineStr"/>
-      <c r="K116" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L116" s="16" t="inlineStr">
+      <c r="J119" s="16" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L119" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>◆  SATURDAY  —  May 23</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr"/>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr"/>
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F119" s="6" t="inlineStr"/>
-      <c r="G119" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H119" s="6" t="inlineStr">
+      <c r="H122" s="6" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
+      <c r="I122" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J119" s="6" t="inlineStr"/>
-      <c r="K119" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L119" s="6" t="inlineStr">
+      <c r="J122" s="6" t="inlineStr"/>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr"/>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr"/>
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr"/>
-      <c r="G120" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H120" s="6" t="inlineStr">
+      <c r="H123" s="6" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr">
+      <c r="I123" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J120" s="6" t="inlineStr"/>
-      <c r="K120" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L120" s="6" t="inlineStr">
+      <c r="J123" s="6" t="inlineStr"/>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="14" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B122" s="14" t="inlineStr"/>
-      <c r="C122" s="14" t="inlineStr">
+      <c r="B125" s="14" t="inlineStr"/>
+      <c r="C125" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D122" s="14" t="inlineStr">
+      <c r="D125" s="14" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E122" s="14" t="inlineStr">
+      <c r="E125" s="14" t="inlineStr">
         <is>
           <t>80 lbs + 15 lbs</t>
         </is>
       </c>
-      <c r="F122" s="14" t="inlineStr"/>
-      <c r="G122" s="14" t="inlineStr">
+      <c r="F125" s="14" t="inlineStr"/>
+      <c r="G125" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H122" s="14" t="inlineStr"/>
-      <c r="I122" s="14" t="inlineStr">
+      <c r="H125" s="14" t="inlineStr"/>
+      <c r="I125" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J122" s="14" t="inlineStr">
+      <c r="J125" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K122" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L122" s="14" t="inlineStr">
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L125" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="inlineStr"/>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D124" s="12" t="inlineStr">
-        <is>
-          <t>Griot Marinade</t>
-        </is>
-      </c>
-      <c r="E124" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F124" s="12" t="inlineStr"/>
-      <c r="G124" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H124" s="12" t="inlineStr"/>
-      <c r="I124" s="12" t="inlineStr">
-        <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
-        </is>
-      </c>
-      <c r="J124" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K124" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L124" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="inlineStr"/>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>Cut/Marinate Pork Griot</t>
-        </is>
-      </c>
-      <c r="E125" s="12" t="inlineStr">
-        <is>
-          <t>30kg raw</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="inlineStr"/>
-      <c r="G125" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="inlineStr">
-        <is>
-          <t>1 bin/2 hotels</t>
-        </is>
-      </c>
-      <c r="I125" s="12" t="inlineStr"/>
-      <c r="J125" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K125" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L125" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B126" s="12" t="inlineStr"/>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Griot</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>25kg raw</t>
-        </is>
-      </c>
-      <c r="F126" s="12" t="inlineStr"/>
-      <c r="G126" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H126" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I126" s="12" t="inlineStr"/>
-      <c r="J126" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K126" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L126" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -5182,43 +5190,39 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr"/>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr"/>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+          <t>For Griot Pork/Chicken/Tofu</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K127" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -5236,158 +5240,197 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Cut/Marinate Pork Griot</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>30kg raw</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr"/>
       <c r="G128" s="12" t="inlineStr">
         <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>1 bin/2 hotels</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr"/>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K128" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L128" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr"/>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Griot</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>25kg raw</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr"/>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="inlineStr"/>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr"/>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr"/>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K130" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L130" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr"/>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr"/>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H128" s="12" t="inlineStr">
+      <c r="H131" s="12" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I128" s="12" t="inlineStr">
+      <c r="I131" s="12" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
-      <c r="J128" s="12" t="inlineStr">
+      <c r="J131" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K128" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L128" s="12" t="inlineStr">
+      <c r="K131" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B130" s="9" t="inlineStr"/>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D130" s="9" t="inlineStr">
-        <is>
-          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="E130" s="9" t="inlineStr">
-        <is>
-          <t>3 bins → 2 hotels</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="inlineStr"/>
-      <c r="G130" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H130" s="9" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>Stir-fry at LAN; send hot PM</t>
-        </is>
-      </c>
-      <c r="J130" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K130" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="14" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B131" s="14" t="inlineStr"/>
-      <c r="C131" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D131" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E131" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F131" s="14" t="inlineStr"/>
-      <c r="G131" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H131" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I131" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J131" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K131" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L131" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -5405,350 +5448,323 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
+          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr"/>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K132" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L132" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr"/>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr"/>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L133" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr"/>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>3 bins → 2 hotels</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr"/>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>Stir-fry at LAN; send hot PM</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K135" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L135" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr"/>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="inlineStr"/>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K136" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr"/>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="E137" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr"/>
-      <c r="G132" s="9" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr">
+      <c r="F137" s="9" t="inlineStr"/>
+      <c r="G137" s="9" t="inlineStr"/>
+      <c r="H137" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I132" s="9" t="inlineStr"/>
-      <c r="J132" s="9" t="inlineStr">
+      <c r="I137" s="9" t="inlineStr"/>
+      <c r="J137" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K132" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L132" s="9" t="inlineStr">
+      <c r="K137" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L137" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="20" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B133" s="20" t="inlineStr"/>
-      <c r="C133" s="20" t="inlineStr">
+      <c r="B138" s="20" t="inlineStr"/>
+      <c r="C138" s="20" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="D133" s="20" t="inlineStr">
+      <c r="D138" s="20" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E133" s="20" t="inlineStr">
+      <c r="E138" s="20" t="inlineStr">
         <is>
           <t>2 pcs</t>
         </is>
       </c>
-      <c r="F133" s="20" t="inlineStr">
+      <c r="F138" s="20" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="G133" s="20" t="inlineStr">
+      <c r="G138" s="20" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H133" s="20" t="inlineStr">
+      <c r="H138" s="20" t="inlineStr">
         <is>
           <t>4" hotel</t>
         </is>
       </c>
-      <c r="I133" s="20" t="inlineStr">
+      <c r="I138" s="20" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
       </c>
-      <c r="J133" s="20" t="inlineStr">
+      <c r="J138" s="20" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K133" s="14" t="inlineStr">
+      <c r="K138" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L133" s="20" t="inlineStr">
+      <c r="L138" s="20" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="15" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B135" s="16" t="inlineStr"/>
-      <c r="C135" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D135" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E135" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F135" s="16" t="inlineStr"/>
-      <c r="G135" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H135" s="16" t="inlineStr"/>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J135" s="16" t="inlineStr"/>
-      <c r="K135" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L135" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B136" s="16" t="inlineStr"/>
-      <c r="C136" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E136" s="16" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F136" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G136" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H136" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J136" s="16" t="inlineStr"/>
-      <c r="K136" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L136" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B137" s="16" t="inlineStr"/>
-      <c r="C137" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D137" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E137" s="16" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F137" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G137" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H137" s="16" t="inlineStr">
-        <is>
-          <t>1 × 4" hotel</t>
-        </is>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J137" s="16" t="inlineStr"/>
-      <c r="K137" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L137" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B138" s="16" t="inlineStr"/>
-      <c r="C138" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D138" s="16" t="inlineStr">
-        <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
-        </is>
-      </c>
-      <c r="E138" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F138" s="16" t="inlineStr"/>
-      <c r="G138" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H138" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I138" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J138" s="16" t="inlineStr"/>
-      <c r="K138" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L138" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B139" s="16" t="inlineStr"/>
-      <c r="C139" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D139" s="16" t="inlineStr">
-        <is>
-          <t>HOT Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="E139" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F139" s="16" t="inlineStr"/>
-      <c r="G139" s="16" t="inlineStr"/>
-      <c r="H139" s="16" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J139" s="16" t="inlineStr"/>
-      <c r="K139" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L139" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -5766,37 +5782,287 @@
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E140" s="16" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F140" s="16" t="inlineStr"/>
       <c r="G140" s="16" t="inlineStr">
         <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H140" s="16" t="inlineStr"/>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="J140" s="16" t="inlineStr"/>
+      <c r="K140" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L140" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr"/>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
+        </is>
+      </c>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G141" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H141" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J141" s="16" t="inlineStr"/>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L141" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr"/>
+      <c r="C142" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E142" s="16" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F142" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H142" s="16" t="inlineStr">
+        <is>
+          <t>1 × 4" hotel</t>
+        </is>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J142" s="16" t="inlineStr"/>
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L142" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr"/>
+      <c r="C143" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="inlineStr">
+        <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E143" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F143" s="16" t="inlineStr"/>
+      <c r="G143" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J143" s="16" t="inlineStr"/>
+      <c r="K143" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L143" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr"/>
+      <c r="C144" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E144" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F144" s="16" t="inlineStr"/>
+      <c r="G144" s="16" t="inlineStr"/>
+      <c r="H144" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J144" s="16" t="inlineStr"/>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L144" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr"/>
+      <c r="C145" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="inlineStr">
+        <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F145" s="16" t="inlineStr"/>
+      <c r="G145" s="16" t="inlineStr">
+        <is>
           <t>bus bin/bag</t>
         </is>
       </c>
-      <c r="H140" s="16" t="inlineStr">
+      <c r="H145" s="16" t="inlineStr">
         <is>
           <t>4 items</t>
         </is>
       </c>
-      <c r="I140" s="16" t="inlineStr">
+      <c r="I145" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex fridge</t>
         </is>
       </c>
-      <c r="J140" s="16" t="inlineStr"/>
-      <c r="K140" s="17" t="inlineStr">
+      <c r="J145" s="16" t="inlineStr"/>
+      <c r="K145" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L140" s="16" t="inlineStr">
+      <c r="L145" s="16" t="inlineStr">
         <is>
           <t>Produced: LAN day-before</t>
         </is>
@@ -5806,21 +6072,21 @@
   <mergeCells count="44">
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A108:L108"/>
     <mergeCell ref="A66:L66"/>
     <mergeCell ref="A74:L74"/>
-    <mergeCell ref="A118:L118"/>
     <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A120:L120"/>
     <mergeCell ref="A57:L57"/>
     <mergeCell ref="A101:L101"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A139:L139"/>
     <mergeCell ref="A104:L104"/>
     <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A129:L129"/>
     <mergeCell ref="A85:L85"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A126:L126"/>
     <mergeCell ref="A106:L106"/>
     <mergeCell ref="A53:L53"/>
     <mergeCell ref="A4:L4"/>
@@ -5830,11 +6096,11 @@
     <mergeCell ref="A96:L96"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A134:L134"/>
-    <mergeCell ref="A112:L112"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A68:L68"/>
     <mergeCell ref="A121:L121"/>
-    <mergeCell ref="A117:L117"/>
+    <mergeCell ref="A115:L115"/>
+    <mergeCell ref="A111:L111"/>
     <mergeCell ref="A102:L102"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A39:L39"/>
@@ -5845,9 +6111,9 @@
     <mergeCell ref="A82:L82"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A123:L123"/>
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A88:L88"/>
+    <mergeCell ref="A124:L124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8125,7 +8391,7 @@
       </c>
       <c r="L59" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Mon–Tue Production</t>
+          <t>Produced: Wk. 1 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8449,7 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Tuesday Production</t>
+          <t>Produced: Wk. 1 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8660,7 @@
       </c>
       <c r="L65" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Mon–Tue Production</t>
+          <t>Produced: Wk. 1 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -8912,7 +9178,7 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Caribbean Stew</t>
+          <t>Caribbean Chicken + Chickpea Curry (→ Wk3 Tue Dinner)</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -12083,7 +12349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L151"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16757,164 +17023,168 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="13" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr"/>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Vindaloo Sauce (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr"/>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr"/>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr"/>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr"/>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr"/>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr"/>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr"/>
-      <c r="C123" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr"/>
-      <c r="G123" s="9" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K123" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L123" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="inlineStr"/>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="E124" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr"/>
-      <c r="G124" s="9" t="inlineStr"/>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K124" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L124" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="14" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B125" s="14" t="inlineStr"/>
-      <c r="C125" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D125" s="14" t="inlineStr">
-        <is>
-          <t>Heat Spring Rolls (Fri Dinner side)</t>
-        </is>
-      </c>
-      <c r="E125" s="14" t="inlineStr">
-        <is>
-          <t>200 pcs</t>
-        </is>
-      </c>
-      <c r="F125" s="14" t="inlineStr"/>
-      <c r="G125" s="14" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H125" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I125" s="14" t="inlineStr">
-        <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
-        </is>
-      </c>
-      <c r="J125" s="14" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="K125" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L125" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -16932,536 +17202,536 @@
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
+          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr"/>
+      <c r="G126" s="9" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr"/>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr"/>
+      <c r="G127" s="9" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr"/>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>Heat Spring Rolls (Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>200 pcs</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="inlineStr"/>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>Purchased frozen; heat day-of at Bloor</t>
+        </is>
+      </c>
+      <c r="J128" s="14" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="K128" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L128" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr"/>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
           <t>Bok Choy (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="E126" s="9" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr"/>
-      <c r="G126" s="9" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr"/>
+      <c r="G129" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H126" s="9" t="inlineStr">
+      <c r="H129" s="9" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="I126" s="9" t="inlineStr">
+      <c r="I129" s="9" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
         </is>
       </c>
-      <c r="J126" s="9" t="inlineStr">
+      <c r="J129" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K126" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L126" s="9" t="inlineStr">
+      <c r="K129" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L129" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="15" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 8 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B128" s="16" t="inlineStr"/>
-      <c r="C128" s="16" t="inlineStr">
+      <c r="B131" s="16" t="inlineStr"/>
+      <c r="C131" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="D131" s="16" t="inlineStr">
         <is>
           <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
         </is>
       </c>
-      <c r="E128" s="16" t="inlineStr">
+      <c r="E131" s="16" t="inlineStr">
         <is>
           <t>5 hotels</t>
         </is>
       </c>
-      <c r="F128" s="16" t="inlineStr"/>
-      <c r="G128" s="16" t="inlineStr">
+      <c r="F131" s="16" t="inlineStr"/>
+      <c r="G131" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H128" s="16" t="inlineStr">
+      <c r="H131" s="16" t="inlineStr">
         <is>
           <t>5 hotels</t>
         </is>
       </c>
-      <c r="I128" s="16" t="inlineStr">
+      <c r="I131" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J128" s="16" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L128" s="16" t="inlineStr">
+      <c r="J131" s="16" t="inlineStr"/>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L131" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B129" s="16" t="inlineStr"/>
-      <c r="C129" s="16" t="inlineStr">
+      <c r="B132" s="16" t="inlineStr"/>
+      <c r="C132" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D129" s="16" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="E129" s="16" t="inlineStr">
+      <c r="E132" s="16" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="F129" s="16" t="inlineStr"/>
-      <c r="G129" s="16" t="inlineStr"/>
-      <c r="H129" s="16" t="inlineStr">
+      <c r="F132" s="16" t="inlineStr"/>
+      <c r="G132" s="16" t="inlineStr"/>
+      <c r="H132" s="16" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I129" s="16" t="inlineStr">
+      <c r="I132" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J129" s="16" t="inlineStr"/>
-      <c r="K129" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L129" s="16" t="inlineStr">
+      <c r="J132" s="16" t="inlineStr"/>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L132" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="16" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B130" s="16" t="inlineStr"/>
-      <c r="C130" s="16" t="inlineStr">
+      <c r="B133" s="16" t="inlineStr"/>
+      <c r="C133" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D130" s="16" t="inlineStr">
+      <c r="D133" s="16" t="inlineStr">
         <is>
           <t>HOT Spring Rolls → Dinner side</t>
         </is>
       </c>
-      <c r="E130" s="16" t="inlineStr">
+      <c r="E133" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F130" s="16" t="inlineStr"/>
-      <c r="G130" s="16" t="inlineStr"/>
-      <c r="H130" s="16" t="inlineStr">
+      <c r="F133" s="16" t="inlineStr"/>
+      <c r="G133" s="16" t="inlineStr"/>
+      <c r="H133" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I130" s="16" t="inlineStr">
+      <c r="I133" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J130" s="16" t="inlineStr"/>
-      <c r="K130" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L130" s="16" t="inlineStr">
+      <c r="J133" s="16" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L133" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
         <is>
           <t>◆  SATURDAY  —  Jun 6</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr"/>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr"/>
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="G133" s="6" t="inlineStr">
+      <c r="G136" s="6" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>2u</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J133" s="6" t="inlineStr"/>
-      <c r="K133" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L133" s="6" t="inlineStr">
+      <c r="J136" s="6" t="inlineStr"/>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L136" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Friday Production</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr"/>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr"/>
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>12 lbs</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G134" s="6" t="inlineStr">
+      <c r="G137" s="6" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J134" s="6" t="inlineStr"/>
-      <c r="K134" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L134" s="6" t="inlineStr">
+      <c r="J137" s="6" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Friday Production</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="14" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B136" s="14" t="inlineStr"/>
-      <c r="C136" s="14" t="inlineStr">
+      <c r="B139" s="14" t="inlineStr"/>
+      <c r="C139" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D136" s="14" t="inlineStr">
+      <c r="D139" s="14" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E136" s="14" t="inlineStr">
+      <c r="E139" s="14" t="inlineStr">
         <is>
           <t>92 lbs (80+12)</t>
         </is>
       </c>
-      <c r="F136" s="14" t="inlineStr">
+      <c r="F139" s="14" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="G136" s="14" t="inlineStr">
+      <c r="G139" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H136" s="14" t="inlineStr"/>
-      <c r="I136" s="14" t="inlineStr">
+      <c r="H139" s="14" t="inlineStr"/>
+      <c r="I139" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J136" s="14" t="inlineStr">
+      <c r="J139" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K136" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L136" s="14" t="inlineStr">
+      <c r="K139" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L139" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B138" s="12" t="inlineStr"/>
-      <c r="C138" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D138" s="12" t="inlineStr">
-        <is>
-          <t>Cut/Season Tandoori Pork</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F138" s="12" t="inlineStr"/>
-      <c r="G138" s="12" t="inlineStr">
-        <is>
-          <t>hotels</t>
-        </is>
-      </c>
-      <c r="H138" s="12" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I138" s="12" t="inlineStr">
-        <is>
-          <t>Season w/Vindaloo Dry Spice Mix</t>
-        </is>
-      </c>
-      <c r="J138" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K138" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L138" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B139" s="12" t="inlineStr"/>
-      <c r="C139" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D139" s="12" t="inlineStr">
-        <is>
-          <t>Tandoori Marinade</t>
-        </is>
-      </c>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F139" s="12" t="inlineStr"/>
-      <c r="G139" s="12" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I139" s="12" t="inlineStr"/>
-      <c r="J139" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K139" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Tandoori Production Wk. 4 Monday</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="inlineStr"/>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D140" s="12" t="inlineStr">
-        <is>
-          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="F140" s="12" t="inlineStr"/>
-      <c r="G140" s="12" t="inlineStr">
-        <is>
-          <t>bins</t>
-        </is>
-      </c>
-      <c r="H140" s="12" t="inlineStr">
-        <is>
-          <t>3 bins (6u)</t>
-        </is>
-      </c>
-      <c r="I140" s="12" t="inlineStr"/>
-      <c r="J140" s="12" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K140" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L140" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
         </is>
       </c>
     </row>
@@ -17479,43 +17749,43 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Cut/Season Tandoori Pork</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr"/>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
+          <t>hotels</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+          <t>Season w/Vindaloo Dry Spice Mix</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K141" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K141" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
+          <t>Serves: Wk. 4 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -17533,35 +17803,39 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+          <t>Tandoori Marinade</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr"/>
-      <c r="G142" s="12" t="inlineStr"/>
-      <c r="H142" s="12" t="inlineStr"/>
-      <c r="I142" s="12" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
-        </is>
-      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr"/>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K142" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K142" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L142" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
+          <t>Serves: Tandoori Production Wk. 4 Monday</t>
         </is>
       </c>
     </row>
@@ -17579,363 +17853,621 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr"/>
       <c r="G143" s="12" t="inlineStr">
         <is>
+          <t>bins</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>3 bins (6u)</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr"/>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K143" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr"/>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr"/>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K144" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr"/>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr"/>
+      <c r="G145" s="12" t="inlineStr"/>
+      <c r="H145" s="12" t="inlineStr"/>
+      <c r="I145" s="12" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+        </is>
+      </c>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K145" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr"/>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr"/>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H143" s="12" t="inlineStr">
+      <c r="H146" s="12" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I143" s="12" t="inlineStr">
+      <c r="I146" s="12" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
-      <c r="J143" s="12" t="inlineStr">
+      <c r="J146" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K143" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L143" s="12" t="inlineStr">
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L146" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="9" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr"/>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="B147" s="9" t="inlineStr"/>
+      <c r="C147" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D144" s="9" t="inlineStr">
+      <c r="D147" s="9" t="inlineStr">
         <is>
           <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
         </is>
       </c>
-      <c r="E144" s="9" t="inlineStr">
+      <c r="E147" s="9" t="inlineStr">
         <is>
           <t>110lbs</t>
         </is>
       </c>
-      <c r="F144" s="9" t="inlineStr">
+      <c r="F147" s="9" t="inlineStr">
         <is>
           <t>12 oz</t>
         </is>
       </c>
-      <c r="G144" s="9" t="inlineStr">
+      <c r="G147" s="9" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H144" s="9" t="inlineStr">
+      <c r="H147" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I144" s="9" t="inlineStr">
+      <c r="I147" s="9" t="inlineStr">
         <is>
           <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
         </is>
       </c>
-      <c r="J144" s="9" t="inlineStr">
+      <c r="J147" s="9" t="inlineStr">
         <is>
           <t>320 min</t>
         </is>
       </c>
-      <c r="K144" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L144" s="9" t="inlineStr">
+      <c r="K147" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L147" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="13" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr"/>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>Cook Pork Vindaloo (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr"/>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K148" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L148" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr"/>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr"/>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K149" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L149" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr"/>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="B151" s="9" t="inlineStr"/>
+      <c r="C151" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D146" s="9" t="inlineStr">
+      <c r="D151" s="9" t="inlineStr">
         <is>
           <t>Potato Wedges (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="E146" s="9" t="inlineStr">
+      <c r="E151" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F146" s="9" t="inlineStr"/>
-      <c r="G146" s="9" t="inlineStr"/>
-      <c r="H146" s="9" t="inlineStr">
+      <c r="F151" s="9" t="inlineStr"/>
+      <c r="G151" s="9" t="inlineStr"/>
+      <c r="H151" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I146" s="9" t="inlineStr">
+      <c r="I151" s="9" t="inlineStr">
         <is>
           <t>Purchased frozen; oven</t>
         </is>
       </c>
-      <c r="J146" s="9" t="inlineStr">
+      <c r="J151" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K146" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L146" s="9" t="inlineStr">
+      <c r="K151" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L151" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="15" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 4.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="16" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B148" s="16" t="inlineStr"/>
-      <c r="C148" s="16" t="inlineStr">
+      <c r="B153" s="16" t="inlineStr"/>
+      <c r="C153" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D148" s="16" t="inlineStr">
+      <c r="D153" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E148" s="16" t="inlineStr">
+      <c r="E153" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F148" s="16" t="inlineStr"/>
-      <c r="G148" s="16" t="inlineStr">
+      <c r="F153" s="16" t="inlineStr"/>
+      <c r="G153" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H148" s="16" t="inlineStr"/>
-      <c r="I148" s="16" t="inlineStr">
+      <c r="H153" s="16" t="inlineStr"/>
+      <c r="I153" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J148" s="16" t="inlineStr"/>
-      <c r="K148" s="18" t="inlineStr">
+      <c r="J153" s="16" t="inlineStr"/>
+      <c r="K153" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L148" s="16" t="inlineStr">
+      <c r="L153" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="16" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B149" s="16" t="inlineStr"/>
-      <c r="C149" s="16" t="inlineStr">
+      <c r="B154" s="16" t="inlineStr"/>
+      <c r="C154" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D149" s="16" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
-      <c r="E149" s="16" t="inlineStr">
+      <c r="E154" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F149" s="16" t="inlineStr"/>
-      <c r="G149" s="16" t="inlineStr">
+      <c r="F154" s="16" t="inlineStr"/>
+      <c r="G154" s="16" t="inlineStr">
         <is>
           <t>boxes</t>
         </is>
       </c>
-      <c r="H149" s="16" t="inlineStr">
+      <c r="H154" s="16" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="I149" s="16" t="inlineStr">
+      <c r="I154" s="16" t="inlineStr">
         <is>
           <t>Vendor → Rex | Driver collects ordered pizza</t>
         </is>
       </c>
-      <c r="J149" s="16" t="inlineStr"/>
-      <c r="K149" s="7" t="inlineStr">
+      <c r="J154" s="16" t="inlineStr"/>
+      <c r="K154" s="7" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="L149" s="16" t="inlineStr">
+      <c r="L154" s="16" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="16" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="16" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B150" s="16" t="inlineStr"/>
-      <c r="C150" s="16" t="inlineStr">
+      <c r="B155" s="16" t="inlineStr"/>
+      <c r="C155" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D150" s="16" t="inlineStr">
+      <c r="D155" s="16" t="inlineStr">
         <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="E150" s="16" t="inlineStr">
+      <c r="E155" s="16" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F150" s="16" t="inlineStr"/>
-      <c r="G150" s="16" t="inlineStr">
+      <c r="F155" s="16" t="inlineStr"/>
+      <c r="G155" s="16" t="inlineStr">
         <is>
           <t>bus bin/bag</t>
         </is>
       </c>
-      <c r="H150" s="16" t="inlineStr">
+      <c r="H155" s="16" t="inlineStr">
         <is>
           <t>4 items</t>
         </is>
       </c>
-      <c r="I150" s="16" t="inlineStr">
+      <c r="I155" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex fridge</t>
         </is>
       </c>
-      <c r="J150" s="16" t="inlineStr"/>
-      <c r="K150" s="17" t="inlineStr">
+      <c r="J155" s="16" t="inlineStr"/>
+      <c r="K155" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L150" s="16" t="inlineStr">
+      <c r="L155" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="16" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B151" s="16" t="inlineStr"/>
-      <c r="C151" s="16" t="inlineStr">
+      <c r="B156" s="16" t="inlineStr"/>
+      <c r="C156" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D151" s="16" t="inlineStr">
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="E151" s="16" t="inlineStr">
+      <c r="E156" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F151" s="16" t="inlineStr">
+      <c r="F156" s="16" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="G151" s="16" t="inlineStr">
+      <c r="G156" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H151" s="16" t="inlineStr">
+      <c r="H156" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I151" s="16" t="inlineStr">
+      <c r="I156" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J151" s="16" t="inlineStr"/>
-      <c r="K151" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L151" s="16" t="inlineStr">
+      <c r="J156" s="16" t="inlineStr"/>
+      <c r="K156" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L156" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Dinner (same day)</t>
         </is>
@@ -17946,11 +18478,9 @@
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A90:L90"/>
-    <mergeCell ref="A137:L137"/>
     <mergeCell ref="A46:L46"/>
     <mergeCell ref="A75:L75"/>
     <mergeCell ref="A80:L80"/>
-    <mergeCell ref="A145:L145"/>
     <mergeCell ref="A57:L57"/>
     <mergeCell ref="A113:L113"/>
     <mergeCell ref="A2:L2"/>
@@ -17959,31 +18489,33 @@
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A97:L97"/>
     <mergeCell ref="A135:L135"/>
+    <mergeCell ref="A150:L150"/>
     <mergeCell ref="A106:L106"/>
-    <mergeCell ref="A122:L122"/>
+    <mergeCell ref="A140:L140"/>
     <mergeCell ref="A91:L91"/>
-    <mergeCell ref="A131:L131"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A62:L62"/>
     <mergeCell ref="A100:L100"/>
-    <mergeCell ref="A147:L147"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="A134:L134"/>
     <mergeCell ref="A43:L43"/>
     <mergeCell ref="A112:L112"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A68:L68"/>
+    <mergeCell ref="A152:L152"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A115:L115"/>
     <mergeCell ref="A117:L117"/>
-    <mergeCell ref="A127:L127"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A130:L130"/>
     <mergeCell ref="A83:L83"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A73:L73"/>
     <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A138:L138"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A94:L94"/>
-    <mergeCell ref="A132:L132"/>
     <mergeCell ref="A36:L36"/>
     <mergeCell ref="A69:L69"/>
   </mergeCells>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2492,711 +2492,719 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr"/>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr"/>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr"/>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool; use same day for marinade</t>
+        </is>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr"/>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr"/>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr"/>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr"/>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr"/>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr"/>
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>Pork Carnitas (Tue Dinner)</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>40 lbs</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F57" s="14" t="inlineStr">
         <is>
           <t>5 oz</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H54" s="14" t="inlineStr">
+      <c r="H57" s="14" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I54" s="14" t="inlineStr">
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Pork braise</t>
         </is>
       </c>
-      <c r="J54" s="14" t="inlineStr">
+      <c r="J57" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K54" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L54" s="14" t="inlineStr">
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L57" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr"/>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr"/>
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>Halal Chicken Carnitas (Tue Dinner)</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t>32 lbs</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F58" s="14" t="inlineStr">
         <is>
           <t>5 oz</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="H58" s="14" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I55" s="14" t="inlineStr">
+      <c r="I58" s="14" t="inlineStr">
         <is>
           <t>Pork braise</t>
         </is>
       </c>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="J58" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K55" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L55" s="14" t="inlineStr">
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr"/>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr"/>
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>Steam Broccoli (Tue Dinner side)</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr"/>
-      <c r="J56" s="9" t="inlineStr">
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K56" s="14" t="inlineStr">
+      <c r="K59" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr">
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Tuesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 7 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr"/>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr"/>
+      <c r="C61" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E61" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr"/>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="F61" s="16" t="inlineStr"/>
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H58" s="16" t="inlineStr"/>
-      <c r="I58" s="16" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr"/>
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J58" s="16" t="inlineStr"/>
-      <c r="K58" s="18" t="inlineStr">
+      <c r="J61" s="16" t="inlineStr"/>
+      <c r="K61" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L58" s="16" t="inlineStr">
+      <c r="L61" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr"/>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr"/>
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F59" s="16" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>5 oz</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H59" s="16" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I59" s="16" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J59" s="16" t="inlineStr"/>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L59" s="16" t="inlineStr">
+      <c r="J62" s="16" t="inlineStr"/>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L62" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr"/>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr"/>
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>HOT Broccoli → Dinner</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E63" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F60" s="16" t="inlineStr">
+      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H60" s="16" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I60" s="16" t="inlineStr">
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J60" s="16" t="inlineStr"/>
-      <c r="K60" s="17" t="inlineStr">
+      <c r="J63" s="16" t="inlineStr"/>
+      <c r="K63" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L60" s="16" t="inlineStr">
+      <c r="L63" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Tuesday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>◆  WEDNESDAY  —  May 20</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 5.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr"/>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr"/>
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>HOT Crispy Chicken Tenders → Lunch</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr"/>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr"/>
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr"/>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr"/>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr"/>
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>HOT Vegan Tenders → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>0.5 hotels</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr"/>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr"/>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J64" s="6" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr"/>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr"/>
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr"/>
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>bus bin</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr"/>
-      <c r="K65" s="17" t="inlineStr">
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr">
+      <c r="L68" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk.1 Wed Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr"/>
-      <c r="C67" s="14" t="inlineStr">
+      <c r="B70" s="14" t="inlineStr"/>
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
         </is>
       </c>
-      <c r="E67" s="14" t="inlineStr">
+      <c r="E70" s="14" t="inlineStr">
         <is>
           <t>4.5 hotels</t>
         </is>
       </c>
-      <c r="F67" s="14" t="inlineStr"/>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="F70" s="14" t="inlineStr"/>
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr"/>
-      <c r="I67" s="14" t="inlineStr">
+      <c r="H70" s="14" t="inlineStr"/>
+      <c r="I70" s="14" t="inlineStr">
         <is>
           <t>Frozen → oven</t>
         </is>
       </c>
-      <c r="J67" s="14" t="inlineStr">
+      <c r="J70" s="14" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K67" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L67" s="14" t="inlineStr">
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L70" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr"/>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>Cook Adobo Pork/Chicken</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>40 lbs/32 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr"/>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>Oven/Combi</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K69" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="inlineStr"/>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="F70" s="12" t="inlineStr"/>
-      <c r="G70" s="12" t="inlineStr"/>
-      <c r="H70" s="12" t="inlineStr"/>
-      <c r="I70" s="12" t="inlineStr">
-        <is>
-          <t>Cook quinoa; combine; form cakes; chill overnight</t>
-        </is>
-      </c>
-      <c r="J70" s="12" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L70" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Thursday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr"/>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr"/>
-      <c r="G71" s="9" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>1/2 hotel</t>
-        </is>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Stove top</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K71" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
@@ -3214,29 +3222,33 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
+          <t>Cook Adobo Pork/Chicken</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>40 lbs/32 lbs cooked</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="I72" s="9" t="inlineStr"/>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>Oven/Combi</t>
+        </is>
+      </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>120 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="K72" s="10" t="inlineStr">
@@ -3246,7 +3258,7 @@
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Saturday Dinner</t>
+          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -3264,631 +3276,678 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
+          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>30 pcs</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr"/>
+      <c r="G73" s="12" t="inlineStr"/>
+      <c r="H73" s="12" t="inlineStr"/>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>Cook quinoa; combine; form cakes; chill overnight</t>
+        </is>
+      </c>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr"/>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr"/>
+      <c r="G74" s="9" t="inlineStr"/>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Stove top</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr"/>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr"/>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr"/>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
           <t>Bean Salad (→ Fri Lunch)</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr"/>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr"/>
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>bus bin</t>
         </is>
       </c>
-      <c r="H73" s="12" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="I73" s="12" t="inlineStr">
+      <c r="I76" s="12" t="inlineStr">
         <is>
           <t>Dress; chill; send Thu PM</t>
         </is>
       </c>
-      <c r="J73" s="12" t="inlineStr">
+      <c r="J76" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K73" s="14" t="inlineStr">
+      <c r="K76" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L73" s="12" t="inlineStr">
+      <c r="L76" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk.1 Friday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="13" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr"/>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr"/>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr"/>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr"/>
-      <c r="C75" s="14" t="inlineStr">
+      <c r="B80" s="14" t="inlineStr"/>
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D75" s="14" t="inlineStr">
+      <c r="D80" s="14" t="inlineStr">
         <is>
           <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E75" s="14" t="inlineStr">
+      <c r="E80" s="14" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F75" s="14" t="inlineStr"/>
-      <c r="G75" s="14" t="inlineStr">
+      <c r="F80" s="14" t="inlineStr"/>
+      <c r="G80" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H75" s="14" t="inlineStr">
+      <c r="H80" s="14" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I75" s="14" t="inlineStr">
+      <c r="I80" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged batch</t>
         </is>
       </c>
-      <c r="J75" s="14" t="inlineStr">
+      <c r="J80" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K75" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L75" s="14" t="inlineStr">
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Monday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr"/>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr"/>
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
         <is>
           <t>Herbed Couscous (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
+      <c r="H81" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr"/>
-      <c r="J76" s="9" t="inlineStr">
+      <c r="I81" s="9" t="inlineStr"/>
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K76" s="14" t="inlineStr">
+      <c r="K81" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L76" s="9" t="inlineStr">
+      <c r="L81" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="15" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 6 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="16" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B78" s="16" t="inlineStr"/>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr"/>
+      <c r="C83" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E78" s="16" t="inlineStr">
+      <c r="E83" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F78" s="16" t="inlineStr"/>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="F83" s="16" t="inlineStr"/>
+      <c r="G83" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H78" s="16" t="inlineStr"/>
-      <c r="I78" s="16" t="inlineStr">
+      <c r="H83" s="16" t="inlineStr"/>
+      <c r="I83" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J78" s="16" t="inlineStr"/>
-      <c r="K78" s="18" t="inlineStr">
+      <c r="J83" s="16" t="inlineStr"/>
+      <c r="K83" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L78" s="16" t="inlineStr">
+      <c r="L83" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B79" s="16" t="inlineStr"/>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr"/>
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>HOT Shakshuka Sauce → Dinner</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F79" s="16" t="inlineStr"/>
-      <c r="G79" s="16" t="inlineStr">
+      <c r="F84" s="16" t="inlineStr"/>
+      <c r="G84" s="16" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H79" s="16" t="inlineStr">
+      <c r="H84" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I79" s="16" t="inlineStr">
+      <c r="I84" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J79" s="16" t="inlineStr"/>
-      <c r="K79" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L79" s="16" t="inlineStr">
+      <c r="J84" s="16" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L84" s="16" t="inlineStr">
         <is>
           <t>Produced: pre-loaded batch (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B80" s="16" t="inlineStr"/>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr"/>
+      <c r="C85" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>HOT Herbed Couscous → Dinner side</t>
         </is>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F80" s="16" t="inlineStr"/>
-      <c r="G80" s="16" t="inlineStr"/>
-      <c r="H80" s="16" t="inlineStr">
+      <c r="F85" s="16" t="inlineStr"/>
+      <c r="G85" s="16" t="inlineStr"/>
+      <c r="H85" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I80" s="16" t="inlineStr">
+      <c r="I85" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J80" s="16" t="inlineStr"/>
-      <c r="K80" s="17" t="inlineStr">
+      <c r="J85" s="16" t="inlineStr"/>
+      <c r="K85" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L80" s="16" t="inlineStr">
+      <c r="L85" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>◆  THURSDAY  —  May 21</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 4 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr"/>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr"/>
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>HOT Halal Chicken Burgers → Lunch</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>185 pcs</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr"/>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr"/>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L83" s="6" t="inlineStr">
+      <c r="J88" s="6" t="inlineStr"/>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr"/>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr"/>
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>HOT Quinoa Burgers → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>20 pcs</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr"/>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr"/>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr"/>
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J84" s="6" t="inlineStr"/>
-      <c r="K84" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L84" s="6" t="inlineStr">
+      <c r="J89" s="6" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr"/>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>185 pcs</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr"/>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I86" s="9" t="inlineStr"/>
-      <c r="J86" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K86" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L86" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Thursday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr"/>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr"/>
-      <c r="G87" s="9" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>Pan fry; send hot AM</t>
-        </is>
-      </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="K87" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L87" s="9" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr"/>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>130 lbs</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr"/>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>3.5 hotels</t>
-        </is>
-      </c>
-      <c r="I89" s="9" t="inlineStr"/>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>240 min</t>
-        </is>
-      </c>
-      <c r="K89" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L89" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Monday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>12 lbs</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="I90" s="9" t="inlineStr"/>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K90" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L90" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3965,12 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>185 pcs</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr"/>
@@ -3922,13 +3981,13 @@
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr"/>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>120 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="K91" s="10" t="inlineStr">
@@ -3938,116 +3997,104 @@
       </c>
       <c r="L91" s="9" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="14" t="inlineStr">
+          <t>Serves: Wk. 1 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B93" s="14" t="inlineStr"/>
-      <c r="C93" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Butter Chicken (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="E93" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F93" s="14" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H93" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I93" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J93" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K93" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L93" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+      <c r="B92" s="9" t="inlineStr"/>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>30 pcs</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr"/>
+      <c r="G92" s="9" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>Pan fry; send hot AM</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="14" t="inlineStr">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B94" s="14" t="inlineStr"/>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D94" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>20 lbs</t>
-        </is>
-      </c>
-      <c r="F94" s="14" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I94" s="14" t="inlineStr"/>
-      <c r="J94" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
+      <c r="B94" s="9" t="inlineStr"/>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>130 lbs</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr"/>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>3.5 hotels</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr"/>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>240 min</t>
         </is>
       </c>
       <c r="K94" s="10" t="inlineStr">
@@ -4055,9 +4102,9 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="L94" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Monday Lunch</t>
         </is>
       </c>
     </row>
@@ -4075,681 +4122,669 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
+          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr"/>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr"/>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr"/>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr"/>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K96" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr"/>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Butter Chicken (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L98" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr"/>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>20 lbs</t>
+        </is>
+      </c>
+      <c r="F99" s="14" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr"/>
+      <c r="J99" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L99" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
           <t>Roasted Cauliflower (Thu Dinner side)</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>3 bins → 3 hotels</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F100" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G95" s="9" t="inlineStr">
+      <c r="G100" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H95" s="9" t="inlineStr">
+      <c r="H100" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
+      <c r="I100" s="9" t="inlineStr">
         <is>
           <t>⚠ CONFIRM carrot role in this side</t>
         </is>
       </c>
-      <c r="J95" s="9" t="inlineStr">
+      <c r="J100" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K95" s="14" t="inlineStr">
+      <c r="K100" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L95" s="9" t="inlineStr">
+      <c r="L100" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Thursday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="16" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 7.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B97" s="16" t="inlineStr"/>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="B102" s="16" t="inlineStr"/>
+      <c r="C102" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D97" s="16" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E97" s="16" t="inlineStr">
+      <c r="E102" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F97" s="16" t="inlineStr"/>
-      <c r="G97" s="16" t="inlineStr">
+      <c r="F102" s="16" t="inlineStr"/>
+      <c r="G102" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H97" s="16" t="inlineStr"/>
-      <c r="I97" s="16" t="inlineStr">
+      <c r="H102" s="16" t="inlineStr"/>
+      <c r="I102" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J97" s="16" t="inlineStr"/>
-      <c r="K97" s="18" t="inlineStr">
+      <c r="J102" s="16" t="inlineStr"/>
+      <c r="K102" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L97" s="16" t="inlineStr">
+      <c r="L102" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="16" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B98" s="16" t="inlineStr"/>
-      <c r="C98" s="16" t="inlineStr">
+      <c r="B103" s="16" t="inlineStr"/>
+      <c r="C103" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
         </is>
       </c>
-      <c r="E98" s="16" t="inlineStr">
+      <c r="E103" s="16" t="inlineStr">
         <is>
           <t>80+20 lbs</t>
         </is>
       </c>
-      <c r="F98" s="16" t="inlineStr">
+      <c r="F103" s="16" t="inlineStr">
         <is>
           <t>12 oz</t>
         </is>
       </c>
-      <c r="G98" s="16" t="inlineStr">
+      <c r="G103" s="16" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H98" s="16" t="inlineStr">
+      <c r="H103" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I98" s="16" t="inlineStr">
+      <c r="I103" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J98" s="16" t="inlineStr"/>
-      <c r="K98" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L98" s="16" t="inlineStr">
+      <c r="J103" s="16" t="inlineStr"/>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L103" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="16" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B99" s="16" t="inlineStr"/>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="B104" s="16" t="inlineStr"/>
+      <c r="C104" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D99" s="16" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>HOT Roasted Cauliflower → Dinner side</t>
         </is>
       </c>
-      <c r="E99" s="16" t="inlineStr">
+      <c r="E104" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F99" s="16" t="inlineStr"/>
-      <c r="G99" s="16" t="inlineStr"/>
-      <c r="H99" s="16" t="inlineStr">
+      <c r="F104" s="16" t="inlineStr"/>
+      <c r="G104" s="16" t="inlineStr"/>
+      <c r="H104" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I99" s="16" t="inlineStr">
+      <c r="I104" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J99" s="16" t="inlineStr"/>
-      <c r="K99" s="17" t="inlineStr">
+      <c r="J104" s="16" t="inlineStr"/>
+      <c r="K104" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L99" s="16" t="inlineStr">
+      <c r="L104" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="16" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B100" s="16" t="inlineStr"/>
-      <c r="C100" s="16" t="inlineStr">
+      <c r="B105" s="16" t="inlineStr"/>
+      <c r="C105" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D100" s="16" t="inlineStr">
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>HOT Naan → Dinner</t>
         </is>
       </c>
-      <c r="E100" s="16" t="inlineStr">
+      <c r="E105" s="16" t="inlineStr">
         <is>
           <t>200 pcs</t>
         </is>
       </c>
-      <c r="F100" s="16" t="inlineStr">
+      <c r="F105" s="16" t="inlineStr">
         <is>
           <t>1 each (?)</t>
         </is>
       </c>
-      <c r="G100" s="16" t="inlineStr">
+      <c r="G105" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H100" s="16" t="inlineStr">
+      <c r="H105" s="16" t="inlineStr">
         <is>
           <t>2 bags</t>
         </is>
       </c>
-      <c r="I100" s="16" t="inlineStr">
+      <c r="I105" s="16" t="inlineStr">
         <is>
           <t>Purchased; delivered direct to Rex or via van</t>
         </is>
       </c>
-      <c r="J100" s="16" t="inlineStr"/>
-      <c r="K100" s="19" t="inlineStr">
+      <c r="J105" s="16" t="inlineStr"/>
+      <c r="K105" s="19" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L100" s="16" t="inlineStr">
+      <c r="L105" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr"/>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F106" s="16" t="inlineStr"/>
+      <c r="G106" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H106" s="16" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J106" s="16" t="inlineStr"/>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L106" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr"/>
+      <c r="C107" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="inlineStr">
+        <is>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F107" s="16" t="inlineStr"/>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H107" s="16" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J107" s="16" t="inlineStr"/>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L107" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>◆  FRIDAY  —  May 22</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: ~1 items</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B103" s="20" t="inlineStr"/>
-      <c r="C103" s="20" t="inlineStr">
+      <c r="B110" s="20" t="inlineStr"/>
+      <c r="C110" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D103" s="20" t="inlineStr">
+      <c r="D110" s="20" t="inlineStr">
         <is>
           <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
-      <c r="E103" s="20" t="inlineStr"/>
-      <c r="F103" s="20" t="inlineStr"/>
-      <c r="G103" s="20" t="inlineStr"/>
-      <c r="H103" s="20" t="inlineStr"/>
-      <c r="I103" s="20" t="inlineStr">
+      <c r="E110" s="20" t="inlineStr"/>
+      <c r="F110" s="20" t="inlineStr"/>
+      <c r="G110" s="20" t="inlineStr"/>
+      <c r="H110" s="20" t="inlineStr"/>
+      <c r="I110" s="20" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-      <c r="J103" s="20" t="inlineStr"/>
-      <c r="K103" s="21" t="inlineStr">
+      <c r="J110" s="20" t="inlineStr"/>
+      <c r="K110" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L103" s="20" t="inlineStr"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="L110" s="20" t="inlineStr"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B105" s="20" t="inlineStr"/>
-      <c r="C105" s="20" t="inlineStr">
+      <c r="B112" s="20" t="inlineStr"/>
+      <c r="C112" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D105" s="20" t="inlineStr">
+      <c r="D112" s="20" t="inlineStr">
         <is>
           <t>Bean Salad (Fri Lunch)</t>
         </is>
       </c>
-      <c r="E105" s="20" t="inlineStr"/>
-      <c r="F105" s="20" t="inlineStr"/>
-      <c r="G105" s="20" t="inlineStr"/>
-      <c r="H105" s="20" t="inlineStr"/>
-      <c r="I105" s="20" t="inlineStr">
+      <c r="E112" s="20" t="inlineStr"/>
+      <c r="F112" s="20" t="inlineStr"/>
+      <c r="G112" s="20" t="inlineStr"/>
+      <c r="H112" s="20" t="inlineStr"/>
+      <c r="I112" s="20" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="J105" s="20" t="inlineStr"/>
-      <c r="K105" s="21" t="inlineStr">
+      <c r="J112" s="20" t="inlineStr"/>
+      <c r="K112" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L105" s="20" t="inlineStr"/>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
+      <c r="L112" s="20" t="inlineStr"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>120 lbs</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr"/>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H107" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>Stove top</t>
-        </is>
-      </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>180 min</t>
-        </is>
-      </c>
-      <c r="K107" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L107" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="12" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="inlineStr"/>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D108" s="12" t="inlineStr">
-        <is>
-          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F108" s="12" t="inlineStr"/>
-      <c r="G108" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H108" s="12" t="inlineStr"/>
-      <c r="I108" s="12" t="inlineStr">
-        <is>
-          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
-        </is>
-      </c>
-      <c r="J108" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K108" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L108" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="12" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="inlineStr"/>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="inlineStr"/>
-      <c r="G109" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I109" s="12" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-      <c r="J109" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K109" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L109" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="12" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B110" s="12" t="inlineStr"/>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D110" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E110" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="inlineStr"/>
-      <c r="G110" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H110" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I110" s="12" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-      <c r="J110" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K110" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L110" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="14" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B112" s="14" t="inlineStr"/>
-      <c r="C112" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D112" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>60 lbs</t>
-        </is>
-      </c>
-      <c r="F112" s="14" t="inlineStr">
-        <is>
-          <t>10 oz</t>
-        </is>
-      </c>
-      <c r="G112" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H112" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels + Vegan</t>
-        </is>
-      </c>
-      <c r="I112" s="14" t="inlineStr"/>
-      <c r="J112" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K112" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L112" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr"/>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Pineapple Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Oven rice</t>
-        </is>
-      </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K113" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L113" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -4767,616 +4802,585 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
+          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>120 lbs</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr"/>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>Stove top</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>180 min</t>
+        </is>
+      </c>
+      <c r="K114" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr"/>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>60 lbs</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>10 oz</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels + Vegan</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr"/>
+      <c r="J116" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K116" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L116" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr"/>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Pineapple Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven rice</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K117" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr"/>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
           <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr">
+      <c r="E118" s="9" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="F114" s="9" t="inlineStr">
+      <c r="F118" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G114" s="9" t="inlineStr">
+      <c r="G118" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H114" s="9" t="inlineStr">
+      <c r="H118" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I114" s="9" t="inlineStr">
+      <c r="I118" s="9" t="inlineStr">
         <is>
           <t>Frozen; steam at Bloor</t>
         </is>
       </c>
-      <c r="J114" s="9" t="inlineStr">
+      <c r="J118" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K114" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L114" s="9" t="inlineStr">
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L118" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="15" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="16" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B116" s="16" t="inlineStr"/>
-      <c r="C116" s="16" t="inlineStr">
+      <c r="B120" s="16" t="inlineStr"/>
+      <c r="C120" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D116" s="16" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E116" s="16" t="inlineStr">
+      <c r="E120" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F116" s="16" t="inlineStr"/>
-      <c r="G116" s="16" t="inlineStr">
+      <c r="F120" s="16" t="inlineStr"/>
+      <c r="G120" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H116" s="16" t="inlineStr"/>
-      <c r="I116" s="16" t="inlineStr">
+      <c r="H120" s="16" t="inlineStr"/>
+      <c r="I120" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J116" s="16" t="inlineStr"/>
-      <c r="K116" s="18" t="inlineStr">
+      <c r="J120" s="16" t="inlineStr"/>
+      <c r="K120" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L116" s="16" t="inlineStr">
+      <c r="L120" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="16" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B117" s="16" t="inlineStr"/>
-      <c r="C117" s="16" t="inlineStr">
+      <c r="B121" s="16" t="inlineStr"/>
+      <c r="C121" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D117" s="16" t="inlineStr">
+      <c r="D121" s="16" t="inlineStr">
         <is>
           <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
         </is>
       </c>
-      <c r="E117" s="16" t="inlineStr">
+      <c r="E121" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F117" s="16" t="inlineStr"/>
-      <c r="G117" s="16" t="inlineStr"/>
-      <c r="H117" s="16" t="inlineStr"/>
-      <c r="I117" s="16" t="inlineStr">
+      <c r="F121" s="16" t="inlineStr"/>
+      <c r="G121" s="16" t="inlineStr"/>
+      <c r="H121" s="16" t="inlineStr"/>
+      <c r="I121" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J117" s="16" t="inlineStr"/>
-      <c r="K117" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L117" s="16" t="inlineStr">
+      <c r="J121" s="16" t="inlineStr"/>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L121" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B118" s="16" t="inlineStr"/>
-      <c r="C118" s="16" t="inlineStr">
+      <c r="B122" s="16" t="inlineStr"/>
+      <c r="C122" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D118" s="16" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>HOT Pineapple Rice → Dinner side</t>
         </is>
       </c>
-      <c r="E118" s="16" t="inlineStr">
+      <c r="E122" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F118" s="16" t="inlineStr"/>
-      <c r="G118" s="16" t="inlineStr"/>
-      <c r="H118" s="16" t="inlineStr">
+      <c r="F122" s="16" t="inlineStr"/>
+      <c r="G122" s="16" t="inlineStr"/>
+      <c r="H122" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I118" s="16" t="inlineStr">
+      <c r="I122" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J118" s="16" t="inlineStr"/>
-      <c r="K118" s="17" t="inlineStr">
+      <c r="J122" s="16" t="inlineStr"/>
+      <c r="K122" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L118" s="16" t="inlineStr">
+      <c r="L122" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="16" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B119" s="16" t="inlineStr"/>
-      <c r="C119" s="16" t="inlineStr">
+      <c r="B123" s="16" t="inlineStr"/>
+      <c r="C123" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D119" s="16" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="E119" s="16" t="inlineStr">
+      <c r="E123" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F119" s="16" t="inlineStr"/>
-      <c r="G119" s="16" t="inlineStr"/>
-      <c r="H119" s="16" t="inlineStr">
+      <c r="F123" s="16" t="inlineStr"/>
+      <c r="G123" s="16" t="inlineStr"/>
+      <c r="H123" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I119" s="16" t="inlineStr">
+      <c r="I123" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J119" s="16" t="inlineStr"/>
-      <c r="K119" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L119" s="16" t="inlineStr">
+      <c r="J123" s="16" t="inlineStr"/>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L123" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>◆  SATURDAY  —  May 23</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr"/>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr"/>
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr"/>
-      <c r="G122" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H122" s="6" t="inlineStr">
+      <c r="H126" s="6" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I122" s="6" t="inlineStr">
+      <c r="I126" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J122" s="6" t="inlineStr"/>
-      <c r="K122" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L122" s="6" t="inlineStr">
+      <c r="J126" s="6" t="inlineStr"/>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L126" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr"/>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr"/>
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr"/>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="H127" s="6" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J123" s="6" t="inlineStr"/>
-      <c r="K123" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L123" s="6" t="inlineStr">
+      <c r="J127" s="6" t="inlineStr"/>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="14" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B125" s="14" t="inlineStr"/>
-      <c r="C125" s="14" t="inlineStr">
+      <c r="B129" s="14" t="inlineStr"/>
+      <c r="C129" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D125" s="14" t="inlineStr">
+      <c r="D129" s="14" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E125" s="14" t="inlineStr">
+      <c r="E129" s="14" t="inlineStr">
         <is>
           <t>80 lbs + 15 lbs</t>
         </is>
       </c>
-      <c r="F125" s="14" t="inlineStr"/>
-      <c r="G125" s="14" t="inlineStr">
+      <c r="F129" s="14" t="inlineStr"/>
+      <c r="G129" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H125" s="14" t="inlineStr"/>
-      <c r="I125" s="14" t="inlineStr">
+      <c r="H129" s="14" t="inlineStr"/>
+      <c r="I129" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J125" s="14" t="inlineStr">
+      <c r="J129" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K125" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L125" s="14" t="inlineStr">
+      <c r="K129" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L129" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="11" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B127" s="12" t="inlineStr"/>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D127" s="12" t="inlineStr">
-        <is>
-          <t>Griot Marinade</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="inlineStr"/>
-      <c r="G127" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="inlineStr"/>
-      <c r="I127" s="12" t="inlineStr">
-        <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
-        </is>
-      </c>
-      <c r="J127" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K127" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L127" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="inlineStr"/>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D128" s="12" t="inlineStr">
-        <is>
-          <t>Cut/Marinate Pork Griot</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>30kg raw</t>
-        </is>
-      </c>
-      <c r="F128" s="12" t="inlineStr"/>
-      <c r="G128" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="inlineStr">
-        <is>
-          <t>1 bin/2 hotels</t>
-        </is>
-      </c>
-      <c r="I128" s="12" t="inlineStr"/>
-      <c r="J128" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K128" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L128" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B129" s="12" t="inlineStr"/>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Griot</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>25kg raw</t>
-        </is>
-      </c>
-      <c r="F129" s="12" t="inlineStr"/>
-      <c r="G129" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I129" s="12" t="inlineStr"/>
-      <c r="J129" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K129" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L129" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="inlineStr"/>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D130" s="12" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>3 bins + 1 bag</t>
-        </is>
-      </c>
-      <c r="F130" s="12" t="inlineStr"/>
-      <c r="G130" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="H130" s="12" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
-      <c r="I130" s="12" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
-        </is>
-      </c>
-      <c r="J130" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K130" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L130" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
     </row>
@@ -5394,266 +5398,254 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr"/>
       <c r="G131" s="12" t="inlineStr">
         <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr"/>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>For Griot Pork/Chicken/Tofu</t>
+        </is>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K131" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr"/>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>Cut/Marinate Pork Griot</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>30kg raw</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr"/>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="inlineStr">
+        <is>
+          <t>1 bin/2 hotels</t>
+        </is>
+      </c>
+      <c r="I132" s="12" t="inlineStr"/>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K132" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L132" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr"/>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Griot</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>25kg raw</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr"/>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I133" s="12" t="inlineStr"/>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr"/>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="inlineStr"/>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+      <c r="J134" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K134" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L134" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr"/>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="inlineStr"/>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H131" s="12" t="inlineStr">
+      <c r="H135" s="12" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I131" s="12" t="inlineStr">
+      <c r="I135" s="12" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
-      <c r="J131" s="12" t="inlineStr">
+      <c r="J135" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K131" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L131" s="12" t="inlineStr">
+      <c r="K135" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L135" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B132" s="9" t="inlineStr"/>
-      <c r="C132" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D132" s="9" t="inlineStr">
-        <is>
-          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E132" s="9" t="inlineStr">
-        <is>
-          <t>40 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="inlineStr"/>
-      <c r="G132" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H132" s="9" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-      <c r="J132" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K132" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L132" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B133" s="9" t="inlineStr"/>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>32 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr"/>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H133" s="9" t="inlineStr">
-        <is>
-          <t>1.0u</t>
-        </is>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-      <c r="J133" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K133" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L133" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="13" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr"/>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>3 bins → 2 hotels</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr"/>
-      <c r="G135" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H135" s="9" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I135" s="9" t="inlineStr">
-        <is>
-          <t>Stir-fry at LAN; send hot PM</t>
-        </is>
-      </c>
-      <c r="J135" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K135" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L135" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="14" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B136" s="14" t="inlineStr"/>
-      <c r="C136" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D136" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E136" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F136" s="14" t="inlineStr"/>
-      <c r="G136" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I136" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J136" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K136" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L136" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -5671,200 +5663,208 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
+          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>3 bins → 2 hotels</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr"/>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>Stir-fry at LAN; send hot PM</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K137" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L137" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="inlineStr"/>
+      <c r="C138" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="inlineStr"/>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K138" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L138" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr"/>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr">
+      <c r="E139" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F137" s="9" t="inlineStr"/>
-      <c r="G137" s="9" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr">
+      <c r="F139" s="9" t="inlineStr"/>
+      <c r="G139" s="9" t="inlineStr"/>
+      <c r="H139" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I137" s="9" t="inlineStr"/>
-      <c r="J137" s="9" t="inlineStr">
+      <c r="I139" s="9" t="inlineStr"/>
+      <c r="J139" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K137" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L137" s="9" t="inlineStr">
+      <c r="K139" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L139" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="20" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B138" s="20" t="inlineStr"/>
-      <c r="C138" s="20" t="inlineStr">
+      <c r="B140" s="20" t="inlineStr"/>
+      <c r="C140" s="20" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="D138" s="20" t="inlineStr">
+      <c r="D140" s="20" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E138" s="20" t="inlineStr">
+      <c r="E140" s="20" t="inlineStr">
         <is>
           <t>2 pcs</t>
         </is>
       </c>
-      <c r="F138" s="20" t="inlineStr">
+      <c r="F140" s="20" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="G138" s="20" t="inlineStr">
+      <c r="G140" s="20" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H138" s="20" t="inlineStr">
+      <c r="H140" s="20" t="inlineStr">
         <is>
           <t>4" hotel</t>
         </is>
       </c>
-      <c r="I138" s="20" t="inlineStr">
+      <c r="I140" s="20" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
       </c>
-      <c r="J138" s="20" t="inlineStr">
+      <c r="J140" s="20" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K138" s="14" t="inlineStr">
+      <c r="K140" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L138" s="20" t="inlineStr">
+      <c r="L140" s="20" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="15" t="inlineStr">
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="inlineStr"/>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E140" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F140" s="16" t="inlineStr"/>
-      <c r="G140" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H140" s="16" t="inlineStr"/>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J140" s="16" t="inlineStr"/>
-      <c r="K140" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L140" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B141" s="16" t="inlineStr"/>
-      <c r="C141" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D141" s="16" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E141" s="16" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F141" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G141" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H141" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J141" s="16" t="inlineStr"/>
-      <c r="K141" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L141" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -5882,43 +5882,35 @@
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E142" s="16" t="inlineStr">
         <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F142" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F142" s="16" t="inlineStr"/>
       <c r="G142" s="16" t="inlineStr">
         <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H142" s="16" t="inlineStr">
-        <is>
-          <t>1 × 4" hotel</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H142" s="16" t="inlineStr"/>
       <c r="I142" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J142" s="16" t="inlineStr"/>
-      <c r="K142" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K142" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L142" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -5936,39 +5928,43 @@
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="E143" s="16" t="inlineStr">
         <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F143" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G143" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F143" s="16" t="inlineStr"/>
-      <c r="G143" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H143" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J143" s="16" t="inlineStr"/>
-      <c r="K143" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L143" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -5986,19 +5982,27 @@
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E144" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F144" s="16" t="inlineStr"/>
-      <c r="G144" s="16" t="inlineStr"/>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F144" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="H144" s="16" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>1 × 4" hotel</t>
         </is>
       </c>
       <c r="I144" s="16" t="inlineStr">
@@ -6014,7 +6018,7 @@
       </c>
       <c r="L144" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -6032,28 +6036,28 @@
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
         </is>
       </c>
       <c r="E145" s="16" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F145" s="16" t="inlineStr"/>
       <c r="G145" s="16" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="H145" s="16" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex fridge</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J145" s="16" t="inlineStr"/>
@@ -6063,6 +6067,102 @@
         </is>
       </c>
       <c r="L145" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr"/>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E146" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F146" s="16" t="inlineStr"/>
+      <c r="G146" s="16" t="inlineStr"/>
+      <c r="H146" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J146" s="16" t="inlineStr"/>
+      <c r="K146" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L146" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr"/>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="inlineStr">
+        <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F147" s="16" t="inlineStr"/>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H147" s="16" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="J147" s="16" t="inlineStr"/>
+      <c r="K147" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L147" s="16" t="inlineStr">
         <is>
           <t>Produced: LAN day-before</t>
         </is>
@@ -6072,48 +6172,48 @@
   <mergeCells count="44">
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A66:L66"/>
-    <mergeCell ref="A74:L74"/>
+    <mergeCell ref="A90:L90"/>
+    <mergeCell ref="A108:L108"/>
+    <mergeCell ref="A128:L128"/>
+    <mergeCell ref="A56:L56"/>
     <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A120:L120"/>
-    <mergeCell ref="A57:L57"/>
+    <mergeCell ref="A136:L136"/>
     <mergeCell ref="A101:L101"/>
+    <mergeCell ref="A113:L113"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A139:L139"/>
-    <mergeCell ref="A104:L104"/>
+    <mergeCell ref="A86:L86"/>
     <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="A71:L71"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A141:L141"/>
     <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A126:L126"/>
-    <mergeCell ref="A106:L106"/>
-    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A97:L97"/>
+    <mergeCell ref="A109:L109"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A62:L62"/>
-    <mergeCell ref="A81:L81"/>
     <mergeCell ref="A38:L38"/>
-    <mergeCell ref="A96:L96"/>
+    <mergeCell ref="A125:L125"/>
     <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A134:L134"/>
     <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A68:L68"/>
-    <mergeCell ref="A121:L121"/>
     <mergeCell ref="A115:L115"/>
+    <mergeCell ref="A93:L93"/>
     <mergeCell ref="A111:L111"/>
-    <mergeCell ref="A102:L102"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A130:L130"/>
     <mergeCell ref="A39:L39"/>
     <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A77:L77"/>
-    <mergeCell ref="A92:L92"/>
     <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A64:L64"/>
     <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A60:L60"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="A88:L88"/>
+    <mergeCell ref="A119:L119"/>
+    <mergeCell ref="A79:L79"/>
     <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A69:L69"/>
+    <mergeCell ref="A87:L87"/>
+    <mergeCell ref="A65:L65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8376,7 +8476,7 @@
       <c r="H59" s="14" t="inlineStr"/>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>Reheat bagged; pulled from Rex fridge Mon AM</t>
         </is>
       </c>
       <c r="J59" s="14" t="inlineStr">
@@ -8391,7 +8491,7 @@
       </c>
       <c r="L59" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Production</t>
+          <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8534,7 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>Reheat bagged; pulled from Rex fridge Mon AM</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
@@ -8449,7 +8549,7 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Production</t>
+          <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8760,7 @@
       </c>
       <c r="L65" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Production</t>
+          <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -12349,7 +12449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L156"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17023,168 +17123,164 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="12" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr"/>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
-        <is>
-          <t>Vindaloo Sauce (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="inlineStr"/>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="inlineStr"/>
-      <c r="I122" s="12" t="inlineStr">
-        <is>
-          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
-        </is>
-      </c>
-      <c r="J122" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K122" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L122" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="12" t="inlineStr">
+      <c r="B123" s="9" t="inlineStr"/>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr"/>
+      <c r="G123" s="9" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr"/>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D123" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Pork in Vindaloo (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr"/>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H123" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I123" s="12" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-      <c r="J123" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K123" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L123" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="12" t="inlineStr">
+      <c r="B124" s="9" t="inlineStr"/>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr"/>
+      <c r="G124" s="9" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B124" s="12" t="inlineStr"/>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D124" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E124" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F124" s="12" t="inlineStr"/>
-      <c r="G124" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H124" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I124" s="12" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-      <c r="J124" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K124" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L124" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+      <c r="B125" s="14" t="inlineStr"/>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>Heat Spring Rolls (Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>200 pcs</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr"/>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>Purchased frozen; heat day-of at Bloor</t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L125" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -17202,536 +17298,536 @@
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
+          <t>Bok Choy (Fri Dinner side)</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr"/>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 8 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr"/>
+      <c r="C128" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E128" s="16" t="inlineStr">
+        <is>
           <t>5 hotels</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr"/>
-      <c r="G126" s="9" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr">
+      <c r="F128" s="16" t="inlineStr"/>
+      <c r="G128" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H128" s="16" t="inlineStr">
         <is>
           <t>5 hotels</t>
         </is>
       </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="J126" s="9" t="inlineStr">
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J128" s="16" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L128" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr"/>
+      <c r="C129" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D129" s="16" t="inlineStr">
+        <is>
+          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E129" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F129" s="16" t="inlineStr"/>
+      <c r="G129" s="16" t="inlineStr"/>
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J129" s="16" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L129" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr"/>
+      <c r="C130" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>HOT Spring Rolls → Dinner side</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F130" s="16" t="inlineStr"/>
+      <c r="G130" s="16" t="inlineStr"/>
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J130" s="16" t="inlineStr"/>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L130" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>◆  SATURDAY  —  Jun 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr"/>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Friday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr"/>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr"/>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Friday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr"/>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>92 lbs (80+12)</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr"/>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K136" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Saturday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr"/>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>Cut/Season Tandoori Pork</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr"/>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>hotels</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="inlineStr">
+        <is>
+          <t>Season w/Vindaloo Dry Spice Mix</t>
+        </is>
+      </c>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K138" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L138" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr"/>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Tandoori Marinade</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr"/>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="inlineStr"/>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K139" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Tandoori Production Wk. 4 Monday</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr"/>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr"/>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>bins</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>3 bins (6u)</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr"/>
+      <c r="J140" s="12" t="inlineStr">
         <is>
           <t>90 min</t>
         </is>
       </c>
-      <c r="K126" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L126" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="inlineStr"/>
-      <c r="C127" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="inlineStr"/>
-      <c r="G127" s="9" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="J127" s="9" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K127" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L127" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="14" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B128" s="14" t="inlineStr"/>
-      <c r="C128" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D128" s="14" t="inlineStr">
-        <is>
-          <t>Heat Spring Rolls (Fri Dinner side)</t>
-        </is>
-      </c>
-      <c r="E128" s="14" t="inlineStr">
-        <is>
-          <t>200 pcs</t>
-        </is>
-      </c>
-      <c r="F128" s="14" t="inlineStr"/>
-      <c r="G128" s="14" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H128" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I128" s="14" t="inlineStr">
-        <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
-        </is>
-      </c>
-      <c r="J128" s="14" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="K128" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L128" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="inlineStr"/>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>Bok Choy (Fri Dinner side)</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="inlineStr"/>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H129" s="9" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
-        </is>
-      </c>
-      <c r="J129" s="9" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K129" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L129" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 8 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="inlineStr"/>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="E131" s="16" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F131" s="16" t="inlineStr"/>
-      <c r="G131" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H131" s="16" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J131" s="16" t="inlineStr"/>
-      <c r="K131" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L131" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B132" s="16" t="inlineStr"/>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E132" s="16" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="F132" s="16" t="inlineStr"/>
-      <c r="G132" s="16" t="inlineStr"/>
-      <c r="H132" s="16" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J132" s="16" t="inlineStr"/>
-      <c r="K132" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L132" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B133" s="16" t="inlineStr"/>
-      <c r="C133" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D133" s="16" t="inlineStr">
-        <is>
-          <t>HOT Spring Rolls → Dinner side</t>
-        </is>
-      </c>
-      <c r="E133" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F133" s="16" t="inlineStr"/>
-      <c r="G133" s="16" t="inlineStr"/>
-      <c r="H133" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J133" s="16" t="inlineStr"/>
-      <c r="K133" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L133" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="22" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>◆  SATURDAY  —  Jun 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr"/>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J136" s="6" t="inlineStr"/>
-      <c r="K136" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L136" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr"/>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>12 lbs</t>
-        </is>
-      </c>
-      <c r="F137" s="6" t="inlineStr">
-        <is>
-          <t>4 oz</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J137" s="6" t="inlineStr"/>
-      <c r="K137" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L137" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="14" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B139" s="14" t="inlineStr"/>
-      <c r="C139" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D139" s="14" t="inlineStr">
-        <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="E139" s="14" t="inlineStr">
-        <is>
-          <t>92 lbs (80+12)</t>
-        </is>
-      </c>
-      <c r="F139" s="14" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="G139" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H139" s="14" t="inlineStr"/>
-      <c r="I139" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J139" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K139" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L139" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Saturday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
+      <c r="K140" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L140" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
         </is>
       </c>
     </row>
@@ -17749,43 +17845,43 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Cut/Season Tandoori Pork</t>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>1 cs</t>
+          <t>3 bins + 1 bag</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr"/>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>hotels</t>
+          <t>bus bin/bag</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>1.5u</t>
+          <t>4 items</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>Season w/Vindaloo Dry Spice Mix</t>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K141" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K141" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
     </row>
@@ -17803,39 +17899,35 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>Tandoori Marinade</t>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr"/>
-      <c r="G142" s="12" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H142" s="12" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I142" s="12" t="inlineStr"/>
+      <c r="G142" s="12" t="inlineStr"/>
+      <c r="H142" s="12" t="inlineStr"/>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+        </is>
+      </c>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K142" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K142" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L142" s="12" t="inlineStr">
         <is>
-          <t>Serves: Tandoori Production Wk. 4 Monday</t>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
     </row>
@@ -17853,29 +17945,33 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr"/>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>bins</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>3 bins (6u)</t>
-        </is>
-      </c>
-      <c r="I143" s="12" t="inlineStr"/>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>90 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="K143" s="10" t="inlineStr">
@@ -17885,589 +17981,327 @@
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="12" t="inlineStr">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B144" s="12" t="inlineStr"/>
-      <c r="C144" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D144" s="12" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="E144" s="12" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr"/>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>110lbs</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>320 min</t>
+        </is>
+      </c>
+      <c r="K144" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L144" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr"/>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>Potato Wedges (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr"/>
+      <c r="G146" s="9" t="inlineStr"/>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>Purchased frozen; oven</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L146" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 4.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr"/>
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F148" s="16" t="inlineStr"/>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr"/>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="J148" s="16" t="inlineStr"/>
+      <c r="K148" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L148" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr"/>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F149" s="16" t="inlineStr"/>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>boxes</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>Vendor → Rex | Driver collects ordered pizza</t>
+        </is>
+      </c>
+      <c r="J149" s="16" t="inlineStr"/>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="L149" s="16" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr"/>
+      <c r="C150" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F144" s="12" t="inlineStr"/>
-      <c r="G144" s="12" t="inlineStr">
+      <c r="F150" s="16" t="inlineStr"/>
+      <c r="G150" s="16" t="inlineStr">
         <is>
           <t>bus bin/bag</t>
         </is>
       </c>
-      <c r="H144" s="12" t="inlineStr">
+      <c r="H150" s="16" t="inlineStr">
         <is>
           <t>4 items</t>
         </is>
       </c>
-      <c r="I144" s="12" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
-        </is>
-      </c>
-      <c r="J144" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K144" s="14" t="inlineStr">
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="J150" s="16" t="inlineStr"/>
+      <c r="K150" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L144" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="12" t="inlineStr">
+      <c r="L150" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B145" s="12" t="inlineStr"/>
-      <c r="C145" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D145" s="12" t="inlineStr">
-        <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="inlineStr">
+      <c r="B151" s="16" t="inlineStr"/>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>HOT Potato Wedges → Dinner</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F145" s="12" t="inlineStr"/>
-      <c r="G145" s="12" t="inlineStr"/>
-      <c r="H145" s="12" t="inlineStr"/>
-      <c r="I145" s="12" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
-        </is>
-      </c>
-      <c r="J145" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K145" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L145" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="inlineStr"/>
-      <c r="C146" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D146" s="12" t="inlineStr">
-        <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="F146" s="12" t="inlineStr"/>
-      <c r="G146" s="12" t="inlineStr">
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H146" s="12" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I146" s="12" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
-      <c r="J146" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K146" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L146" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="inlineStr"/>
-      <c r="C147" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
-        </is>
-      </c>
-      <c r="E147" s="9" t="inlineStr">
-        <is>
-          <t>110lbs</t>
-        </is>
-      </c>
-      <c r="F147" s="9" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H147" s="9" t="inlineStr">
+      <c r="H151" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I147" s="9" t="inlineStr">
-        <is>
-          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
-        </is>
-      </c>
-      <c r="J147" s="9" t="inlineStr">
-        <is>
-          <t>320 min</t>
-        </is>
-      </c>
-      <c r="K147" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L147" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="inlineStr"/>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr">
-        <is>
-          <t>Cook Pork Vindaloo (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>40 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr"/>
-      <c r="G148" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H148" s="9" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K148" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L148" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="inlineStr"/>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>Cook Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>32 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr"/>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H149" s="9" t="inlineStr">
-        <is>
-          <t>1.0u</t>
-        </is>
-      </c>
-      <c r="I149" s="9" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-      <c r="J149" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K149" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L149" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="inlineStr"/>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>Potato Wedges (Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr"/>
-      <c r="G151" s="9" t="inlineStr"/>
-      <c r="H151" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I151" s="9" t="inlineStr">
-        <is>
-          <t>Purchased frozen; oven</t>
-        </is>
-      </c>
-      <c r="J151" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K151" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 4.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B153" s="16" t="inlineStr"/>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D153" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E153" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F153" s="16" t="inlineStr"/>
-      <c r="G153" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H153" s="16" t="inlineStr"/>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J153" s="16" t="inlineStr"/>
-      <c r="K153" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L153" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B154" s="16" t="inlineStr"/>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D154" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
-        </is>
-      </c>
-      <c r="E154" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F154" s="16" t="inlineStr"/>
-      <c r="G154" s="16" t="inlineStr">
-        <is>
-          <t>boxes</t>
-        </is>
-      </c>
-      <c r="H154" s="16" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="I154" s="16" t="inlineStr">
-        <is>
-          <t>Vendor → Rex | Driver collects ordered pizza</t>
-        </is>
-      </c>
-      <c r="J154" s="16" t="inlineStr"/>
-      <c r="K154" s="7" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="L154" s="16" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B155" s="16" t="inlineStr"/>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D155" s="16" t="inlineStr">
-        <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
-        </is>
-      </c>
-      <c r="E155" s="16" t="inlineStr">
-        <is>
-          <t>3 bins + 1 bag</t>
-        </is>
-      </c>
-      <c r="F155" s="16" t="inlineStr"/>
-      <c r="G155" s="16" t="inlineStr">
-        <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="H155" s="16" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
-      <c r="I155" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex fridge</t>
-        </is>
-      </c>
-      <c r="J155" s="16" t="inlineStr"/>
-      <c r="K155" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L155" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="inlineStr"/>
-      <c r="C156" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>HOT Potato Wedges → Dinner</t>
-        </is>
-      </c>
-      <c r="E156" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F156" s="16" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="G156" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H156" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I156" s="16" t="inlineStr">
+      <c r="I151" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J156" s="16" t="inlineStr"/>
-      <c r="K156" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L156" s="16" t="inlineStr">
+      <c r="J151" s="16" t="inlineStr"/>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L151" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Dinner (same day)</t>
         </is>
@@ -18478,9 +18312,11 @@
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A90:L90"/>
+    <mergeCell ref="A137:L137"/>
     <mergeCell ref="A46:L46"/>
     <mergeCell ref="A75:L75"/>
     <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A145:L145"/>
     <mergeCell ref="A57:L57"/>
     <mergeCell ref="A113:L113"/>
     <mergeCell ref="A2:L2"/>
@@ -18489,33 +18325,31 @@
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A97:L97"/>
     <mergeCell ref="A135:L135"/>
-    <mergeCell ref="A150:L150"/>
     <mergeCell ref="A106:L106"/>
-    <mergeCell ref="A140:L140"/>
+    <mergeCell ref="A122:L122"/>
     <mergeCell ref="A91:L91"/>
+    <mergeCell ref="A131:L131"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A62:L62"/>
     <mergeCell ref="A100:L100"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="A134:L134"/>
+    <mergeCell ref="A147:L147"/>
     <mergeCell ref="A43:L43"/>
     <mergeCell ref="A112:L112"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A68:L68"/>
-    <mergeCell ref="A152:L152"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A115:L115"/>
     <mergeCell ref="A117:L117"/>
+    <mergeCell ref="A127:L127"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A130:L130"/>
     <mergeCell ref="A83:L83"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A73:L73"/>
     <mergeCell ref="A49:L49"/>
-    <mergeCell ref="A138:L138"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A94:L94"/>
+    <mergeCell ref="A132:L132"/>
     <mergeCell ref="A36:L36"/>
     <mergeCell ref="A69:L69"/>
   </mergeCells>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -837,7 +837,7 @@
       <c r="H10" s="12" t="inlineStr"/>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>PREP ONLY — no oven. Shape, bread, freeze in blast chiller all day.</t>
+          <t>Bread, shape, blast-chill; NO oven — all hands-on</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -12755,7 +12755,7 @@
       <c r="H11" s="12" t="inlineStr"/>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>PREP ONLY — no oven. Shape, bread, freeze; blast chiller</t>
+          <t>Bread, shape, blast-chill; NO oven — all hands-on</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L147"/>
+  <dimension ref="A1:L155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1530,176 +1530,168 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr"/>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr"/>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr"/>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool; use same day for marinade</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr"/>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr"/>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr"/>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr"/>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Cook Jerk Chicken Legs (Mon Dinner)</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>165 pcs</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr"/>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>3 bins (6u)</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Bone-in legs; roast</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr"/>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Jerk Cauliflower (Mon Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>12 portions</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Roast</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr"/>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Rice &amp; Beans</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels (hot)</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Oven</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1709,12 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Cabbage &amp; Carrot Stir-fry (Mon Dinner side)</t>
+          <t>Cook Jerk Chicken Legs (Mon Dinner)</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>165 pcs</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -1733,662 +1725,666 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
+          <t>3 bins (6u)</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Bone-in legs; roast</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Monday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Jerk Cauliflower (Mon Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>12 portions</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Roast</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Monday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Rice &amp; Beans</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels (hot)</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Monday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Cabbage &amp; Carrot Stir-fry (Mon Dinner side)</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr"/>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>Stir-fry at LAN; send hot PM</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
+      <c r="K36" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Monday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 5.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr"/>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr"/>
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr"/>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr"/>
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr"/>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr"/>
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J35" s="16" t="inlineStr"/>
-      <c r="K35" s="18" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr"/>
+      <c r="K38" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L35" s="16" t="inlineStr">
+      <c r="L38" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr"/>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr"/>
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>HOT Jerk Chicken → Dinner</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>1.5 hotels</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr"/>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr"/>
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>3 bins (6u)</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr"/>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L36" s="16" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Monday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr"/>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr"/>
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>HOT Rice &amp; Beans → Dinner</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr"/>
-      <c r="G37" s="16" t="inlineStr"/>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr"/>
+      <c r="G40" s="16" t="inlineStr"/>
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J37" s="16" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L37" s="16" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L40" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Monday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>◆  TUESDAY  —  May 19</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr"/>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr"/>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>HOT Beef Nacho Mix → Lunch</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J40" s="6" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L40" s="6" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Tuesday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr"/>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr"/>
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>HOT Vegan Nacho Mix → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>0.5 hotels</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J41" s="6" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Tuesday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr"/>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr"/>
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>Reheat Beef Nacho Mix (Tue Lunch)</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr"/>
-      <c r="I43" s="14" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr"/>
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged; pulled from Rex fridge Mon AM</t>
         </is>
       </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Wednesday Production (cold chain via Rex)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr"/>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr"/>
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>Reheat Vegan Nacho Mix (Tue Lunch)</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>15 lbs</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr"/>
-      <c r="G44" s="14" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr"/>
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr"/>
-      <c r="I44" s="14" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr"/>
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Tuesday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr"/>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr"/>
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>Trim/Season Shakshuka Chicken Legs (→ Wed Dinner)</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>165 pcs</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>bus bin</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>3 bins (6u)</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr"/>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr"/>
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>120 min</t>
         </is>
       </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr"/>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr"/>
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>Adobo Marinade (→ Fri Dinner)</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>recipe</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr"/>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr"/>
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>cambro</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="12" t="inlineStr"/>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr"/>
+      <c r="I50" s="12" t="inlineStr"/>
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K47" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Pork/Chicken Adobo (→ Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr"/>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>2 bins/4 hotels</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="12" t="inlineStr"/>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>3 min</t>
-        </is>
-      </c>
-      <c r="K48" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr"/>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Cook West African Peanut Stew Base (→ Wk2 Mon Dinner)</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>2.5u</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Stove top braise 3hrs; reserve 12 lbs vegan BEFORE adding chicken; vac bag</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>180 min</t>
-        </is>
-      </c>
-      <c r="K49" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Monday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr"/>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>Vegan Peanut Stew (→ Wk2 Mon Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>12 lbs</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Reserved from base stew before chicken added; vac bag separately</t>
-        </is>
-      </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>(incl. above) min</t>
-        </is>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L50" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Monday Dinner</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2402,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Tomato Cucumber Salad (→ Thu Lunch)</t>
+          <t>Cut &amp; Marinate Pork for Adobo (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr"/>
@@ -2427,22 +2423,22 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Mix; chill; send Wed PM</t>
+          <t>Cut pork; coat in Adobo Marinade; chill overnight</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk.1 Thursday Lunch</t>
+          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -2460,75 +2456,91 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Prep Chiffonade Lettuce &amp; Sliced Peppers (→ Wed Lunch)</t>
+          <t>Marinate Chicken for Adobo — Halal (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr"/>
-      <c r="G52" s="12" t="inlineStr"/>
-      <c r="H52" s="12" t="inlineStr"/>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Prep at LAN; send cold Wed AM</t>
+          <t>Coat in Adobo Marinade; chill overnight</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K52" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Wednesday Lunch</t>
+          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr"/>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr"/>
-      <c r="G53" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>Stove; simmer; cool; use same day for marinade</t>
-        </is>
-      </c>
-      <c r="J53" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
+      <c r="B53" s="9" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Cook West African Peanut Stew Base (→ Wk2 Mon Dinner)</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>2.5u</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Stove top braise 3hrs; reserve 12 lbs vegan BEFORE adding chicken; vac bag</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>180 min</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
@@ -2536,53 +2548,57 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Monday Dinner</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr"/>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr"/>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-      <c r="J54" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
+      <c r="B54" s="9" t="inlineStr"/>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Vegan Peanut Stew (→ Wk2 Mon Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Reserved from base stew before chicken added; vac bag separately</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>(incl. above) min</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
@@ -2590,9 +2606,9 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="L54" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Monday Dinner</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2626,12 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+          <t>Tomato Cucumber Salad (→ Thu Lunch)</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>1 cs</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr"/>
@@ -2626,839 +2642,835 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+          <t>Mix; chill; send Wed PM</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk.1 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr"/>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Prep Chiffonade Lettuce &amp; Sliced Peppers (→ Wed Lunch)</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr"/>
+      <c r="G56" s="12" t="inlineStr"/>
+      <c r="H56" s="12" t="inlineStr"/>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>Prep at LAN; send cold Wed AM</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Wednesday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr"/>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor → send Wed PM</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr"/>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr"/>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor → send Wed PM</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr"/>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Pork Carnitas (Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>5 oz</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>Pork braise</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L60" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr"/>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Halal Chicken Carnitas (Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>5 oz</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>Pork braise</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L61" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr"/>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Steam Broccoli (Tue Dinner side)</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K55" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L55" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 7 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr"/>
-      <c r="C57" s="14" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr"/>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr"/>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="inlineStr"/>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="J64" s="16" t="inlineStr"/>
+      <c r="K64" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L64" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr"/>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>5 oz</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J65" s="16" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L65" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr"/>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>HOT Broccoli → Dinner</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J66" s="16" t="inlineStr"/>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L66" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Tuesday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>◆  WEDNESDAY  —  May 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 5.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr"/>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>HOT Crispy Chicken Tenders → Lunch</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Lunch (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr"/>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>HOT Vegan Tenders → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Lunch (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr"/>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk.1 Wed Lunch (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr"/>
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>Pork Carnitas (Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>40 lbs</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>5 oz</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>Pork braise</t>
-        </is>
-      </c>
-      <c r="J57" s="14" t="inlineStr">
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>4.5 hotels</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr"/>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr"/>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>Frozen → oven</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L73" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Wednesday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr"/>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>30 pcs</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr"/>
+      <c r="G75" s="12" t="inlineStr"/>
+      <c r="H75" s="12" t="inlineStr"/>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>Cook quinoa; combine; form cakes; chill overnight</t>
+        </is>
+      </c>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr"/>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr"/>
+      <c r="G76" s="9" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>Stove top</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K57" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L57" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="inlineStr"/>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>Halal Chicken Carnitas (Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>32 lbs</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>5 oz</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>Pork braise</t>
-        </is>
-      </c>
-      <c r="J58" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K58" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L58" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr"/>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>Steam Broccoli (Tue Dinner side)</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>4 oz</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K59" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 7 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B61" s="16" t="inlineStr"/>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr"/>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H61" s="16" t="inlineStr"/>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J61" s="16" t="inlineStr"/>
-      <c r="K61" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L61" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="inlineStr"/>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>5 oz</t>
-        </is>
-      </c>
-      <c r="G62" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H62" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J62" s="16" t="inlineStr"/>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L62" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr"/>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>HOT Broccoli → Dinner</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>4 oz</t>
-        </is>
-      </c>
-      <c r="G63" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H63" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J63" s="16" t="inlineStr"/>
-      <c r="K63" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L63" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Tuesday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>◆  WEDNESDAY  —  May 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 5.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr"/>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>HOT Crispy Chicken Tenders → Lunch</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr"/>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr"/>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L66" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Lunch (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr"/>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>HOT Vegan Tenders → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr"/>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr"/>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Lunch (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr"/>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr"/>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr"/>
-      <c r="K68" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L68" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk.1 Wed Lunch (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="inlineStr"/>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
-        <is>
-          <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>4.5 hotels</t>
-        </is>
-      </c>
-      <c r="F70" s="14" t="inlineStr"/>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H70" s="14" t="inlineStr"/>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>Frozen → oven</t>
-        </is>
-      </c>
-      <c r="J70" s="14" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L70" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Wednesday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>Cook Adobo Pork/Chicken</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>40 lbs/32 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>Oven/Combi</t>
-        </is>
-      </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K72" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L72" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="inlineStr"/>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr"/>
-      <c r="G73" s="12" t="inlineStr"/>
-      <c r="H73" s="12" t="inlineStr"/>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>Cook quinoa; combine; form cakes; chill overnight</t>
-        </is>
-      </c>
-      <c r="J73" s="12" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K73" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L73" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Thursday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr"/>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr"/>
-      <c r="G74" s="9" t="inlineStr"/>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>1/2 hotel</t>
-        </is>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>Stove top</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L74" s="9" t="inlineStr">
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr"/>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr"/>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="I75" s="9" t="inlineStr"/>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K75" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="inlineStr"/>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D76" s="12" t="inlineStr">
-        <is>
-          <t>Bean Salad (→ Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="inlineStr"/>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I76" s="12" t="inlineStr">
-        <is>
-          <t>Dress; chill; send Thu PM</t>
-        </is>
-      </c>
-      <c r="J76" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K76" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L76" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk.1 Friday Lunch</t>
         </is>
       </c>
     </row>
@@ -3476,158 +3488,201 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
+          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>40 lbs cooked</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
       <c r="G77" s="9" t="inlineStr">
         <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr"/>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr"/>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Bean Salad (→ Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr"/>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>Dress; chill; send Thu PM</t>
+        </is>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K78" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L78" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk.1 Friday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr"/>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Cook Pork Adobo (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr"/>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>1.5u</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>Oven/Combi; cool; vac bag</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>120 min</t>
         </is>
       </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr"/>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>32 lbs cooked</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr"/>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>1.0u</t>
-        </is>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
-        </is>
-      </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Oven/Combi; cool; vac bag</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Tuesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B80" s="14" t="inlineStr"/>
-      <c r="C80" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F80" s="14" t="inlineStr"/>
-      <c r="G80" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H80" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged batch</t>
-        </is>
-      </c>
-      <c r="J80" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="L80" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Monday Production (prev. cycle)</t>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -3645,685 +3700,681 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
+          <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>165 pcs</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr"/>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr"/>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged batch</t>
+        </is>
+      </c>
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L83" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Monday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
           <t>Herbed Couscous (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F84" s="9" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G84" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr"/>
-      <c r="J81" s="9" t="inlineStr">
+      <c r="I84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K81" s="14" t="inlineStr">
+      <c r="K84" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr">
+      <c r="L84" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 6 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="16" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 12.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B83" s="16" t="inlineStr"/>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr"/>
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E86" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F83" s="16" t="inlineStr"/>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="F86" s="16" t="inlineStr"/>
+      <c r="G86" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H83" s="16" t="inlineStr"/>
-      <c r="I83" s="16" t="inlineStr">
+      <c r="H86" s="16" t="inlineStr"/>
+      <c r="I86" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J83" s="16" t="inlineStr"/>
-      <c r="K83" s="18" t="inlineStr">
+      <c r="J86" s="16" t="inlineStr"/>
+      <c r="K86" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L83" s="16" t="inlineStr">
+      <c r="L86" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="16" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B84" s="16" t="inlineStr"/>
-      <c r="C84" s="16" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr"/>
+      <c r="C87" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>HOT Shakshuka Sauce → Dinner</t>
         </is>
       </c>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="E87" s="16" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F84" s="16" t="inlineStr"/>
-      <c r="G84" s="16" t="inlineStr">
+      <c r="F87" s="16" t="inlineStr"/>
+      <c r="G87" s="16" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H84" s="16" t="inlineStr">
+      <c r="H87" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I84" s="16" t="inlineStr">
+      <c r="I87" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J84" s="16" t="inlineStr"/>
-      <c r="K84" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L84" s="16" t="inlineStr">
+      <c r="J87" s="16" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L87" s="16" t="inlineStr">
         <is>
           <t>Produced: pre-loaded batch (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B85" s="16" t="inlineStr"/>
-      <c r="C85" s="16" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr"/>
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>HOT Herbed Couscous → Dinner side</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E88" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F85" s="16" t="inlineStr"/>
-      <c r="G85" s="16" t="inlineStr"/>
-      <c r="H85" s="16" t="inlineStr">
+      <c r="F88" s="16" t="inlineStr"/>
+      <c r="G88" s="16" t="inlineStr"/>
+      <c r="H88" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I85" s="16" t="inlineStr">
+      <c r="I88" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J85" s="16" t="inlineStr"/>
-      <c r="K85" s="17" t="inlineStr">
+      <c r="J88" s="16" t="inlineStr"/>
+      <c r="K88" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L85" s="16" t="inlineStr">
+      <c r="L88" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr"/>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr"/>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H89" s="16" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J89" s="16" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L89" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Tuesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr"/>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr"/>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J90" s="16" t="inlineStr"/>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L90" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Tuesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="inlineStr"/>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>HOT Shakshuka Chicken Legs → Dinner</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="inlineStr">
+        <is>
+          <t>165 pcs</t>
+        </is>
+      </c>
+      <c r="F91" s="16" t="inlineStr"/>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H91" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J91" s="16" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L91" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>◆  THURSDAY  —  May 21</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 4 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr"/>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>HOT Halal Chicken Burgers → Lunch</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>185 pcs</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr"/>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I94" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J88" s="6" t="inlineStr"/>
-      <c r="K88" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L88" s="6" t="inlineStr">
+      <c r="J94" s="6" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr"/>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr"/>
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>HOT Quinoa Burgers → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>20 pcs</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr"/>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr"/>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J89" s="6" t="inlineStr"/>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L89" s="6" t="inlineStr">
+      <c r="J95" s="6" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr"/>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr"/>
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
         <is>
           <t>Halal Chicken Burgers (Thu Lunch)</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="E97" s="9" t="inlineStr">
         <is>
           <t>185 pcs</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr"/>
-      <c r="G91" s="9" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr"/>
+      <c r="G97" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H91" s="9" t="inlineStr">
+      <c r="H97" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I91" s="9" t="inlineStr"/>
-      <c r="J91" s="9" t="inlineStr">
+      <c r="I97" s="9" t="inlineStr"/>
+      <c r="J97" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K91" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L91" s="9" t="inlineStr">
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Thursday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr"/>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="D98" s="9" t="inlineStr">
         <is>
           <t>Quinoa Burgers (Thu Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="E98" s="9" t="inlineStr">
         <is>
           <t>30 pcs</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr"/>
-      <c r="G92" s="9" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr">
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
+      <c r="I98" s="9" t="inlineStr">
         <is>
           <t>Pan fry; send hot AM</t>
         </is>
       </c>
-      <c r="J92" s="9" t="inlineStr">
+      <c r="J98" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K92" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L92" s="9" t="inlineStr">
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr"/>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>130 lbs</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>3.5 hotels</t>
-        </is>
-      </c>
-      <c r="I94" s="9" t="inlineStr"/>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>240 min</t>
-        </is>
-      </c>
-      <c r="K94" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L94" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Monday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr"/>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>12 lbs</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr"/>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="I95" s="9" t="inlineStr"/>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K95" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr"/>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr"/>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H96" s="9" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="I96" s="9" t="inlineStr"/>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K96" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B98" s="14" t="inlineStr"/>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D98" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Butter Chicken (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F98" s="14" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G98" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H98" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I98" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J98" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K98" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L98" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B99" s="14" t="inlineStr"/>
-      <c r="C99" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="inlineStr">
-        <is>
-          <t>20 lbs</t>
-        </is>
-      </c>
-      <c r="F99" s="14" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H99" s="14" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I99" s="14" t="inlineStr"/>
-      <c r="J99" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K99" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L99" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -4341,623 +4392,619 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
+          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>130 lbs</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>3.5 hotels</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>240 min</t>
+        </is>
+      </c>
+      <c r="K100" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Monday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr"/>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr"/>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr"/>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr"/>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Butter Chicken (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L104" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr"/>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>20 lbs</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr"/>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L105" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr"/>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
           <t>Roasted Cauliflower (Thu Dinner side)</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="E106" s="9" t="inlineStr">
         <is>
           <t>3 bins → 3 hotels</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="F106" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="G106" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H100" s="9" t="inlineStr">
+      <c r="H106" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
+      <c r="I106" s="9" t="inlineStr">
         <is>
           <t>⚠ CONFIRM carrot role in this side</t>
         </is>
       </c>
-      <c r="J100" s="9" t="inlineStr">
+      <c r="J106" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K100" s="14" t="inlineStr">
+      <c r="K106" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L100" s="9" t="inlineStr">
+      <c r="L106" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Thursday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 7.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="16" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B102" s="16" t="inlineStr"/>
-      <c r="C102" s="16" t="inlineStr">
+      <c r="B108" s="16" t="inlineStr"/>
+      <c r="C108" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D102" s="16" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E102" s="16" t="inlineStr">
+      <c r="E108" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F102" s="16" t="inlineStr"/>
-      <c r="G102" s="16" t="inlineStr">
+      <c r="F108" s="16" t="inlineStr"/>
+      <c r="G108" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H102" s="16" t="inlineStr"/>
-      <c r="I102" s="16" t="inlineStr">
+      <c r="H108" s="16" t="inlineStr"/>
+      <c r="I108" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J102" s="16" t="inlineStr"/>
-      <c r="K102" s="18" t="inlineStr">
+      <c r="J108" s="16" t="inlineStr"/>
+      <c r="K108" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L102" s="16" t="inlineStr">
+      <c r="L108" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="16" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B103" s="16" t="inlineStr"/>
-      <c r="C103" s="16" t="inlineStr">
+      <c r="B109" s="16" t="inlineStr"/>
+      <c r="C109" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D103" s="16" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
         <is>
           <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
         </is>
       </c>
-      <c r="E103" s="16" t="inlineStr">
+      <c r="E109" s="16" t="inlineStr">
         <is>
           <t>80+20 lbs</t>
         </is>
       </c>
-      <c r="F103" s="16" t="inlineStr">
+      <c r="F109" s="16" t="inlineStr">
         <is>
           <t>12 oz</t>
         </is>
       </c>
-      <c r="G103" s="16" t="inlineStr">
+      <c r="G109" s="16" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H103" s="16" t="inlineStr">
+      <c r="H109" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I103" s="16" t="inlineStr">
+      <c r="I109" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J103" s="16" t="inlineStr"/>
-      <c r="K103" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L103" s="16" t="inlineStr">
+      <c r="J109" s="16" t="inlineStr"/>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L109" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="16" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B104" s="16" t="inlineStr"/>
-      <c r="C104" s="16" t="inlineStr">
+      <c r="B110" s="16" t="inlineStr"/>
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D104" s="16" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>HOT Roasted Cauliflower → Dinner side</t>
         </is>
       </c>
-      <c r="E104" s="16" t="inlineStr">
+      <c r="E110" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F104" s="16" t="inlineStr"/>
-      <c r="G104" s="16" t="inlineStr"/>
-      <c r="H104" s="16" t="inlineStr">
+      <c r="F110" s="16" t="inlineStr"/>
+      <c r="G110" s="16" t="inlineStr"/>
+      <c r="H110" s="16" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I104" s="16" t="inlineStr">
+      <c r="I110" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J104" s="16" t="inlineStr"/>
-      <c r="K104" s="17" t="inlineStr">
+      <c r="J110" s="16" t="inlineStr"/>
+      <c r="K110" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L104" s="16" t="inlineStr">
+      <c r="L110" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="16" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B105" s="16" t="inlineStr"/>
-      <c r="C105" s="16" t="inlineStr">
+      <c r="B111" s="16" t="inlineStr"/>
+      <c r="C111" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D105" s="16" t="inlineStr">
+      <c r="D111" s="16" t="inlineStr">
         <is>
           <t>HOT Naan → Dinner</t>
         </is>
       </c>
-      <c r="E105" s="16" t="inlineStr">
+      <c r="E111" s="16" t="inlineStr">
         <is>
           <t>200 pcs</t>
         </is>
       </c>
-      <c r="F105" s="16" t="inlineStr">
+      <c r="F111" s="16" t="inlineStr">
         <is>
           <t>1 each (?)</t>
         </is>
       </c>
-      <c r="G105" s="16" t="inlineStr">
+      <c r="G111" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H105" s="16" t="inlineStr">
+      <c r="H111" s="16" t="inlineStr">
         <is>
           <t>2 bags</t>
         </is>
       </c>
-      <c r="I105" s="16" t="inlineStr">
+      <c r="I111" s="16" t="inlineStr">
         <is>
           <t>Purchased; delivered direct to Rex or via van</t>
         </is>
       </c>
-      <c r="J105" s="16" t="inlineStr"/>
-      <c r="K105" s="19" t="inlineStr">
+      <c r="J111" s="16" t="inlineStr"/>
+      <c r="K111" s="19" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L105" s="16" t="inlineStr">
+      <c r="L111" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B106" s="16" t="inlineStr"/>
-      <c r="C106" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D106" s="16" t="inlineStr">
-        <is>
-          <t>Cold Pork Vindaloo → Rex fridge</t>
-        </is>
-      </c>
-      <c r="E106" s="16" t="inlineStr">
-        <is>
-          <t>40 lbs</t>
-        </is>
-      </c>
-      <c r="F106" s="16" t="inlineStr"/>
-      <c r="G106" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H106" s="16" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J106" s="16" t="inlineStr"/>
-      <c r="K106" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L106" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B107" s="16" t="inlineStr"/>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D107" s="16" t="inlineStr">
-        <is>
-          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
-        </is>
-      </c>
-      <c r="E107" s="16" t="inlineStr">
-        <is>
-          <t>32 lbs</t>
-        </is>
-      </c>
-      <c r="F107" s="16" t="inlineStr"/>
-      <c r="G107" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H107" s="16" t="inlineStr">
-        <is>
-          <t>1.0u</t>
-        </is>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J107" s="16" t="inlineStr"/>
-      <c r="K107" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L107" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>◆  FRIDAY  —  May 22</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: ~1 items</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B110" s="20" t="inlineStr"/>
-      <c r="C110" s="20" t="inlineStr">
+      <c r="B114" s="20" t="inlineStr"/>
+      <c r="C114" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D110" s="20" t="inlineStr">
+      <c r="D114" s="20" t="inlineStr">
         <is>
           <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
-      <c r="E110" s="20" t="inlineStr"/>
-      <c r="F110" s="20" t="inlineStr"/>
-      <c r="G110" s="20" t="inlineStr"/>
-      <c r="H110" s="20" t="inlineStr"/>
-      <c r="I110" s="20" t="inlineStr">
+      <c r="E114" s="20" t="inlineStr"/>
+      <c r="F114" s="20" t="inlineStr"/>
+      <c r="G114" s="20" t="inlineStr"/>
+      <c r="H114" s="20" t="inlineStr"/>
+      <c r="I114" s="20" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-      <c r="J110" s="20" t="inlineStr"/>
-      <c r="K110" s="21" t="inlineStr">
+      <c r="J114" s="20" t="inlineStr"/>
+      <c r="K114" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L110" s="20" t="inlineStr"/>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="8" t="inlineStr">
+      <c r="L114" s="20" t="inlineStr"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B112" s="20" t="inlineStr"/>
-      <c r="C112" s="20" t="inlineStr">
+      <c r="B116" s="20" t="inlineStr"/>
+      <c r="C116" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D112" s="20" t="inlineStr">
+      <c r="D116" s="20" t="inlineStr">
         <is>
           <t>Bean Salad (Fri Lunch)</t>
         </is>
       </c>
-      <c r="E112" s="20" t="inlineStr"/>
-      <c r="F112" s="20" t="inlineStr"/>
-      <c r="G112" s="20" t="inlineStr"/>
-      <c r="H112" s="20" t="inlineStr"/>
-      <c r="I112" s="20" t="inlineStr">
+      <c r="E116" s="20" t="inlineStr"/>
+      <c r="F116" s="20" t="inlineStr"/>
+      <c r="G116" s="20" t="inlineStr"/>
+      <c r="H116" s="20" t="inlineStr"/>
+      <c r="I116" s="20" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="J112" s="20" t="inlineStr"/>
-      <c r="K112" s="21" t="inlineStr">
+      <c r="J116" s="20" t="inlineStr"/>
+      <c r="K116" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L112" s="20" t="inlineStr"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="11" t="inlineStr">
+      <c r="L116" s="20" t="inlineStr"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="inlineStr"/>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>120 lbs</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr"/>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>Stove top</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>180 min</t>
-        </is>
-      </c>
-      <c r="K114" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L114" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="14" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B116" s="14" t="inlineStr"/>
-      <c r="C116" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D116" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t>60 lbs</t>
-        </is>
-      </c>
-      <c r="F116" s="14" t="inlineStr">
-        <is>
-          <t>10 oz</t>
-        </is>
-      </c>
-      <c r="G116" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H116" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels + Vegan</t>
-        </is>
-      </c>
-      <c r="I116" s="14" t="inlineStr"/>
-      <c r="J116" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K116" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L116" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr"/>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>Pineapple Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Oven rice</t>
-        </is>
-      </c>
-      <c r="J117" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K117" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L117" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -4975,1194 +5022,1579 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
+          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>120 lbs</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr"/>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>Stove top</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>180 min</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr"/>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Pineapple Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven rice</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K120" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L120" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr"/>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
           <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="E118" s="9" t="inlineStr">
+      <c r="E121" s="9" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="F118" s="9" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G118" s="9" t="inlineStr">
+      <c r="G121" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H118" s="9" t="inlineStr">
+      <c r="H121" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I118" s="9" t="inlineStr">
+      <c r="I121" s="9" t="inlineStr">
         <is>
           <t>Frozen; steam at Bloor</t>
         </is>
       </c>
-      <c r="J118" s="9" t="inlineStr">
+      <c r="J121" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K118" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L118" s="9" t="inlineStr">
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="15" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr"/>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Pork Adobo (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t>10 oz</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr"/>
+      <c r="J122" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L122" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr"/>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Halal Chicken Adobo (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr"/>
+      <c r="J123" s="14" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L123" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr"/>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>Roast Adobo Tofu (Fri Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>12 pcs</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr"/>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM cook time | Same-day roast at Bloor</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="16" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B120" s="16" t="inlineStr"/>
-      <c r="C120" s="16" t="inlineStr">
+      <c r="B126" s="16" t="inlineStr"/>
+      <c r="C126" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D120" s="16" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="E120" s="16" t="inlineStr">
+      <c r="E126" s="16" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="F120" s="16" t="inlineStr"/>
-      <c r="G120" s="16" t="inlineStr">
+      <c r="F126" s="16" t="inlineStr"/>
+      <c r="G126" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H120" s="16" t="inlineStr"/>
-      <c r="I120" s="16" t="inlineStr">
+      <c r="H126" s="16" t="inlineStr"/>
+      <c r="I126" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="J120" s="16" t="inlineStr"/>
-      <c r="K120" s="18" t="inlineStr">
+      <c r="J126" s="16" t="inlineStr"/>
+      <c r="K126" s="18" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="L120" s="16" t="inlineStr">
+      <c r="L126" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="16" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B121" s="16" t="inlineStr"/>
-      <c r="C121" s="16" t="inlineStr">
+      <c r="B127" s="16" t="inlineStr"/>
+      <c r="C127" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
-        </is>
-      </c>
-      <c r="E121" s="16" t="inlineStr">
+      <c r="D127" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pineapple Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="E127" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F127" s="16" t="inlineStr"/>
+      <c r="G127" s="16" t="inlineStr"/>
+      <c r="H127" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J127" s="16" t="inlineStr"/>
+      <c r="K127" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L127" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr"/>
+      <c r="C128" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>HOT Green Beans → Dinner side</t>
+        </is>
+      </c>
+      <c r="E128" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F121" s="16" t="inlineStr"/>
-      <c r="G121" s="16" t="inlineStr"/>
-      <c r="H121" s="16" t="inlineStr"/>
-      <c r="I121" s="16" t="inlineStr">
+      <c r="F128" s="16" t="inlineStr"/>
+      <c r="G128" s="16" t="inlineStr"/>
+      <c r="H128" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J121" s="16" t="inlineStr"/>
-      <c r="K121" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L121" s="16" t="inlineStr">
+      <c r="J128" s="16" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L128" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr"/>
+      <c r="C129" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D129" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pork Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="E129" s="16" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F129" s="16" t="inlineStr"/>
+      <c r="G129" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J129" s="16" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L129" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="16" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B122" s="16" t="inlineStr"/>
-      <c r="C122" s="16" t="inlineStr">
+      <c r="B130" s="16" t="inlineStr"/>
+      <c r="C130" s="16" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
-        </is>
-      </c>
-      <c r="E122" s="16" t="inlineStr">
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F130" s="16" t="inlineStr"/>
+      <c r="G130" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J130" s="16" t="inlineStr"/>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L130" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr"/>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="inlineStr">
+        <is>
+          <t>HOT Adobo Tofu → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E131" s="16" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="F131" s="16" t="inlineStr"/>
+      <c r="G131" s="16" t="inlineStr"/>
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J131" s="16" t="inlineStr"/>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L131" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>◆  SATURDAY  —  May 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr"/>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr"/>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Sunday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr"/>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr"/>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Sunday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="inlineStr"/>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs + 15 lbs</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="inlineStr"/>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H137" s="14" t="inlineStr"/>
+      <c r="I137" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J137" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K137" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L137" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Sunday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr"/>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Griot Marinade</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr"/>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr"/>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>For Griot Pork/Chicken/Tofu</t>
+        </is>
+      </c>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K139" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr"/>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>Cut/Marinate Pork Griot</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>30kg raw</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr"/>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>1 bin/2 hotels</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr"/>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K140" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L140" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr"/>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Griot</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>25kg raw</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr"/>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr"/>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K141" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr"/>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr"/>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K142" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L142" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr"/>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr"/>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K143" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr"/>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>3 bins → 2 hotels</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr"/>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>Stir-fry at LAN; send hot PM</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K145" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="inlineStr"/>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F146" s="14" t="inlineStr"/>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H146" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L146" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr"/>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>Rice (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F122" s="16" t="inlineStr"/>
-      <c r="G122" s="16" t="inlineStr"/>
-      <c r="H122" s="16" t="inlineStr">
+      <c r="F147" s="9" t="inlineStr"/>
+      <c r="G147" s="9" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="inlineStr"/>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="K147" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L147" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr"/>
+      <c r="C148" s="20" t="inlineStr">
+        <is>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E148" s="20" t="inlineStr">
+        <is>
+          <t>2 pcs</t>
+        </is>
+      </c>
+      <c r="F148" s="20" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="G148" s="20" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H148" s="20" t="inlineStr">
+        <is>
+          <t>4" hotel</t>
+        </is>
+      </c>
+      <c r="I148" s="20" t="inlineStr">
+        <is>
+          <t>For bland/no-tomato/no-greens</t>
+        </is>
+      </c>
+      <c r="J148" s="20" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K148" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L148" s="20" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr"/>
+      <c r="C150" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F150" s="16" t="inlineStr"/>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr"/>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="J150" s="16" t="inlineStr"/>
+      <c r="K150" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L150" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr"/>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H151" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J151" s="16" t="inlineStr"/>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L151" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr"/>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F152" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H152" s="16" t="inlineStr">
+        <is>
+          <t>1 × 4" hotel</t>
+        </is>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J152" s="16" t="inlineStr"/>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L152" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr"/>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr"/>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J153" s="16" t="inlineStr"/>
+      <c r="K153" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L153" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr"/>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J122" s="16" t="inlineStr"/>
-      <c r="K122" s="17" t="inlineStr">
+      <c r="F154" s="16" t="inlineStr"/>
+      <c r="G154" s="16" t="inlineStr"/>
+      <c r="H154" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J154" s="16" t="inlineStr"/>
+      <c r="K154" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L154" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr"/>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr"/>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="J155" s="16" t="inlineStr"/>
+      <c r="K155" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L122" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B123" s="16" t="inlineStr"/>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D123" s="16" t="inlineStr">
-        <is>
-          <t>HOT Green Beans → Dinner side</t>
-        </is>
-      </c>
-      <c r="E123" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F123" s="16" t="inlineStr"/>
-      <c r="G123" s="16" t="inlineStr"/>
-      <c r="H123" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J123" s="16" t="inlineStr"/>
-      <c r="K123" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L123" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>◆  SATURDAY  —  May 23</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr"/>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr"/>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J126" s="6" t="inlineStr"/>
-      <c r="K126" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L126" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Sunday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr"/>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J127" s="6" t="inlineStr"/>
-      <c r="K127" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L127" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Sunday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="14" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B129" s="14" t="inlineStr"/>
-      <c r="C129" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D129" s="14" t="inlineStr">
-        <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="E129" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs + 15 lbs</t>
-        </is>
-      </c>
-      <c r="F129" s="14" t="inlineStr"/>
-      <c r="G129" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H129" s="14" t="inlineStr"/>
-      <c r="I129" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J129" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K129" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L129" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Sunday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B131" s="12" t="inlineStr"/>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D131" s="12" t="inlineStr">
-        <is>
-          <t>Griot Marinade</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F131" s="12" t="inlineStr"/>
-      <c r="G131" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="inlineStr"/>
-      <c r="I131" s="12" t="inlineStr">
-        <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
-        </is>
-      </c>
-      <c r="J131" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K131" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L131" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B132" s="12" t="inlineStr"/>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D132" s="12" t="inlineStr">
-        <is>
-          <t>Cut/Marinate Pork Griot</t>
-        </is>
-      </c>
-      <c r="E132" s="12" t="inlineStr">
-        <is>
-          <t>30kg raw</t>
-        </is>
-      </c>
-      <c r="F132" s="12" t="inlineStr"/>
-      <c r="G132" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H132" s="12" t="inlineStr">
-        <is>
-          <t>1 bin/2 hotels</t>
-        </is>
-      </c>
-      <c r="I132" s="12" t="inlineStr"/>
-      <c r="J132" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K132" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L132" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B133" s="12" t="inlineStr"/>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D133" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Griot</t>
-        </is>
-      </c>
-      <c r="E133" s="12" t="inlineStr">
-        <is>
-          <t>25kg raw</t>
-        </is>
-      </c>
-      <c r="F133" s="12" t="inlineStr"/>
-      <c r="G133" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H133" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I133" s="12" t="inlineStr"/>
-      <c r="J133" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K133" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B134" s="12" t="inlineStr"/>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D134" s="12" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="E134" s="12" t="inlineStr">
-        <is>
-          <t>3 bins + 1 bag</t>
-        </is>
-      </c>
-      <c r="F134" s="12" t="inlineStr"/>
-      <c r="G134" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="H134" s="12" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
-      <c r="I134" s="12" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
-        </is>
-      </c>
-      <c r="J134" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K134" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L134" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B135" s="12" t="inlineStr"/>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D135" s="12" t="inlineStr">
-        <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="inlineStr"/>
-      <c r="G135" s="12" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H135" s="12" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I135" s="12" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
-      <c r="J135" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K135" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L135" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="inlineStr"/>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>3 bins → 2 hotels</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr"/>
-      <c r="G137" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>Stir-fry at LAN; send hot PM</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K137" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L137" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="14" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B138" s="14" t="inlineStr"/>
-      <c r="C138" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D138" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E138" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F138" s="14" t="inlineStr"/>
-      <c r="G138" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H138" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I138" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J138" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K138" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L138" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="inlineStr"/>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>Rice (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E139" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F139" s="9" t="inlineStr"/>
-      <c r="G139" s="9" t="inlineStr"/>
-      <c r="H139" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I139" s="9" t="inlineStr"/>
-      <c r="J139" s="9" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="K139" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L139" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B140" s="20" t="inlineStr"/>
-      <c r="C140" s="20" t="inlineStr">
-        <is>
-          <t>ALT</t>
-        </is>
-      </c>
-      <c r="D140" s="20" t="inlineStr">
-        <is>
-          <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E140" s="20" t="inlineStr">
-        <is>
-          <t>2 pcs</t>
-        </is>
-      </c>
-      <c r="F140" s="20" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="G140" s="20" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H140" s="20" t="inlineStr">
-        <is>
-          <t>4" hotel</t>
-        </is>
-      </c>
-      <c r="I140" s="20" t="inlineStr">
-        <is>
-          <t>For bland/no-tomato/no-greens</t>
-        </is>
-      </c>
-      <c r="J140" s="20" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K140" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L140" s="20" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B142" s="16" t="inlineStr"/>
-      <c r="C142" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D142" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E142" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F142" s="16" t="inlineStr"/>
-      <c r="G142" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H142" s="16" t="inlineStr"/>
-      <c r="I142" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J142" s="16" t="inlineStr"/>
-      <c r="K142" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L142" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B143" s="16" t="inlineStr"/>
-      <c r="C143" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D143" s="16" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E143" s="16" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F143" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G143" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H143" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J143" s="16" t="inlineStr"/>
-      <c r="K143" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L143" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="inlineStr"/>
-      <c r="C144" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D144" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E144" s="16" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F144" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G144" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H144" s="16" t="inlineStr">
-        <is>
-          <t>1 × 4" hotel</t>
-        </is>
-      </c>
-      <c r="I144" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J144" s="16" t="inlineStr"/>
-      <c r="K144" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L144" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B145" s="16" t="inlineStr"/>
-      <c r="C145" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D145" s="16" t="inlineStr">
-        <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
-        </is>
-      </c>
-      <c r="E145" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F145" s="16" t="inlineStr"/>
-      <c r="G145" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H145" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I145" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J145" s="16" t="inlineStr"/>
-      <c r="K145" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L145" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B146" s="16" t="inlineStr"/>
-      <c r="C146" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D146" s="16" t="inlineStr">
-        <is>
-          <t>HOT Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="E146" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F146" s="16" t="inlineStr"/>
-      <c r="G146" s="16" t="inlineStr"/>
-      <c r="H146" s="16" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I146" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J146" s="16" t="inlineStr"/>
-      <c r="K146" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L146" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B147" s="16" t="inlineStr"/>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D147" s="16" t="inlineStr">
-        <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
-        </is>
-      </c>
-      <c r="E147" s="16" t="inlineStr">
-        <is>
-          <t>3 bins + 1 bag</t>
-        </is>
-      </c>
-      <c r="F147" s="16" t="inlineStr"/>
-      <c r="G147" s="16" t="inlineStr">
-        <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="H147" s="16" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
-      <c r="I147" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex fridge</t>
-        </is>
-      </c>
-      <c r="J147" s="16" t="inlineStr"/>
-      <c r="K147" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L147" s="16" t="inlineStr">
+      <c r="L155" s="16" t="inlineStr">
         <is>
           <t>Produced: LAN day-before</t>
         </is>
@@ -6172,48 +6604,48 @@
   <mergeCells count="44">
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A90:L90"/>
-    <mergeCell ref="A108:L108"/>
-    <mergeCell ref="A128:L128"/>
-    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A99:L99"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A133:L133"/>
+    <mergeCell ref="A74:L74"/>
+    <mergeCell ref="A149:L149"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="A136:L136"/>
-    <mergeCell ref="A101:L101"/>
     <mergeCell ref="A113:L113"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A86:L86"/>
     <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A71:L71"/>
+    <mergeCell ref="A85:L85"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A141:L141"/>
+    <mergeCell ref="A32:L32"/>
     <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A97:L97"/>
-    <mergeCell ref="A109:L109"/>
+    <mergeCell ref="A144:L144"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A96:L96"/>
     <mergeCell ref="A125:L125"/>
-    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A72:L72"/>
+    <mergeCell ref="A112:L112"/>
     <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A63:L63"/>
+    <mergeCell ref="A68:L68"/>
     <mergeCell ref="A115:L115"/>
+    <mergeCell ref="A117:L117"/>
     <mergeCell ref="A93:L93"/>
-    <mergeCell ref="A111:L111"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A130:L130"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A67:L67"/>
+    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A92:L92"/>
     <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A64:L64"/>
     <mergeCell ref="A82:L82"/>
-    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="A138:L138"/>
+    <mergeCell ref="A107:L107"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A103:L103"/>
+    <mergeCell ref="A132:L132"/>
     <mergeCell ref="A119:L119"/>
-    <mergeCell ref="A79:L79"/>
-    <mergeCell ref="A124:L124"/>
-    <mergeCell ref="A69:L69"/>
-    <mergeCell ref="A87:L87"/>
-    <mergeCell ref="A65:L65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8491,7 +8923,7 @@
       </c>
       <c r="L59" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
+          <t>Produced: Wk. 1 Tuesday Production</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8981,7 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
+          <t>Produced: Wk. 1 Tuesday Production</t>
         </is>
       </c>
     </row>
@@ -8760,7 +9192,7 @@
       </c>
       <c r="L65" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
+          <t>Produced: Wk. 1 Tuesday Production</t>
         </is>
       </c>
     </row>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -3686,64 +3686,64 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr">
         <is>
           <t>165 pcs</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="F82" s="9" t="inlineStr"/>
+      <c r="G82" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="H82" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr">
         <is>
           <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>90 min</t>
         </is>
       </c>
-      <c r="K81" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L81" s="9" t="inlineStr">
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
@@ -6622,6 +6622,7 @@
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A144:L144"/>
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A81:L81"/>
     <mergeCell ref="A96:L96"/>
     <mergeCell ref="A125:L125"/>
     <mergeCell ref="A72:L72"/>
@@ -6638,7 +6639,6 @@
     <mergeCell ref="A48:L48"/>
     <mergeCell ref="A92:L92"/>
     <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A82:L82"/>
     <mergeCell ref="A138:L138"/>
     <mergeCell ref="A107:L107"/>
     <mergeCell ref="A1:L1"/>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Monday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Lunch</t>
+          <t>Produced: Wk. 4 Wednesday Production (cold chain via Rex; prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="L73" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Wednesday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L157"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9858,64 +9858,64 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="13" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr"/>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Refried Beans (→ Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr"/>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | ⚠ CONFIRM cook time</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>Yetisse Fish (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>150 pcs</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>hotels</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr"/>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Bake; serve HOT</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K84" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L84" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Wednesday Dinner</t>
         </is>
       </c>
     </row>
@@ -9933,12 +9933,12 @@
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Spiced Tofu (Wed Dinner — Veg)</t>
+          <t>Yetisse Fish (Wed Dinner)</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>50 pcs</t>
+          <t>150 pcs</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
@@ -9948,13 +9948,13 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>hotels</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr"/>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>Oven</t>
+          <t>Bake; serve HOT</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
@@ -9987,150 +9987,158 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Coconut Rice &amp; Peas (Wed Dinner)</t>
+          <t>Spiced Tofu (Wed Dinner — Veg)</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>5 hotels</t>
+          <t>50 pcs</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>8 oz</t>
+          <t>1 pc</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr"/>
       <c r="I86" s="9" t="inlineStr">
         <is>
+          <t>Oven</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr"/>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Coconut Rice &amp; Peas (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
           <t>Oven rice</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr">
+      <c r="J87" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K86" s="14" t="inlineStr">
+      <c r="K87" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L86" s="9" t="inlineStr">
+      <c r="L87" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="14" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B87" s="14" t="inlineStr"/>
-      <c r="C87" s="14" t="inlineStr">
+      <c r="B88" s="14" t="inlineStr"/>
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
+      <c r="D88" s="14" t="inlineStr">
         <is>
           <t>Reheat Eggplant/Cassava Stew (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E87" s="14" t="inlineStr">
+      <c r="E88" s="14" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F87" s="14" t="inlineStr"/>
-      <c r="G87" s="14" t="inlineStr">
+      <c r="F88" s="14" t="inlineStr"/>
+      <c r="G88" s="14" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H87" s="14" t="inlineStr">
+      <c r="H88" s="14" t="inlineStr">
         <is>
           <t>2u</t>
         </is>
       </c>
-      <c r="I87" s="14" t="inlineStr">
+      <c r="I88" s="14" t="inlineStr">
         <is>
           <t>Reheat</t>
         </is>
       </c>
-      <c r="J87" s="14" t="inlineStr">
+      <c r="J88" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K87" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L87" s="14" t="inlineStr">
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L88" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Production</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="15" t="inlineStr">
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 12 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B89" s="16" t="inlineStr"/>
-      <c r="C89" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E89" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F89" s="16" t="inlineStr"/>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H89" s="16" t="inlineStr"/>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J89" s="16" t="inlineStr"/>
-      <c r="K89" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L89" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -10148,43 +10156,35 @@
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>HOT Yetisse Fish → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>150 pcs</t>
-        </is>
-      </c>
-      <c r="F90" s="16" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr"/>
       <c r="G90" s="16" t="inlineStr">
         <is>
-          <t>hotels</t>
-        </is>
-      </c>
-      <c r="H90" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="inlineStr"/>
       <c r="I90" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J90" s="16" t="inlineStr"/>
-      <c r="K90" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K90" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L90" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Tuesday Production (trayed prev day, LAN cook)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -10202,12 +10202,12 @@
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>HOT Spiced Tofu → Dinner (Veg)</t>
+          <t>HOT Yetisse Fish → Dinner</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>50 pcs</t>
+          <t>150 pcs</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="G91" s="16" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>hotels</t>
         </is>
       </c>
       <c r="H91" s="16" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="L91" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Tuesday Production (LAN cook)</t>
+          <t>Produced: Wk. 2 Tuesday Production (trayed prev day, LAN cook)</t>
         </is>
       </c>
     </row>
@@ -10256,21 +10256,29 @@
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>HOT Coconut Rice &amp; Peas → Dinner</t>
+          <t>HOT Spiced Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F92" s="16" t="inlineStr"/>
+          <t>50 pcs</t>
+        </is>
+      </c>
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
       <c r="G92" s="16" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H92" s="16" t="inlineStr"/>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H92" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
@@ -10284,7 +10292,7 @@
       </c>
       <c r="L92" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Wednesday Dinner (same day)</t>
+          <t>Produced: Wk. 2 Tuesday Production (LAN cook)</t>
         </is>
       </c>
     </row>
@@ -10302,12 +10310,12 @@
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>HOT Coconut Rice &amp; Peas → Dinner</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F93" s="16" t="inlineStr"/>
@@ -10319,18 +10327,18 @@
       <c r="H93" s="16" t="inlineStr"/>
       <c r="I93" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J93" s="16" t="inlineStr"/>
-      <c r="K93" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K93" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L93" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Thursday Production</t>
+          <t>Produced: Wk. 2 Wednesday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -10348,99 +10356,91 @@
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>Cold Chickpea Salad → Thu Lunch</t>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
       <c r="E94" s="16" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F94" s="16" t="inlineStr"/>
-      <c r="G94" s="16" t="inlineStr"/>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="H94" s="16" t="inlineStr"/>
       <c r="I94" s="16" t="inlineStr">
         <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J94" s="16" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L94" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Thursday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="inlineStr"/>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Salad → Thu Lunch</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F95" s="16" t="inlineStr"/>
+      <c r="G95" s="16" t="inlineStr"/>
+      <c r="H95" s="16" t="inlineStr"/>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J94" s="16" t="inlineStr"/>
-      <c r="K94" s="17" t="inlineStr">
+      <c r="J95" s="16" t="inlineStr"/>
+      <c r="K95" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L94" s="16" t="inlineStr">
+      <c r="L95" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk.2 Tue Production (LAN)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>◆  THURSDAY  —  May 28</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 4 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr"/>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>HOT Halal Beef Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>160 pcs</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J97" s="6" t="inlineStr"/>
-      <c r="K97" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L97" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -10458,12 +10458,12 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+          <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>20 pcs</t>
+          <t>160 pcs</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>0.5 hotel</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
@@ -10498,68 +10498,64 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr"/>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Thursday Lunch (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr"/>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>Halal Beef Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>150 pcs</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H100" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>From freezer; oven 30 min day-of</t>
-        </is>
-      </c>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K100" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L100" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk.2 Thursday Lunch</t>
         </is>
       </c>
     </row>
@@ -10577,100 +10573,104 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
+          <t>Halal Beef Burgers (Thu Lunch)</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>150 pcs</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>From freezer; oven 30 min day-of</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk.2 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
           <t>Black Bean Patties (Thu Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E101" s="9" t="inlineStr">
+      <c r="E102" s="9" t="inlineStr">
         <is>
           <t>20 pcs</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr">
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H101" s="9" t="inlineStr">
+      <c r="H102" s="9" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="9" t="inlineStr">
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K101" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L101" s="9" t="inlineStr">
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Thursday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr"/>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>Pork Griot (→ Wk 3Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>30 kg raw</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr"/>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel / 40 lbs</t>
-        </is>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>Combi</t>
-        </is>
-      </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K103" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L103" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -10688,12 +10688,12 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Chicken Griot — Halal option (→ Wk 3Thu Dinner)</t>
+          <t>Pork Griot (→ Wk 3Thu Dinner)</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>25 kg raw</t>
+          <t>30 kg raw</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -10704,81 +10704,81 @@
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
+          <t>1 hotel / 40 lbs</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>Combi</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr"/>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Chicken Griot — Halal option (→ Wk 3Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>25 kg raw</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
           <t>1 hotel / 32 lbs</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
+      <c r="I105" s="9" t="inlineStr">
         <is>
           <t>Oven</t>
         </is>
       </c>
-      <c r="J104" s="9" t="inlineStr">
+      <c r="J105" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K104" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L104" s="9" t="inlineStr">
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L105" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="12" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="inlineStr"/>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D105" s="12" t="inlineStr">
-        <is>
-          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F105" s="12" t="inlineStr"/>
-      <c r="G105" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H105" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I105" s="12" t="inlineStr">
-        <is>
-          <t>Mix; chill; send cold day-of</t>
-        </is>
-      </c>
-      <c r="J105" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K105" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L105" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk.2 Saturday Lunch</t>
         </is>
       </c>
     </row>
@@ -10796,12 +10796,12 @@
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
+          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>1 unit</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr"/>
@@ -10812,92 +10812,88 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
+        <is>
+          <t>Mix; chill; send cold day-of</t>
+        </is>
+      </c>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K106" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L106" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk.2 Saturday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr"/>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
           <t>1 unit</t>
         </is>
       </c>
-      <c r="I106" s="12" t="inlineStr">
+      <c r="F107" s="12" t="inlineStr"/>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>1 unit</t>
+        </is>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
         <is>
           <t>Dress; chill; send cold</t>
         </is>
       </c>
-      <c r="J106" s="12" t="inlineStr">
+      <c r="J107" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K106" s="14" t="inlineStr">
+      <c r="K107" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L106" s="12" t="inlineStr">
+      <c r="L107" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk.2 Saturday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="13" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr"/>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>Beef Sausages (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>100 pcs</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H108" s="9" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>Cook sausages for dinner service</t>
-        </is>
-      </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K108" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L108" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -10915,12 +10911,12 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Halal Sausages (Thu Dinner)</t>
+          <t>Beef Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>60 pcs</t>
+          <t>100 pcs</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
@@ -10935,7 +10931,7 @@
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="I109" s="9" t="inlineStr">
@@ -10973,12 +10969,12 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Vegan Sausages (Thu Dinner)</t>
+          <t>Halal Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>15 pcs</t>
+          <t>60 pcs</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
@@ -10993,7 +10989,7 @@
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>0.5 hotel</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="I110" s="9" t="inlineStr">
@@ -11031,162 +11027,166 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
+          <t>Vegan Sausages (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>15 pcs</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>Cook sausages for dinner service</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K111" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr"/>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
           <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E112" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F112" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G111" s="9" t="inlineStr">
+      <c r="G112" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H111" s="9" t="inlineStr">
+      <c r="H112" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I111" s="9" t="inlineStr">
+      <c r="I112" s="9" t="inlineStr">
         <is>
           <t>Combi</t>
         </is>
       </c>
-      <c r="J111" s="9" t="inlineStr">
+      <c r="J112" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K111" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L111" s="9" t="inlineStr">
+      <c r="K112" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Thursday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="14" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="14" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B112" s="14" t="inlineStr"/>
-      <c r="C112" s="14" t="inlineStr">
+      <c r="B113" s="14" t="inlineStr"/>
+      <c r="C113" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D112" s="14" t="inlineStr">
+      <c r="D113" s="14" t="inlineStr">
         <is>
           <t>Reheat Gravy (Thu Dinner + hold portion for Sat Dinner Meatloaf)</t>
         </is>
       </c>
-      <c r="E112" s="14" t="inlineStr">
+      <c r="E113" s="14" t="inlineStr">
         <is>
           <t>2 batches</t>
         </is>
       </c>
-      <c r="F112" s="14" t="inlineStr"/>
-      <c r="G112" s="14" t="inlineStr">
+      <c r="F113" s="14" t="inlineStr"/>
+      <c r="G113" s="14" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H112" s="14" t="inlineStr">
+      <c r="H113" s="14" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I112" s="14" t="inlineStr">
+      <c r="I113" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged; portion ½ for Thu PM, hold ½ at Bloor for Sat</t>
         </is>
       </c>
-      <c r="J112" s="14" t="inlineStr">
+      <c r="J113" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K112" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L112" s="14" t="inlineStr">
+      <c r="K113" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L113" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="15" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 19 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="inlineStr"/>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>250 pcs</t>
-        </is>
-      </c>
-      <c r="F114" s="16" t="inlineStr">
-        <is>
-          <t>2 pcs</t>
-        </is>
-      </c>
-      <c r="G114" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H114" s="16" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J114" s="16" t="inlineStr"/>
-      <c r="K114" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L114" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -11204,17 +11204,17 @@
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>HOT Mashed Potato → Dinner</t>
+          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
         </is>
       </c>
       <c r="E115" s="16" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>250 pcs</t>
         </is>
       </c>
       <c r="F115" s="16" t="inlineStr">
         <is>
-          <t>8 oz</t>
+          <t>2 pcs</t>
         </is>
       </c>
       <c r="G115" s="16" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H115" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>6 hotels</t>
         </is>
       </c>
       <c r="I115" s="16" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="L115" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Production (via LAN)</t>
+          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -11258,17 +11258,17 @@
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
+          <t>HOT Mashed Potato → Dinner</t>
         </is>
       </c>
       <c r="E116" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F116" s="16" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>8 oz</t>
         </is>
       </c>
       <c r="G116" s="16" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="L116" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
+          <t>Produced: Wk. 1 Saturday Production (via LAN)</t>
         </is>
       </c>
     </row>
@@ -11312,15 +11312,19 @@
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>HOT Gravy → Dinner</t>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
       <c r="E117" s="16" t="inlineStr">
         <is>
-          <t>½ batch</t>
-        </is>
-      </c>
-      <c r="F117" s="16" t="inlineStr"/>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
       <c r="G117" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
@@ -11328,7 +11332,7 @@
       </c>
       <c r="H117" s="16" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="I117" s="16" t="inlineStr">
@@ -11362,39 +11366,39 @@
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>HOT Gravy → Dinner</t>
         </is>
       </c>
       <c r="E118" s="16" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>½ batch</t>
         </is>
       </c>
       <c r="F118" s="16" t="inlineStr"/>
       <c r="G118" s="16" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="H118" s="16" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J118" s="16" t="inlineStr"/>
-      <c r="K118" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L118" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk.2 Wed Production (LAN)</t>
+          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11416,7 @@
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
         </is>
       </c>
       <c r="E119" s="16" t="inlineStr">
@@ -11448,185 +11452,177 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr"/>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>Cold Slaw → Fri Lunch side</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F120" s="16" t="inlineStr"/>
+      <c r="G120" s="16" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H120" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J120" s="16" t="inlineStr"/>
+      <c r="K120" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L120" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk.2 Wed Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>◆  FRIDAY  —  May 29</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 0.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr"/>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr"/>
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>HOT Crispy Falafel → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr"/>
-      <c r="G122" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H122" s="6" t="inlineStr">
+      <c r="H123" s="6" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="I122" s="6" t="inlineStr">
+      <c r="I123" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J122" s="6" t="inlineStr"/>
-      <c r="K122" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L122" s="6" t="inlineStr">
+      <c r="J123" s="6" t="inlineStr"/>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk.2 Fri Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="14" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B124" s="14" t="inlineStr"/>
-      <c r="C124" s="14" t="inlineStr">
+      <c r="B125" s="14" t="inlineStr"/>
+      <c r="C125" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D124" s="14" t="inlineStr">
+      <c r="D125" s="14" t="inlineStr">
         <is>
           <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E124" s="14" t="inlineStr">
+      <c r="E125" s="14" t="inlineStr">
         <is>
           <t>30 pcs</t>
         </is>
       </c>
-      <c r="F124" s="14" t="inlineStr"/>
-      <c r="G124" s="14" t="inlineStr"/>
-      <c r="H124" s="14" t="inlineStr"/>
-      <c r="I124" s="14" t="inlineStr">
+      <c r="F125" s="14" t="inlineStr"/>
+      <c r="G125" s="14" t="inlineStr"/>
+      <c r="H125" s="14" t="inlineStr"/>
+      <c r="I125" s="14" t="inlineStr">
         <is>
           <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
-      <c r="J124" s="14" t="inlineStr">
+      <c r="J125" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K124" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L124" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Friday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L125" s="14" t="inlineStr">
+        <is>
+          <t>Serves: same day (purchased frozen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="inlineStr"/>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H126" s="9" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
-        </is>
-      </c>
-      <c r="J126" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K126" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L126" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Saturday Lunch</t>
         </is>
       </c>
     </row>
@@ -11644,101 +11640,105 @@
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
+          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Saturday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr"/>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
           <t>Vegan CONC Salad Mix (→ Wk3 Sat Lunch)</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>12 lbs</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr">
+      <c r="F128" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G127" s="9" t="inlineStr">
+      <c r="G128" s="9" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H127" s="9" t="inlineStr">
+      <c r="H128" s="9" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="I127" s="9" t="inlineStr">
+      <c r="I128" s="9" t="inlineStr">
         <is>
           <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
         </is>
       </c>
-      <c r="J127" s="9" t="inlineStr">
+      <c r="J128" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K127" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L127" s="9" t="inlineStr">
+      <c r="K128" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L128" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="12" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="inlineStr"/>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D128" s="12" t="inlineStr">
-        <is>
-          <t>Prep Butternut Squash (→ Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="F128" s="12" t="inlineStr"/>
-      <c r="G128" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="I128" s="12" t="inlineStr">
-        <is>
-          <t>Peel/dice at LAN; chill overnight</t>
-        </is>
-      </c>
-      <c r="J128" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K128" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L128" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Saturday Dinner</t>
         </is>
       </c>
     </row>
@@ -11756,34 +11756,38 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
+          <t>Prep Butternut Squash (→ Sat Dinner side)</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>7 loaves</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr"/>
-      <c r="G129" s="12" t="inlineStr"/>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>7 trays</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>Peel/dice at LAN; chill overnight</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>75 min</t>
-        </is>
-      </c>
-      <c r="K129" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K129" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L129" s="12" t="inlineStr">
@@ -11806,211 +11810,211 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
+          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>1 loaves</t>
+          <t>7 loaves</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr"/>
       <c r="G130" s="12" t="inlineStr"/>
       <c r="H130" s="12" t="inlineStr">
         <is>
+          <t>7 trays</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>75 min</t>
+        </is>
+      </c>
+      <c r="K130" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L130" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr"/>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>1 loaves</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr"/>
+      <c r="G131" s="12" t="inlineStr"/>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
           <t>1 tray</t>
         </is>
       </c>
-      <c r="I130" s="12" t="inlineStr">
+      <c r="I131" s="12" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J130" s="12" t="inlineStr">
+      <c r="J131" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K130" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L130" s="12" t="inlineStr">
+      <c r="K131" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="13" t="inlineStr">
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="14" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="14" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B132" s="14" t="inlineStr"/>
-      <c r="C132" s="14" t="inlineStr">
+      <c r="B133" s="14" t="inlineStr"/>
+      <c r="C133" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D132" s="14" t="inlineStr">
+      <c r="D133" s="14" t="inlineStr">
         <is>
           <t>Reheat Refried Beans (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="E132" s="14" t="inlineStr">
+      <c r="E133" s="14" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F132" s="14" t="inlineStr"/>
-      <c r="G132" s="14" t="inlineStr">
+      <c r="F133" s="14" t="inlineStr"/>
+      <c r="G133" s="14" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H132" s="14" t="inlineStr">
+      <c r="H133" s="14" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I132" s="14" t="inlineStr">
+      <c r="I133" s="14" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE — Reheat bagged</t>
         </is>
       </c>
-      <c r="J132" s="14" t="inlineStr">
+      <c r="J133" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K132" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L132" s="14" t="inlineStr">
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L133" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr"/>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>Arroz con Pollo</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr"/>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>300 min</t>
+        </is>
+      </c>
+      <c r="K134" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L134" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B133" s="9" t="inlineStr"/>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>Arroz con Pollo</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H133" s="9" t="inlineStr"/>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J133" s="9" t="inlineStr">
-        <is>
-          <t>300 min</t>
-        </is>
-      </c>
-      <c r="K133" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L133" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="15" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 6.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B135" s="16" t="inlineStr"/>
-      <c r="C135" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D135" s="16" t="inlineStr">
-        <is>
-          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
-        </is>
-      </c>
-      <c r="E135" s="16" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="F135" s="16" t="inlineStr"/>
-      <c r="G135" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H135" s="16" t="inlineStr">
-        <is>
-          <t>2½ hotels</t>
-        </is>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J135" s="16" t="inlineStr"/>
-      <c r="K135" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L135" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -12028,23 +12032,23 @@
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>HOT Refried Beans → Dinner side</t>
+          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
         </is>
       </c>
       <c r="E136" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="F136" s="16" t="inlineStr"/>
       <c r="G136" s="16" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="H136" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>2½ hotels</t>
         </is>
       </c>
       <c r="I136" s="16" t="inlineStr">
@@ -12060,7 +12064,7 @@
       </c>
       <c r="L136" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Wednesday Production</t>
+          <t>Produced: Wk. 2 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -12078,173 +12082,177 @@
       </c>
       <c r="D137" s="16" t="inlineStr">
         <is>
+          <t>HOT Refried Beans → Dinner side</t>
+        </is>
+      </c>
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F137" s="16" t="inlineStr"/>
+      <c r="G137" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H137" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J137" s="16" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L137" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr"/>
+      <c r="C138" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
           <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
         </is>
       </c>
-      <c r="E137" s="16" t="inlineStr">
+      <c r="E138" s="16" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F137" s="16" t="inlineStr"/>
-      <c r="G137" s="16" t="inlineStr"/>
-      <c r="H137" s="16" t="inlineStr"/>
-      <c r="I137" s="16" t="inlineStr">
+      <c r="F138" s="16" t="inlineStr"/>
+      <c r="G138" s="16" t="inlineStr"/>
+      <c r="H138" s="16" t="inlineStr"/>
+      <c r="I138" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J137" s="16" t="inlineStr"/>
-      <c r="K137" s="17" t="inlineStr">
+      <c r="J138" s="16" t="inlineStr"/>
+      <c r="K138" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L137" s="16" t="inlineStr">
+      <c r="L138" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk.2 Thu Production (LAN)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>◆  SATURDAY  —  May 30</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: ~1 items</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="20" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B140" s="20" t="inlineStr"/>
-      <c r="C140" s="20" t="inlineStr">
+      <c r="B141" s="20" t="inlineStr"/>
+      <c r="C141" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D140" s="20" t="inlineStr">
+      <c r="D141" s="20" t="inlineStr">
         <is>
           <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
         </is>
       </c>
-      <c r="E140" s="20" t="inlineStr"/>
-      <c r="F140" s="20" t="inlineStr"/>
-      <c r="G140" s="20" t="inlineStr"/>
-      <c r="H140" s="20" t="inlineStr"/>
-      <c r="I140" s="20" t="inlineStr">
+      <c r="E141" s="20" t="inlineStr"/>
+      <c r="F141" s="20" t="inlineStr"/>
+      <c r="G141" s="20" t="inlineStr"/>
+      <c r="H141" s="20" t="inlineStr"/>
+      <c r="I141" s="20" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-      <c r="J140" s="20" t="inlineStr"/>
-      <c r="K140" s="21" t="inlineStr">
+      <c r="J141" s="20" t="inlineStr"/>
+      <c r="K141" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L140" s="20" t="inlineStr"/>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="L141" s="20" t="inlineStr"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="20" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B142" s="20" t="inlineStr"/>
-      <c r="C142" s="20" t="inlineStr">
+      <c r="B143" s="20" t="inlineStr"/>
+      <c r="C143" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D142" s="20" t="inlineStr">
+      <c r="D143" s="20" t="inlineStr">
         <is>
           <t>Tuna Rex + Chickpea Rex Salad (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E142" s="20" t="inlineStr"/>
-      <c r="F142" s="20" t="inlineStr"/>
-      <c r="G142" s="20" t="inlineStr"/>
-      <c r="H142" s="20" t="inlineStr"/>
-      <c r="I142" s="20" t="inlineStr">
+      <c r="E143" s="20" t="inlineStr"/>
+      <c r="F143" s="20" t="inlineStr"/>
+      <c r="G143" s="20" t="inlineStr"/>
+      <c r="H143" s="20" t="inlineStr"/>
+      <c r="I143" s="20" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="J142" s="20" t="inlineStr"/>
-      <c r="K142" s="21" t="inlineStr">
+      <c r="J143" s="20" t="inlineStr"/>
+      <c r="K143" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L142" s="20" t="inlineStr"/>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="11" t="inlineStr">
+      <c r="L143" s="20" t="inlineStr"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B144" s="12" t="inlineStr"/>
-      <c r="C144" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D144" s="12" t="inlineStr">
-        <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="E144" s="12" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F144" s="12" t="inlineStr"/>
-      <c r="G144" s="12" t="inlineStr"/>
-      <c r="H144" s="12" t="inlineStr"/>
-      <c r="I144" s="12" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
-        </is>
-      </c>
-      <c r="J144" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K144" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L144" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
     </row>
@@ -12262,33 +12270,25 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Tuna Salad Mix (→ Wk3 Mon Lunch)</t>
+          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr"/>
-      <c r="G145" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H145" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
+      <c r="G145" s="12" t="inlineStr"/>
+      <c r="H145" s="12" t="inlineStr"/>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>Mix; chill; send Sun PM</t>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="K145" s="14" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk.3 Monday Lunch</t>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
     </row>
@@ -12316,92 +12316,96 @@
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
+          <t>Tuna Salad Mix (→ Wk3 Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr"/>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H146" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="inlineStr">
+        <is>
+          <t>Mix; chill; send Sun PM</t>
+        </is>
+      </c>
+      <c r="J146" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K146" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L146" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk.3 Monday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr"/>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
           <t>Prep Broccoli Salad (→ Wk3 Sun Lunch)</t>
         </is>
       </c>
-      <c r="E146" s="12" t="inlineStr">
+      <c r="E147" s="12" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F146" s="12" t="inlineStr"/>
-      <c r="G146" s="12" t="inlineStr"/>
-      <c r="H146" s="12" t="inlineStr"/>
-      <c r="I146" s="12" t="inlineStr">
+      <c r="F147" s="12" t="inlineStr"/>
+      <c r="G147" s="12" t="inlineStr"/>
+      <c r="H147" s="12" t="inlineStr"/>
+      <c r="I147" s="12" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
         </is>
       </c>
-      <c r="J146" s="12" t="inlineStr">
+      <c r="J147" s="12" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K146" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L146" s="12" t="inlineStr">
+      <c r="K147" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Sunday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="13" t="inlineStr">
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="inlineStr"/>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr">
-        <is>
-          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>7 trays</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr"/>
-      <c r="G148" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H148" s="9" t="inlineStr"/>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>Bake meatloaf from tray</t>
-        </is>
-      </c>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K148" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L148" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Saturday Dinner</t>
         </is>
       </c>
     </row>
@@ -12419,12 +12423,12 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
+          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>1 tray</t>
+          <t>7 trays</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -12434,7 +12438,11 @@
         </is>
       </c>
       <c r="H149" s="9" t="inlineStr"/>
-      <c r="I149" s="9" t="inlineStr"/>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>Bake meatloaf from tray</t>
+        </is>
+      </c>
       <c r="J149" s="9" t="inlineStr">
         <is>
           <t>90 min</t>
@@ -12465,30 +12473,22 @@
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>Roasted Potatoes (Sat Dinner)</t>
+          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
+          <t>1 tray</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr"/>
       <c r="G150" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr"/>
-      <c r="I150" s="9" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
+      <c r="I150" s="9" t="inlineStr"/>
       <c r="J150" s="9" t="inlineStr">
         <is>
           <t>90 min</t>
@@ -12519,104 +12519,108 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
+          <t>Roasted Potatoes (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr"/>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K151" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L151" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Saturday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr"/>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
           <t>Roasted Butternut Squash (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="E151" s="9" t="inlineStr">
+      <c r="E152" s="9" t="inlineStr">
         <is>
           <t>3 bins → 3 hotels</t>
         </is>
       </c>
-      <c r="F151" s="9" t="inlineStr">
+      <c r="F152" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G151" s="9" t="inlineStr">
+      <c r="G152" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H151" s="9" t="inlineStr">
+      <c r="H152" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I151" s="9" t="inlineStr">
+      <c r="I152" s="9" t="inlineStr">
         <is>
           <t>Roast at LAN day-of</t>
         </is>
       </c>
-      <c r="J151" s="9" t="inlineStr">
+      <c r="J152" s="9" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K151" s="14" t="inlineStr">
+      <c r="K152" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L151" s="9" t="inlineStr">
+      <c r="L152" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="15" t="inlineStr">
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 19 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B153" s="16" t="inlineStr"/>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D153" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
-        </is>
-      </c>
-      <c r="E153" s="16" t="inlineStr">
-        <is>
-          <t>8 trays</t>
-        </is>
-      </c>
-      <c r="F153" s="16" t="inlineStr"/>
-      <c r="G153" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H153" s="16" t="inlineStr">
-        <is>
-          <t>8 hotels</t>
-        </is>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J153" s="16" t="inlineStr"/>
-      <c r="K153" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L153" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Wednesday Production (LAN bake same day)</t>
         </is>
       </c>
     </row>
@@ -12634,19 +12638,15 @@
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
+          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
         </is>
       </c>
       <c r="E154" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F154" s="16" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
+          <t>8 trays</t>
+        </is>
+      </c>
+      <c r="F154" s="16" t="inlineStr"/>
       <c r="G154" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="H154" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="I154" s="16" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="L154" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Saturday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 2 Wednesday Production (LAN bake same day)</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12688,17 @@
       </c>
       <c r="D155" s="16" t="inlineStr">
         <is>
-          <t>HOT Butternut Squash → Dinner side</t>
+          <t>HOT Roasted Potatoes → Dinner</t>
         </is>
       </c>
       <c r="E155" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>6 oz</t>
         </is>
       </c>
       <c r="G155" s="16" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="H155" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="I155" s="16" t="inlineStr">
@@ -12742,15 +12742,19 @@
       </c>
       <c r="D156" s="16" t="inlineStr">
         <is>
-          <t>HOT Gravy → Dinner (Meatloaf)</t>
+          <t>HOT Butternut Squash → Dinner side</t>
         </is>
       </c>
       <c r="E156" s="16" t="inlineStr">
         <is>
-          <t>½ batch</t>
-        </is>
-      </c>
-      <c r="F156" s="16" t="inlineStr"/>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F156" s="16" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
       <c r="G156" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
@@ -12758,23 +12762,23 @@
       </c>
       <c r="H156" s="16" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="I156" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex | Held from Thu batch</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J156" s="16" t="inlineStr"/>
-      <c r="K156" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K156" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L156" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Thursday Dinner (held at Bloor)</t>
+          <t>Produced: Wk. 2 Saturday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
@@ -12792,24 +12796,28 @@
       </c>
       <c r="D157" s="16" t="inlineStr">
         <is>
-          <t>Cold Broccoli Salad → Wk3 Sun Lunch</t>
+          <t>HOT Gravy → Dinner (Meatloaf)</t>
         </is>
       </c>
       <c r="E157" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>½ batch</t>
         </is>
       </c>
       <c r="F157" s="16" t="inlineStr"/>
-      <c r="G157" s="16" t="inlineStr"/>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="H157" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="I157" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex fridge</t>
+          <t>Bloor → Rex | Held from Thu batch</t>
         </is>
       </c>
       <c r="J157" s="16" t="inlineStr"/>
@@ -12819,6 +12827,52 @@
         </is>
       </c>
       <c r="L157" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Thursday Dinner (held at Bloor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr"/>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>Cold Broccoli Salad → Wk3 Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr"/>
+      <c r="G158" s="16" t="inlineStr"/>
+      <c r="H158" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex fridge</t>
+        </is>
+      </c>
+      <c r="J158" s="16" t="inlineStr"/>
+      <c r="K158" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L158" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Saturday Production</t>
         </is>
@@ -12828,47 +12882,47 @@
   <mergeCells count="44">
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A99:L99"/>
+    <mergeCell ref="A108:L108"/>
+    <mergeCell ref="A153:L153"/>
     <mergeCell ref="A75:L75"/>
+    <mergeCell ref="A84:L84"/>
+    <mergeCell ref="A89:L89"/>
     <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A120:L120"/>
     <mergeCell ref="A50:L50"/>
     <mergeCell ref="A12:L12"/>
-    <mergeCell ref="A95:L95"/>
-    <mergeCell ref="A113:L113"/>
+    <mergeCell ref="A139:L139"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A139:L139"/>
     <mergeCell ref="A47:L47"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A141:L141"/>
+    <mergeCell ref="A97:L97"/>
+    <mergeCell ref="A135:L135"/>
+    <mergeCell ref="A126:L126"/>
+    <mergeCell ref="A144:L144"/>
+    <mergeCell ref="A122:L122"/>
     <mergeCell ref="A53:L53"/>
-    <mergeCell ref="A131:L131"/>
+    <mergeCell ref="A140:L140"/>
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A100:L100"/>
     <mergeCell ref="A96:L96"/>
-    <mergeCell ref="A125:L125"/>
     <mergeCell ref="A72:L72"/>
-    <mergeCell ref="A147:L147"/>
-    <mergeCell ref="A134:L134"/>
     <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A152:L152"/>
     <mergeCell ref="A121:L121"/>
     <mergeCell ref="A58:L58"/>
-    <mergeCell ref="A102:L102"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A143:L143"/>
-    <mergeCell ref="A83:L83"/>
+    <mergeCell ref="A114:L114"/>
+    <mergeCell ref="A148:L148"/>
     <mergeCell ref="A48:L48"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A64:L64"/>
-    <mergeCell ref="A138:L138"/>
-    <mergeCell ref="A107:L107"/>
+    <mergeCell ref="A142:L142"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A103:L103"/>
+    <mergeCell ref="A132:L132"/>
     <mergeCell ref="A36:L36"/>
-    <mergeCell ref="A123:L123"/>
-    <mergeCell ref="A88:L88"/>
     <mergeCell ref="A70:L70"/>
+    <mergeCell ref="A124:L124"/>
     <mergeCell ref="A69:L69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13915,7 +13969,7 @@
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Monday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -14640,7 +14694,7 @@
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Tuesday Lunch</t>
+          <t>Produced: Wk. 2 Wednesday Production (cold chain via Rex)</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14744,7 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Tuesday Lunch</t>
+          <t>Produced: Wk. 2 Wednesday Production (cold chain via Rex)</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15822,7 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Wednesday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -17712,7 +17766,7 @@
       </c>
       <c r="L125" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -18098,7 +18152,7 @@
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Saturday Lunch</t>
+          <t>Produced: Wk. 3 Sunday Production</t>
         </is>
       </c>
     </row>
@@ -23871,7 +23925,7 @@
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Friday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -18849,7 +18849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L170"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21914,7 +21914,7 @@
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 8.5 HOTELS (hot)</t>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -22144,153 +22144,149 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr"/>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Shakshuka → Rex fridge (NC Wk1 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr"/>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H82" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J82" s="16" t="inlineStr"/>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L82" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Monday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>◆  WEDNESDAY  —  Jun 10</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: ~1 items</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B84" s="20" t="inlineStr"/>
-      <c r="C84" s="20" t="inlineStr">
+      <c r="B85" s="20" t="inlineStr"/>
+      <c r="C85" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
-      <c r="E84" s="20" t="inlineStr"/>
-      <c r="F84" s="20" t="inlineStr"/>
-      <c r="G84" s="20" t="inlineStr"/>
-      <c r="H84" s="20" t="inlineStr"/>
-      <c r="I84" s="20" t="inlineStr">
+      <c r="E85" s="20" t="inlineStr"/>
+      <c r="F85" s="20" t="inlineStr"/>
+      <c r="G85" s="20" t="inlineStr"/>
+      <c r="H85" s="20" t="inlineStr"/>
+      <c r="I85" s="20" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-      <c r="J84" s="20" t="inlineStr"/>
-      <c r="K84" s="21" t="inlineStr">
+      <c r="J85" s="20" t="inlineStr"/>
+      <c r="K85" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L84" s="20" t="inlineStr"/>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="L85" s="20" t="inlineStr"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B86" s="20" t="inlineStr"/>
-      <c r="C86" s="20" t="inlineStr">
+      <c r="B87" s="20" t="inlineStr"/>
+      <c r="C87" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D86" s="20" t="inlineStr">
+      <c r="D87" s="20" t="inlineStr">
         <is>
           <t>Coronation Chicken Salad (Wed Lunch)</t>
         </is>
       </c>
-      <c r="E86" s="20" t="inlineStr"/>
-      <c r="F86" s="20" t="inlineStr"/>
-      <c r="G86" s="20" t="inlineStr"/>
-      <c r="H86" s="20" t="inlineStr"/>
-      <c r="I86" s="20" t="inlineStr">
+      <c r="E87" s="20" t="inlineStr"/>
+      <c r="F87" s="20" t="inlineStr"/>
+      <c r="G87" s="20" t="inlineStr"/>
+      <c r="H87" s="20" t="inlineStr"/>
+      <c r="I87" s="20" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="J86" s="20" t="inlineStr"/>
-      <c r="K86" s="21" t="inlineStr">
+      <c r="J87" s="20" t="inlineStr"/>
+      <c r="K87" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L86" s="20" t="inlineStr"/>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
+      <c r="L87" s="20" t="inlineStr"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr"/>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>Vegan Nacho Mix (→ Wk1 Tue Lunch)</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr"/>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K88" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L88" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Lunch (next cycle)</t>
         </is>
       </c>
     </row>
@@ -22308,12 +22304,12 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Beef Nacho Mix (→ Wk1 Tue Lunch)</t>
+          <t>Vegan Nacho Mix (→ Wk1 Tue Lunch)</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr"/>
@@ -22324,127 +22320,131 @@
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Lunch (next cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr"/>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Beef Nacho Mix (→ Wk1 Tue Lunch)</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr"/>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
           <t>2u</t>
         </is>
       </c>
-      <c r="I89" s="9" t="inlineStr">
+      <c r="I90" s="9" t="inlineStr">
         <is>
           <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
+      <c r="J90" s="9" t="inlineStr">
         <is>
           <t>90 min</t>
         </is>
       </c>
-      <c r="K89" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L89" s="9" t="inlineStr">
+      <c r="K90" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L90" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Tuesday Lunch (next cycle)</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr"/>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr"/>
+      <c r="C91" s="12" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>Marinade Five Spice Tofu</t>
         </is>
       </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="E91" s="12" t="inlineStr">
         <is>
           <t>15 pcs</t>
         </is>
       </c>
-      <c r="F90" s="12" t="inlineStr"/>
-      <c r="G90" s="12" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr"/>
+      <c r="G91" s="12" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr">
+      <c r="H91" s="12" t="inlineStr">
         <is>
           <t>1/2 hotel</t>
         </is>
       </c>
-      <c r="I90" s="12" t="inlineStr"/>
-      <c r="J90" s="12" t="inlineStr">
+      <c r="I91" s="12" t="inlineStr"/>
+      <c r="J91" s="12" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K90" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L90" s="12" t="inlineStr">
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="inlineStr"/>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>Beef Stroganoff</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr"/>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I91" s="9" t="inlineStr"/>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>180 min</t>
-        </is>
-      </c>
-      <c r="K91" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L91" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Sunday Dinner</t>
         </is>
       </c>
     </row>
@@ -22462,12 +22462,12 @@
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Vegan Mushroom Stroganoff</t>
+          <t>Beef Stroganoff</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr"/>
@@ -22478,77 +22478,73 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>1/2 hotel</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr"/>
       <c r="J92" s="9" t="inlineStr">
         <is>
+          <t>180 min</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Sunday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr"/>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Vegan Mushroom Stroganoff</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr"/>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr"/>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K92" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L92" s="9" t="inlineStr">
+      <c r="K93" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L93" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Sunday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr"/>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>Chicken Ranch Salad Mix (→ Fri Lunch — make day before send)</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F93" s="12" t="inlineStr"/>
-      <c r="G93" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I93" s="12" t="inlineStr">
-        <is>
-          <t>Mix; chill overnight; send Thu PM</t>
-        </is>
-      </c>
-      <c r="J93" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K93" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L93" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Friday Lunch</t>
         </is>
       </c>
     </row>
@@ -22566,12 +22562,12 @@
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Prep Slaw (→ Fri Lunch)</t>
+          <t>Chicken Ranch Salad Mix (→ Fri Lunch — make day before send)</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr"/>
@@ -22580,255 +22576,259 @@
           <t>bus bin</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr"/>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
+          <t>Mix; chill overnight; send Thu PM</t>
+        </is>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K94" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L94" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk.4 Friday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr"/>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Prep Slaw (→ Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr"/>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr"/>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
           <t>Shred; dress; chill; send Thu PM</t>
         </is>
       </c>
-      <c r="J94" s="12" t="inlineStr">
+      <c r="J95" s="12" t="inlineStr">
         <is>
           <t>??? min</t>
         </is>
       </c>
-      <c r="K94" s="14" t="inlineStr">
+      <c r="K95" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L94" s="12" t="inlineStr">
+      <c r="L95" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk.4 Friday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="13" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="14" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B96" s="14" t="inlineStr"/>
-      <c r="C96" s="14" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr"/>
+      <c r="C97" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D96" s="14" t="inlineStr">
+      <c r="D97" s="14" t="inlineStr">
         <is>
           <t>Reheat Beef &amp; Vegetable Stew (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E96" s="14" t="inlineStr">
+      <c r="E97" s="14" t="inlineStr">
         <is>
           <t>130 lbs</t>
         </is>
       </c>
-      <c r="F96" s="14" t="inlineStr"/>
-      <c r="G96" s="14" t="inlineStr">
+      <c r="F97" s="14" t="inlineStr"/>
+      <c r="G97" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H96" s="14" t="inlineStr">
+      <c r="H97" s="14" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I96" s="14" t="inlineStr">
+      <c r="I97" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J96" s="14" t="inlineStr">
+      <c r="J97" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K96" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L96" s="14" t="inlineStr">
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L97" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Tuesday Production</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr"/>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
+      <c r="D98" s="9" t="inlineStr">
         <is>
           <t>Roasted Potatoes (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E97" s="9" t="inlineStr">
+      <c r="E98" s="9" t="inlineStr">
         <is>
           <t>2 bins/4 hotels</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F98" s="9" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
+      <c r="G98" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H97" s="9" t="inlineStr">
+      <c r="H98" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
+      <c r="I98" s="9" t="inlineStr">
         <is>
           <t>Steam/Roast</t>
         </is>
       </c>
-      <c r="J97" s="9" t="inlineStr">
+      <c r="J98" s="9" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K97" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="14" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B98" s="14" t="inlineStr"/>
-      <c r="C98" s="14" t="inlineStr">
+      <c r="B99" s="14" t="inlineStr"/>
+      <c r="C99" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D98" s="14" t="inlineStr">
+      <c r="D99" s="14" t="inlineStr">
         <is>
           <t>Reheat Eggplant/Cassava Stew (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E98" s="14" t="inlineStr">
+      <c r="E99" s="14" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F98" s="14" t="inlineStr"/>
-      <c r="G98" s="14" t="inlineStr">
+      <c r="F99" s="14" t="inlineStr"/>
+      <c r="G99" s="14" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr">
+      <c r="H99" s="14" t="inlineStr">
         <is>
           <t>2u</t>
         </is>
       </c>
-      <c r="I98" s="14" t="inlineStr">
+      <c r="I99" s="14" t="inlineStr">
         <is>
           <t>Reheat</t>
         </is>
       </c>
-      <c r="J98" s="14" t="inlineStr">
+      <c r="J99" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K98" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L98" s="14" t="inlineStr">
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L99" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Friday Production</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="15" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 11 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr"/>
-      <c r="C100" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E100" s="16" t="inlineStr">
-        <is>
-          <t>30 lbs</t>
-        </is>
-      </c>
-      <c r="F100" s="16" t="inlineStr"/>
-      <c r="G100" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H100" s="16" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J100" s="16" t="inlineStr"/>
-      <c r="K100" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L100" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Thursday Production</t>
         </is>
       </c>
     </row>
@@ -22846,27 +22846,23 @@
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
+          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E101" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F101" s="16" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
+          <t>30 lbs</t>
+        </is>
+      </c>
+      <c r="F101" s="16" t="inlineStr"/>
       <c r="G101" s="16" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="H101" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="I101" s="16" t="inlineStr">
@@ -22882,7 +22878,7 @@
       </c>
       <c r="L101" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Wednesday Dinner (same day)</t>
+          <t>Produced: Wk. 3 Thursday Production</t>
         </is>
       </c>
     </row>
@@ -22900,21 +22896,29 @@
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>HOT Roasted Potatoes → Dinner</t>
         </is>
       </c>
       <c r="E102" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F102" s="16" t="inlineStr"/>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
       <c r="G102" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H102" s="16" t="inlineStr"/>
+      <c r="H102" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -22928,7 +22932,7 @@
       </c>
       <c r="L102" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Friday Production</t>
+          <t>Produced: Wk. 4 Wednesday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -22946,21 +22950,21 @@
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
       <c r="E103" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="F103" s="16" t="inlineStr"/>
-      <c r="G103" s="16" t="inlineStr"/>
-      <c r="H103" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+      <c r="G103" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H103" s="16" t="inlineStr"/>
       <c r="I103" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -22974,7 +22978,7 @@
       </c>
       <c r="L103" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Tuesday Production</t>
+          <t>Produced: Wk. 3 Friday Production</t>
         </is>
       </c>
     </row>
@@ -22992,91 +22996,91 @@
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>Cold Chickpea Salad → Thu Lunch</t>
+          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
         </is>
       </c>
       <c r="E104" s="16" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F104" s="16" t="inlineStr"/>
       <c r="G104" s="16" t="inlineStr"/>
-      <c r="H104" s="16" t="inlineStr"/>
+      <c r="H104" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J104" s="16" t="inlineStr"/>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L104" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Tuesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr"/>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Salad → Thu Lunch</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F105" s="16" t="inlineStr"/>
+      <c r="G105" s="16" t="inlineStr"/>
+      <c r="H105" s="16" t="inlineStr"/>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J104" s="16" t="inlineStr"/>
-      <c r="K104" s="17" t="inlineStr">
+      <c r="J105" s="16" t="inlineStr"/>
+      <c r="K105" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L104" s="16" t="inlineStr">
+      <c r="L105" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Tue Production (LAN)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>◆  THURSDAY  —  Jun 11</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 4 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr"/>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>HOT Halal Beef Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr"/>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H107" s="6" t="inlineStr"/>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J107" s="6" t="inlineStr"/>
-      <c r="K107" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L107" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -23094,29 +23098,21 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+          <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr"/>
       <c r="G108" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
+      <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -23130,7 +23126,7 @@
       </c>
       <c r="L108" s="6" t="inlineStr">
         <is>
-          <t>Produced: Wk.4 Sun Production (LAN — shaped earlier)</t>
+          <t>Produced: Wk. 4 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -23148,96 +23144,100 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
+          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr"/>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Sun Production (LAN — shaped earlier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr"/>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
           <t>Cold Lettuce / Tomato → Lunch</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>1 unit</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr"/>
-      <c r="G109" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="H110" s="6" t="inlineStr">
         <is>
           <t>1 unit</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I110" s="6" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J109" s="6" t="inlineStr"/>
-      <c r="K109" s="17" t="inlineStr">
+      <c r="J110" s="6" t="inlineStr"/>
+      <c r="K110" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L109" s="6" t="inlineStr">
+      <c r="L110" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Thu Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>Halal Beef Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>160 pcs</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr"/>
-      <c r="G111" s="9" t="inlineStr"/>
-      <c r="H111" s="9" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>From freezer; oven 30 min day-of</t>
-        </is>
-      </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K111" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L111" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Lunch</t>
         </is>
       </c>
     </row>
@@ -23255,108 +23255,104 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
+          <t>Halal Beef Burgers (Thu Lunch)</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>160 pcs</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr"/>
+      <c r="G112" s="9" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>From freezer; oven 30 min day-of</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K112" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr"/>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
           <t>Black Bean Patties (Thu Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E112" s="9" t="inlineStr">
+      <c r="E113" s="9" t="inlineStr">
         <is>
           <t>20 pcs</t>
         </is>
       </c>
-      <c r="F112" s="9" t="inlineStr">
+      <c r="F113" s="9" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="G112" s="9" t="inlineStr">
+      <c r="G113" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H112" s="9" t="inlineStr">
+      <c r="H113" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I112" s="9" t="inlineStr">
+      <c r="I113" s="9" t="inlineStr">
         <is>
           <t>Oven or pan</t>
         </is>
       </c>
-      <c r="J112" s="9" t="inlineStr">
+      <c r="J113" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K112" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L112" s="9" t="inlineStr">
+      <c r="K113" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk.4 Thursday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="11" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="12" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr"/>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D114" s="12" t="inlineStr">
-        <is>
-          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F114" s="12" t="inlineStr"/>
-      <c r="G114" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H114" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I114" s="12" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
-        </is>
-      </c>
-      <c r="J114" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K114" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L114" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Saturday Lunch</t>
         </is>
       </c>
     </row>
@@ -23374,12 +23370,12 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
+          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr"/>
@@ -23390,80 +23386,88 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
+        </is>
+      </c>
+      <c r="J115" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K115" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L115" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk.4 Saturday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr"/>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="I115" s="12" t="inlineStr">
+      <c r="F116" s="12" t="inlineStr"/>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="I116" s="12" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Dress; chill; send cold</t>
         </is>
       </c>
-      <c r="J115" s="12" t="inlineStr">
+      <c r="J116" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K115" s="14" t="inlineStr">
+      <c r="K116" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L115" s="12" t="inlineStr">
+      <c r="L116" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk.4 Saturday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="13" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr"/>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr"/>
-      <c r="G117" s="9" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
-      <c r="I117" s="9" t="inlineStr">
-        <is>
-          <t>Combi roast</t>
-        </is>
-      </c>
-      <c r="J117" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K117" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L117" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -23481,12 +23485,12 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>6 hotels</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -23494,79 +23498,75 @@
       <c r="H118" s="9" t="inlineStr"/>
       <c r="I118" s="9" t="inlineStr">
         <is>
+          <t>Combi roast</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr"/>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr"/>
+      <c r="G119" s="9" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
           <t>Wok/oven</t>
         </is>
       </c>
-      <c r="J118" s="9" t="inlineStr">
+      <c r="J119" s="9" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K118" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L118" s="9" t="inlineStr">
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Thursday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="15" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 24.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="inlineStr"/>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
-        </is>
-      </c>
-      <c r="E120" s="16" t="inlineStr">
-        <is>
-          <t>215 pcs</t>
-        </is>
-      </c>
-      <c r="F120" s="16" t="inlineStr"/>
-      <c r="G120" s="16" t="inlineStr">
-        <is>
-          <t>hotel/vac</t>
-        </is>
-      </c>
-      <c r="H120" s="16" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J120" s="16" t="inlineStr"/>
-      <c r="K120" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L120" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
         </is>
       </c>
     </row>
@@ -23584,23 +23584,23 @@
       </c>
       <c r="D121" s="16" t="inlineStr">
         <is>
-          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
+          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
         </is>
       </c>
       <c r="E121" s="16" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>215 pcs</t>
         </is>
       </c>
       <c r="F121" s="16" t="inlineStr"/>
       <c r="G121" s="16" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>hotel/vac</t>
         </is>
       </c>
       <c r="H121" s="16" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>6 hotels</t>
         </is>
       </c>
       <c r="I121" s="16" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="L121" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
         </is>
       </c>
     </row>
@@ -23634,28 +23634,28 @@
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>Cold Beef Nacho Mix → Rex fridge</t>
+          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
       <c r="E122" s="16" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="F122" s="16" t="inlineStr"/>
       <c r="G122" s="16" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="H122" s="16" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J122" s="16" t="inlineStr"/>
@@ -23666,7 +23666,7 @@
       </c>
       <c r="L122" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Wednesday Production</t>
+          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
@@ -23684,12 +23684,12 @@
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>Cold Vegan Nacho Mix → Rex fridge</t>
+          <t>Cold Beef Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E123" s="16" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F123" s="16" t="inlineStr"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="H123" s="16" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="I123" s="16" t="inlineStr">
@@ -23734,39 +23734,39 @@
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>Cold Vegan Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="E124" s="16" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="F124" s="16" t="inlineStr"/>
       <c r="G124" s="16" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="H124" s="16" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>0.5u</t>
         </is>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
         </is>
       </c>
       <c r="J124" s="16" t="inlineStr"/>
-      <c r="K124" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L124" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk.4 Wed Production (LAN)</t>
+          <t>Produced: Wk. 4 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -23784,7 +23784,7 @@
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
         </is>
       </c>
       <c r="E125" s="16" t="inlineStr">
@@ -23793,11 +23793,19 @@
         </is>
       </c>
       <c r="F125" s="16" t="inlineStr"/>
-      <c r="G125" s="16" t="inlineStr"/>
-      <c r="H125" s="16" t="inlineStr"/>
+      <c r="G125" s="16" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H125" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
-          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J125" s="16" t="inlineStr"/>
@@ -23812,231 +23820,223 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr"/>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>Cold Slaw → Fri Lunch side</t>
+        </is>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F126" s="16" t="inlineStr"/>
+      <c r="G126" s="16" t="inlineStr"/>
+      <c r="H126" s="16" t="inlineStr"/>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J126" s="16" t="inlineStr"/>
+      <c r="K126" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L126" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Wed Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>◆  FRIDAY  —  Jun 12</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 0.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr"/>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr"/>
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>HOT Crispy Falafel → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr"/>
-      <c r="G128" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H128" s="6" t="inlineStr">
+      <c r="H129" s="6" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="I128" s="6" t="inlineStr">
+      <c r="I129" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J128" s="6" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L128" s="6" t="inlineStr">
+      <c r="J129" s="6" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Fri Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="14" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B130" s="14" t="inlineStr"/>
-      <c r="C130" s="14" t="inlineStr">
+      <c r="B131" s="14" t="inlineStr"/>
+      <c r="C131" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D130" s="14" t="inlineStr">
+      <c r="D131" s="14" t="inlineStr">
         <is>
           <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E130" s="14" t="inlineStr">
+      <c r="E131" s="14" t="inlineStr">
         <is>
           <t>30 pcs</t>
         </is>
       </c>
-      <c r="F130" s="14" t="inlineStr"/>
-      <c r="G130" s="14" t="inlineStr"/>
-      <c r="H130" s="14" t="inlineStr"/>
-      <c r="I130" s="14" t="inlineStr">
+      <c r="F131" s="14" t="inlineStr"/>
+      <c r="G131" s="14" t="inlineStr"/>
+      <c r="H131" s="14" t="inlineStr"/>
+      <c r="I131" s="14" t="inlineStr">
         <is>
           <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
-      <c r="J130" s="14" t="inlineStr">
+      <c r="J131" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K130" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L130" s="14" t="inlineStr">
+      <c r="K131" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L131" s="14" t="inlineStr">
         <is>
           <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="11" t="inlineStr">
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="9" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr"/>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr"/>
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>Vegan Carnitas</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>15 lbs</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr"/>
-      <c r="G132" s="9" t="inlineStr">
+      <c r="F133" s="9" t="inlineStr"/>
+      <c r="G133" s="9" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H132" s="9" t="inlineStr">
+      <c r="H133" s="9" t="inlineStr">
         <is>
           <t>1/2 hotel</t>
         </is>
       </c>
-      <c r="I132" s="9" t="inlineStr">
+      <c r="I133" s="9" t="inlineStr">
         <is>
           <t>Stove</t>
         </is>
       </c>
-      <c r="J132" s="9" t="inlineStr">
+      <c r="J133" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K132" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L132" s="9" t="inlineStr">
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L133" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="12" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B133" s="12" t="inlineStr"/>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D133" s="12" t="inlineStr">
-        <is>
-          <t>Broccoli Prep (Saturday Lunch)</t>
-        </is>
-      </c>
-      <c r="E133" s="12" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="F133" s="12" t="inlineStr"/>
-      <c r="G133" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H133" s="12" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="I133" s="12" t="inlineStr"/>
-      <c r="J133" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K133" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Saturday Lunch</t>
         </is>
       </c>
     </row>
@@ -24054,35 +24054,39 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
+          <t>Broccoli Prep (Saturday Lunch)</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>4 hotels veg</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr"/>
-      <c r="G134" s="12" t="inlineStr"/>
-      <c r="H134" s="12" t="inlineStr"/>
-      <c r="I134" s="12" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
-        </is>
-      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="inlineStr"/>
       <c r="J134" s="12" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K134" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K134" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L134" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
+          <t>Serves: Wk. 4 Saturday Lunch</t>
         </is>
       </c>
     </row>
@@ -24100,26 +24104,22 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Jerk Marinade</t>
+          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>4 hotels veg</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr"/>
-      <c r="G135" s="12" t="inlineStr">
-        <is>
-          <t>cambro/bag</t>
-        </is>
-      </c>
-      <c r="H135" s="12" t="inlineStr">
-        <is>
-          <t>1 bag/8 qt</t>
-        </is>
-      </c>
-      <c r="I135" s="12" t="inlineStr"/>
+      <c r="G135" s="12" t="inlineStr"/>
+      <c r="H135" s="12" t="inlineStr"/>
+      <c r="I135" s="12" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
+        </is>
+      </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
@@ -24132,7 +24132,7 @@
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
+          <t>Serves: Wk. 4 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -24150,29 +24150,29 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>Jerk Cauliflower</t>
+          <t>Jerk Marinade</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>15 pcs</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr"/>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>cambro/bag</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>1/2 hotel</t>
+          <t>1 bag/8 qt</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr"/>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="K136" s="10" t="inlineStr">
@@ -24200,25 +24200,29 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
+          <t>Jerk Cauliflower</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>15 pcs</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr"/>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H137" s="12" t="inlineStr"/>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
       <c r="I137" s="12" t="inlineStr"/>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
@@ -24228,7 +24232,7 @@
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+          <t>Serves: Wk. 1 Monday Dinner</t>
         </is>
       </c>
     </row>
@@ -24246,29 +24250,25 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
+          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>1 cs</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr"/>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H138" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr"/>
       <c r="I138" s="12" t="inlineStr"/>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="K138" s="10" t="inlineStr">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
+          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -24318,78 +24318,74 @@
       <c r="I139" s="12" t="inlineStr"/>
       <c r="J139" s="12" t="inlineStr">
         <is>
+          <t>10 min</t>
+        </is>
+      </c>
+      <c r="K139" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr"/>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr"/>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr"/>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K139" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
+      <c r="K140" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L140" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="13" t="inlineStr">
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="14" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B141" s="14" t="inlineStr"/>
-      <c r="C141" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D141" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Tandoori Pork (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E141" s="14" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="F141" s="14" t="inlineStr"/>
-      <c r="G141" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H141" s="14" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I141" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J141" s="14" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K141" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L141" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Monday Production</t>
         </is>
       </c>
     </row>
@@ -24407,12 +24403,12 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>Reheat Tandoori Chicken — Halal (Fri Dinner)</t>
+          <t>Reheat Tandoori Pork (Fri Dinner)</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="F142" s="14" t="inlineStr"/>
@@ -24423,130 +24419,138 @@
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K142" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Monday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="inlineStr"/>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Tandoori Chicken — Halal (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
           <t>1u</t>
         </is>
       </c>
-      <c r="I142" s="14" t="inlineStr">
+      <c r="F143" s="14" t="inlineStr"/>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J142" s="14" t="inlineStr">
+      <c r="J143" s="14" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K142" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
+      <c r="K143" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L143" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Tuesday Production</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="9" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B143" s="9" t="inlineStr"/>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr"/>
+      <c r="C144" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D143" s="9" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>Roast Tandoori Tofu (Fri Dinner — Veg)</t>
         </is>
       </c>
-      <c r="E143" s="9" t="inlineStr">
+      <c r="E144" s="9" t="inlineStr">
         <is>
           <t>12 pcs</t>
         </is>
       </c>
-      <c r="F143" s="9" t="inlineStr"/>
-      <c r="G143" s="9" t="inlineStr"/>
-      <c r="H143" s="9" t="inlineStr">
+      <c r="F144" s="9" t="inlineStr"/>
+      <c r="G144" s="9" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="I143" s="9" t="inlineStr">
+      <c r="I144" s="9" t="inlineStr">
         <is>
           <t>Oven roast</t>
         </is>
       </c>
-      <c r="J143" s="9" t="inlineStr">
+      <c r="J144" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K143" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L143" s="9" t="inlineStr">
+      <c r="K144" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L144" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="15" t="inlineStr">
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 7.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B145" s="16" t="inlineStr"/>
-      <c r="C145" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D145" s="16" t="inlineStr">
-        <is>
-          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E145" s="16" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="F145" s="16" t="inlineStr"/>
-      <c r="G145" s="16" t="inlineStr"/>
-      <c r="H145" s="16" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="I145" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J145" s="16" t="inlineStr"/>
-      <c r="K145" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L145" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -24564,31 +24568,35 @@
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>Pick up Baked Rolls at GC</t>
+          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E146" s="16" t="inlineStr">
         <is>
-          <t>pickup</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F146" s="16" t="inlineStr"/>
       <c r="G146" s="16" t="inlineStr"/>
-      <c r="H146" s="16" t="inlineStr"/>
+      <c r="H146" s="16" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
-          <t>GC → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J146" s="16" t="inlineStr"/>
-      <c r="K146" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
+      <c r="K146" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L146" s="16" t="inlineStr">
         <is>
-          <t>N/A — logistics</t>
+          <t>Produced: Wk. 4 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -24606,43 +24614,31 @@
       </c>
       <c r="D147" s="16" t="inlineStr">
         <is>
-          <t>HOT Vegetable Biryani → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E147" s="16" t="inlineStr">
         <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="F147" s="16" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
-      <c r="G147" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H147" s="16" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F147" s="16" t="inlineStr"/>
+      <c r="G147" s="16" t="inlineStr"/>
+      <c r="H147" s="16" t="inlineStr"/>
       <c r="I147" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J147" s="16" t="inlineStr"/>
-      <c r="K147" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K147" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L147" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Friday Dinner (LAN same day)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -24660,197 +24656,197 @@
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
+          <t>HOT Vegetable Biryani → Dinner</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="F148" s="16" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J148" s="16" t="inlineStr"/>
+      <c r="K148" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L148" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Friday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr"/>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
           <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
         </is>
       </c>
-      <c r="E148" s="16" t="inlineStr">
+      <c r="E149" s="16" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="F148" s="16" t="inlineStr"/>
-      <c r="G148" s="16" t="inlineStr"/>
-      <c r="H148" s="16" t="inlineStr"/>
-      <c r="I148" s="16" t="inlineStr">
+      <c r="F149" s="16" t="inlineStr"/>
+      <c r="G149" s="16" t="inlineStr"/>
+      <c r="H149" s="16" t="inlineStr"/>
+      <c r="I149" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J148" s="16" t="inlineStr"/>
-      <c r="K148" s="17" t="inlineStr">
+      <c r="J149" s="16" t="inlineStr"/>
+      <c r="K149" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L148" s="16" t="inlineStr">
+      <c r="L149" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Friday Production</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>◆  SATURDAY  —  Jun 13</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 1.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="6" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B151" s="6" t="inlineStr"/>
-      <c r="C151" s="6" t="inlineStr">
+      <c r="B152" s="6" t="inlineStr"/>
+      <c r="C152" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>Cold Mixed Lettuce → Lunch</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E152" s="6" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr"/>
-      <c r="G151" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr"/>
+      <c r="G152" s="6" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H151" s="6" t="inlineStr">
+      <c r="H152" s="6" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="I151" s="6" t="inlineStr">
+      <c r="I152" s="6" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="J151" s="6" t="inlineStr"/>
-      <c r="K151" s="17" t="inlineStr">
+      <c r="J152" s="6" t="inlineStr"/>
+      <c r="K152" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L151" s="6" t="inlineStr">
+      <c r="L152" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Sat Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="20" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B153" s="20" t="inlineStr"/>
-      <c r="C153" s="20" t="inlineStr">
+      <c r="B154" s="20" t="inlineStr"/>
+      <c r="C154" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D153" s="20" t="inlineStr">
+      <c r="D154" s="20" t="inlineStr">
         <is>
           <t>Tuna Rex + Chickpea Rex Salad (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E153" s="20" t="inlineStr"/>
-      <c r="F153" s="20" t="inlineStr"/>
-      <c r="G153" s="20" t="inlineStr"/>
-      <c r="H153" s="20" t="inlineStr"/>
-      <c r="I153" s="20" t="inlineStr">
+      <c r="E154" s="20" t="inlineStr"/>
+      <c r="F154" s="20" t="inlineStr"/>
+      <c r="G154" s="20" t="inlineStr"/>
+      <c r="H154" s="20" t="inlineStr"/>
+      <c r="I154" s="20" t="inlineStr">
         <is>
           <t>Cold salad pre-sent Fri PM; Mixed Lettuce sent AM</t>
         </is>
       </c>
-      <c r="J153" s="20" t="inlineStr"/>
-      <c r="K153" s="21" t="inlineStr">
+      <c r="J154" s="20" t="inlineStr"/>
+      <c r="K154" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L153" s="20" t="inlineStr"/>
-    </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="11" t="inlineStr">
+      <c r="L154" s="20" t="inlineStr"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B155" s="12" t="inlineStr"/>
-      <c r="C155" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D155" s="12" t="inlineStr">
-        <is>
-          <t>Tuna Salad Mix (→ NC Wk1 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F155" s="12" t="inlineStr"/>
-      <c r="G155" s="12" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="H155" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I155" s="12" t="inlineStr">
-        <is>
-          <t>Mix; chill; send Sun PM</t>
-        </is>
-      </c>
-      <c r="J155" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K155" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L155" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk.1 Monday Lunch (next cycle)</t>
         </is>
       </c>
     </row>
@@ -24868,35 +24864,43 @@
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>Prep Broccoli Salad (→ NC Wk1 Sun Lunch)</t>
+          <t>Tuna Salad Mix (→ NC Wk1 Mon Lunch)</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr"/>
-      <c r="G156" s="12" t="inlineStr"/>
-      <c r="H156" s="12" t="inlineStr"/>
+      <c r="G156" s="12" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="H156" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
       <c r="I156" s="12" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
+          <t>Mix; chill; send Sun PM</t>
         </is>
       </c>
       <c r="J156" s="12" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K156" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K156" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L156" s="12" t="inlineStr">
         <is>
-          <t>Serves: NC Wk. 1 Sunday Lunch</t>
+          <t>Serves: Wk.1 Monday Lunch (next cycle)</t>
         </is>
       </c>
     </row>
@@ -24914,12 +24918,12 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Trim/Season Jerk Chicken Legs (→ NC Wk1 Mon Dinner)</t>
+          <t>Prep Broccoli Salad (→ NC Wk1 Sun Lunch)</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>165 pcs / 3 bins</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr"/>
@@ -24927,12 +24931,12 @@
       <c r="H157" s="12" t="inlineStr"/>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>Season; hold in bins at Bloor</t>
+          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="K157" s="10" t="inlineStr">
@@ -24942,7 +24946,7 @@
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>Serves: NC Wk. 1 Monday Dinner</t>
+          <t>Serves: NC Wk. 1 Sunday Lunch</t>
         </is>
       </c>
     </row>
@@ -24960,12 +24964,12 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg Stacks (→ NC Wk1 Sun Lunch — Veg)</t>
+          <t>Trim/Season Jerk Chicken Legs (→ NC Wk1 Mon Dinner)</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>165 pcs / 3 bins</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr"/>
@@ -24973,76 +24977,68 @@
       <c r="H158" s="12" t="inlineStr"/>
       <c r="I158" s="12" t="inlineStr">
         <is>
+          <t>Season; hold in bins at Bloor</t>
+        </is>
+      </c>
+      <c r="J158" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K158" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L158" s="12" t="inlineStr">
+        <is>
+          <t>Serves: NC Wk. 1 Monday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr"/>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg Stacks (→ NC Wk1 Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr"/>
+      <c r="G159" s="12" t="inlineStr"/>
+      <c r="H159" s="12" t="inlineStr"/>
+      <c r="I159" s="12" t="inlineStr">
+        <is>
           <t>Slice/season at Bloor; roast Sun AM</t>
         </is>
       </c>
-      <c r="J158" s="12" t="inlineStr">
+      <c r="J159" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K158" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L158" s="12" t="inlineStr">
+      <c r="K159" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L159" s="12" t="inlineStr">
         <is>
           <t>Serves: NC Wk. 1 Sunday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B159" s="9" t="inlineStr"/>
-      <c r="C159" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>Cook Carnitas Pork (→ NC Wk1 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="E159" s="9" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F159" s="9" t="inlineStr"/>
-      <c r="G159" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H159" s="9" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I159" s="9" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-      <c r="J159" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K159" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L159" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
         </is>
       </c>
     </row>
@@ -25060,7 +25056,7 @@
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>Cook Carnitas Chicken (→ NC Wk1 Tue Dinner)</t>
+          <t>Cook Carnitas Pork (→ NC Wk1 Tue Dinner)</t>
         </is>
       </c>
       <c r="E160" s="9" t="inlineStr">
@@ -25076,142 +25072,142 @@
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K160" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L160" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="inlineStr"/>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>Cook Carnitas Chicken (→ NC Wk1 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr"/>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
           <t>1.0u</t>
         </is>
       </c>
-      <c r="I160" s="9" t="inlineStr">
+      <c r="I161" s="9" t="inlineStr">
         <is>
           <t>Oven; cool then vac bag; hold Bloor fridge</t>
         </is>
       </c>
-      <c r="J160" s="9" t="inlineStr">
+      <c r="J161" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K160" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L160" s="9" t="inlineStr">
+      <c r="K161" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L161" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="13" t="inlineStr">
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="20" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B162" s="20" t="inlineStr"/>
-      <c r="C162" s="20" t="inlineStr">
+      <c r="B163" s="20" t="inlineStr"/>
+      <c r="C163" s="20" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="D162" s="20" t="inlineStr">
+      <c r="D163" s="20" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E162" s="20" t="inlineStr">
+      <c r="E163" s="20" t="inlineStr">
         <is>
           <t>3 pcs</t>
         </is>
       </c>
-      <c r="F162" s="20" t="inlineStr">
+      <c r="F163" s="20" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="G162" s="20" t="inlineStr">
+      <c r="G163" s="20" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H162" s="20" t="inlineStr"/>
-      <c r="I162" s="20" t="inlineStr">
+      <c r="H163" s="20" t="inlineStr"/>
+      <c r="I163" s="20" t="inlineStr">
         <is>
           <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
         </is>
       </c>
-      <c r="J162" s="20" t="inlineStr">
+      <c r="J163" s="20" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K162" s="14" t="inlineStr">
+      <c r="K163" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L162" s="20" t="inlineStr">
+      <c r="L163" s="20" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="14" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B163" s="14" t="inlineStr"/>
-      <c r="C163" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D163" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="E163" s="14" t="inlineStr">
-        <is>
-          <t>110 lbs</t>
-        </is>
-      </c>
-      <c r="F163" s="14" t="inlineStr"/>
-      <c r="G163" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H163" s="14" t="inlineStr">
-        <is>
-          <t>3u</t>
-        </is>
-      </c>
-      <c r="I163" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J163" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K163" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L163" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -25229,12 +25225,12 @@
       </c>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
+          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>110 lbs</t>
         </is>
       </c>
       <c r="F164" s="14" t="inlineStr"/>
@@ -25245,130 +25241,138 @@
       </c>
       <c r="H164" s="14" t="inlineStr">
         <is>
+          <t>3u</t>
+        </is>
+      </c>
+      <c r="I164" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K164" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L164" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="14" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B165" s="14" t="inlineStr"/>
+      <c r="C165" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D165" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E165" s="14" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F165" s="14" t="inlineStr"/>
+      <c r="G165" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H165" s="14" t="inlineStr">
+        <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="I164" s="14" t="inlineStr">
+      <c r="I165" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J164" s="14" t="inlineStr">
+      <c r="J165" s="14" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K164" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L164" s="14" t="inlineStr">
+      <c r="K165" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L165" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="9" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B165" s="9" t="inlineStr"/>
-      <c r="C165" s="9" t="inlineStr">
+      <c r="B166" s="9" t="inlineStr"/>
+      <c r="C166" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D165" s="9" t="inlineStr">
+      <c r="D166" s="9" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E165" s="9" t="inlineStr">
+      <c r="E166" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F165" s="9" t="inlineStr"/>
-      <c r="G165" s="9" t="inlineStr">
+      <c r="F166" s="9" t="inlineStr"/>
+      <c r="G166" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H165" s="9" t="inlineStr">
+      <c r="H166" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I165" s="9" t="inlineStr"/>
-      <c r="J165" s="9" t="inlineStr">
+      <c r="I166" s="9" t="inlineStr"/>
+      <c r="J166" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K165" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L165" s="9" t="inlineStr">
+      <c r="K166" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L166" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="15" t="inlineStr">
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B167" s="16" t="inlineStr"/>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D167" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef Massaman Curry → Dinner</t>
-        </is>
-      </c>
-      <c r="E167" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F167" s="16" t="inlineStr"/>
-      <c r="G167" s="16" t="inlineStr"/>
-      <c r="H167" s="16" t="inlineStr">
-        <is>
-          <t>3u</t>
-        </is>
-      </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J167" s="16" t="inlineStr"/>
-      <c r="K167" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L167" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -25386,19 +25390,19 @@
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
+          <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
       <c r="E168" s="16" t="inlineStr">
         <is>
-          <t>0.5 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F168" s="16" t="inlineStr"/>
       <c r="G168" s="16" t="inlineStr"/>
       <c r="H168" s="16" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>3u</t>
         </is>
       </c>
       <c r="I168" s="16" t="inlineStr">
@@ -25432,21 +25436,21 @@
       </c>
       <c r="D169" s="16" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner side</t>
+          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E169" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="F169" s="16" t="inlineStr"/>
-      <c r="G169" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H169" s="16" t="inlineStr"/>
+      <c r="G169" s="16" t="inlineStr"/>
+      <c r="H169" s="16" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
       <c r="I169" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -25460,7 +25464,7 @@
       </c>
       <c r="L169" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -25478,24 +25482,24 @@
       </c>
       <c r="D170" s="16" t="inlineStr">
         <is>
-          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+          <t>HOT Rice → Dinner side</t>
         </is>
       </c>
       <c r="E170" s="16" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F170" s="16" t="inlineStr"/>
-      <c r="G170" s="16" t="inlineStr"/>
-      <c r="H170" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+      <c r="G170" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H170" s="16" t="inlineStr"/>
       <c r="I170" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex fridge</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J170" s="16" t="inlineStr"/>
@@ -25506,56 +25510,102 @@
       </c>
       <c r="L170" s="16" t="inlineStr">
         <is>
+          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr"/>
+      <c r="C171" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="inlineStr">
+        <is>
+          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E171" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F171" s="16" t="inlineStr"/>
+      <c r="G171" s="16" t="inlineStr"/>
+      <c r="H171" s="16" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex fridge</t>
+        </is>
+      </c>
+      <c r="J171" s="16" t="inlineStr"/>
+      <c r="K171" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L171" s="16" t="inlineStr">
+        <is>
           <t>Produced: Wk. 4 Saturday Production</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A99:L99"/>
-    <mergeCell ref="A149:L149"/>
+    <mergeCell ref="A128:L128"/>
+    <mergeCell ref="A84:L84"/>
     <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A154:L154"/>
-    <mergeCell ref="A105:L105"/>
+    <mergeCell ref="A120:L120"/>
     <mergeCell ref="A50:L50"/>
     <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A145:L145"/>
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A57:L57"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A95:L95"/>
-    <mergeCell ref="A113:L113"/>
+    <mergeCell ref="A86:L86"/>
     <mergeCell ref="A76:L76"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A71:L71"/>
-    <mergeCell ref="A129:L129"/>
-    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="A151:L151"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A116:L116"/>
+    <mergeCell ref="A141:L141"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="A150:L150"/>
-    <mergeCell ref="A126:L126"/>
     <mergeCell ref="A106:L106"/>
-    <mergeCell ref="A144:L144"/>
-    <mergeCell ref="A140:L140"/>
-    <mergeCell ref="A131:L131"/>
+    <mergeCell ref="A162:L162"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A161:L161"/>
-    <mergeCell ref="A152:L152"/>
+    <mergeCell ref="A100:L100"/>
+    <mergeCell ref="A96:L96"/>
+    <mergeCell ref="A117:L117"/>
+    <mergeCell ref="A155:L155"/>
+    <mergeCell ref="A111:L111"/>
     <mergeCell ref="A127:L127"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A167:L167"/>
+    <mergeCell ref="A130:L130"/>
     <mergeCell ref="A39:L39"/>
     <mergeCell ref="A83:L83"/>
+    <mergeCell ref="A114:L114"/>
     <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A82:L82"/>
-    <mergeCell ref="A166:L166"/>
     <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A107:L107"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A132:L132"/>
     <mergeCell ref="A61:L61"/>
-    <mergeCell ref="A119:L119"/>
-    <mergeCell ref="A110:L110"/>
-    <mergeCell ref="A87:L87"/>
+    <mergeCell ref="A88:L88"/>
+    <mergeCell ref="A153:L153"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L155"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>Dress; chill; send Thu PM</t>
+          <t>Dress; chill; send Thu PM | ⚠ NO RECIPE</t>
         </is>
       </c>
       <c r="J78" s="12" t="inlineStr">
@@ -3579,56 +3579,48 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>Cook Pork Adobo (→ Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>40 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr"/>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>Oven/Combi; cool; vac bag</t>
-        </is>
-      </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t>120 min</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
+      <c r="B79" s="12" t="inlineStr"/>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Egg Salad Mix (→ Fri Lunch — make at LAN)</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr"/>
+      <c r="G79" s="12" t="inlineStr"/>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I79" s="12" t="inlineStr"/>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K79" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Lunch</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3638,12 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
+          <t>Cook Pork Adobo (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>32 lbs cooked</t>
+          <t>40 lbs cooked</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -3662,249 +3654,257 @@
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Oven/Combi; cool; vac bag</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr"/>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
           <t>1u</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
+      <c r="I81" s="9" t="inlineStr">
         <is>
           <t>Oven/Combi; cool; vac bag</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K80" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L80" s="9" t="inlineStr">
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="13" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr"/>
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>165 pcs</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr"/>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr"/>
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
+      <c r="H83" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I83" s="9" t="inlineStr">
         <is>
           <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>90 min</t>
         </is>
       </c>
-      <c r="K82" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L82" s="9" t="inlineStr">
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr"/>
-      <c r="C83" s="14" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr"/>
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D84" s="14" t="inlineStr">
         <is>
           <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E83" s="14" t="inlineStr">
+      <c r="E84" s="14" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F83" s="14" t="inlineStr"/>
-      <c r="G83" s="14" t="inlineStr">
+      <c r="F84" s="14" t="inlineStr"/>
+      <c r="G84" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H83" s="14" t="inlineStr">
+      <c r="H84" s="14" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I83" s="14" t="inlineStr">
+      <c r="I84" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged batch</t>
         </is>
       </c>
-      <c r="J83" s="14" t="inlineStr">
+      <c r="J84" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K83" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L83" s="14" t="inlineStr">
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L84" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Monday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr"/>
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>Herbed Couscous (Wed Dinner)</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H84" s="9" t="inlineStr">
+      <c r="H85" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr"/>
-      <c r="J84" s="9" t="inlineStr">
+      <c r="I85" s="9" t="inlineStr"/>
+      <c r="J85" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K84" s="14" t="inlineStr">
+      <c r="K85" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L84" s="9" t="inlineStr">
+      <c r="L85" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="15" t="inlineStr">
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 12.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="16" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="inlineStr"/>
-      <c r="C86" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F86" s="16" t="inlineStr"/>
-      <c r="G86" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H86" s="16" t="inlineStr"/>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J86" s="16" t="inlineStr"/>
-      <c r="K86" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L86" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -3922,39 +3922,35 @@
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>HOT Shakshuka Sauce → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr"/>
       <c r="G87" s="16" t="inlineStr">
         <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H87" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H87" s="16" t="inlineStr"/>
       <c r="I87" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J87" s="16" t="inlineStr"/>
-      <c r="K87" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K87" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L87" s="16" t="inlineStr">
         <is>
-          <t>Produced: pre-loaded batch (prev. cycle)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -3972,35 +3968,39 @@
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>HOT Herbed Couscous → Dinner side</t>
+          <t>HOT Shakshuka Sauce → Dinner</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr"/>
-      <c r="G88" s="16" t="inlineStr"/>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="H88" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J88" s="16" t="inlineStr"/>
-      <c r="K88" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L88" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Dinner (LAN same day)</t>
+          <t>Produced: pre-loaded batch (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -4018,39 +4018,35 @@
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Cold Pork Vindaloo → Rex fridge</t>
+          <t>HOT Herbed Couscous → Dinner side</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
-          <t>40 lbs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr"/>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
+      <c r="G89" s="16" t="inlineStr"/>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>1.5u</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J89" s="16" t="inlineStr"/>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K89" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L89" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Tuesday Production</t>
+          <t>Produced: Wk. 1 Wednesday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4064,12 @@
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>40 lbs</t>
         </is>
       </c>
       <c r="F90" s="16" t="inlineStr"/>
@@ -4084,7 +4080,7 @@
       </c>
       <c r="H90" s="16" t="inlineStr">
         <is>
-          <t>1.0u</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="I90" s="16" t="inlineStr">
@@ -4118,23 +4114,23 @@
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>HOT Shakshuka Chicken Legs → Dinner</t>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>165 pcs</t>
+          <t>32 lbs</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr"/>
       <c r="G91" s="16" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="H91" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>1.0u</t>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
@@ -4150,71 +4146,71 @@
       </c>
       <c r="L91" s="16" t="inlineStr">
         <is>
+          <t>Produced: Wk. 1 Tuesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr"/>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>HOT Shakshuka Chicken Legs → Dinner</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>165 pcs</t>
+        </is>
+      </c>
+      <c r="F92" s="16" t="inlineStr"/>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H92" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J92" s="16" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L92" s="16" t="inlineStr">
+        <is>
           <t>Produced: Wk. 1 Wednesday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>◆  THURSDAY  —  May 21</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 4 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr"/>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>HOT Halal Chicken Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>185 pcs</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr"/>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J94" s="6" t="inlineStr"/>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L94" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4228,12 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
+          <t>HOT Halal Chicken Burgers → Lunch</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>20 pcs</t>
+          <t>185 pcs</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -4246,7 +4242,11 @@
           <t>hotel</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -4264,60 +4264,56 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr"/>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr"/>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr"/>
+      <c r="K96" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr"/>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>185 pcs</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr"/>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I97" s="9" t="inlineStr"/>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K97" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Thursday Lunch</t>
         </is>
       </c>
     </row>
@@ -4335,96 +4331,96 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>185 pcs</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr"/>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
           <t>Quinoa Burgers (Thu Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>30 pcs</t>
         </is>
       </c>
-      <c r="F98" s="9" t="inlineStr"/>
-      <c r="G98" s="9" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr"/>
+      <c r="G99" s="9" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>Pan fry; send hot AM</t>
         </is>
       </c>
-      <c r="J98" s="9" t="inlineStr">
+      <c r="J99" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K98" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L98" s="9" t="inlineStr">
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr"/>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>130 lbs</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr"/>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H100" s="9" t="inlineStr">
-        <is>
-          <t>3.5 hotels</t>
-        </is>
-      </c>
-      <c r="I100" s="9" t="inlineStr"/>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>240 min</t>
-        </is>
-      </c>
-      <c r="K100" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L100" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Monday Lunch</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4438,12 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
+          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>130 lbs</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -4458,13 +4454,13 @@
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>0.5 hotel</t>
+          <t>3.5 hotels</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr"/>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>240 min</t>
         </is>
       </c>
       <c r="K101" s="10" t="inlineStr">
@@ -4474,7 +4470,7 @@
       </c>
       <c r="L101" s="9" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
+          <t>Serves: Wk. 2 Monday Lunch</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4488,12 @@
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>12 lbs</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -4508,88 +4504,80 @@
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>0.5 hotel</t>
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr"/>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr"/>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr"/>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
           <t>120 min</t>
         </is>
       </c>
-      <c r="K102" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L102" s="9" t="inlineStr">
+      <c r="K103" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L103" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="13" t="inlineStr">
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B104" s="14" t="inlineStr"/>
-      <c r="C104" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D104" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Butter Chicken (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F104" s="14" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G104" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H104" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I104" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="J104" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K104" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L104" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -4607,154 +4595,166 @@
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
+          <t>Reheat Butter Chicken (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L105" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr"/>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
           <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
         </is>
       </c>
-      <c r="E105" s="14" t="inlineStr">
+      <c r="E106" s="14" t="inlineStr">
         <is>
           <t>20 lbs</t>
         </is>
       </c>
-      <c r="F105" s="14" t="inlineStr">
+      <c r="F106" s="14" t="inlineStr">
         <is>
           <t>12 oz</t>
         </is>
       </c>
-      <c r="G105" s="14" t="inlineStr">
+      <c r="G106" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H105" s="14" t="inlineStr">
+      <c r="H106" s="14" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I105" s="14" t="inlineStr"/>
-      <c r="J105" s="14" t="inlineStr">
+      <c r="I106" s="14" t="inlineStr"/>
+      <c r="J106" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K105" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L105" s="14" t="inlineStr">
+      <c r="K106" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L106" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr"/>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="B107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D107" s="9" t="inlineStr">
         <is>
           <t>Roasted Cauliflower (Thu Dinner side)</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="E107" s="9" t="inlineStr">
         <is>
           <t>3 bins → 3 hotels</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="G106" s="9" t="inlineStr">
+      <c r="G107" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H106" s="9" t="inlineStr">
+      <c r="H107" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I106" s="9" t="inlineStr">
+      <c r="I107" s="9" t="inlineStr">
         <is>
           <t>⚠ CONFIRM carrot role in this side</t>
         </is>
       </c>
-      <c r="J106" s="9" t="inlineStr">
+      <c r="J107" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K106" s="14" t="inlineStr">
+      <c r="K107" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L106" s="9" t="inlineStr">
+      <c r="L107" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Thursday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="16" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="inlineStr"/>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E108" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F108" s="16" t="inlineStr"/>
-      <c r="G108" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H108" s="16" t="inlineStr"/>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J108" s="16" t="inlineStr"/>
-      <c r="K108" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L108" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 9 HOTELS (hot)</t>
         </is>
       </c>
     </row>
@@ -4772,43 +4772,35 @@
       </c>
       <c r="D109" s="16" t="inlineStr">
         <is>
-          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>80+20 lbs</t>
-        </is>
-      </c>
-      <c r="F109" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F109" s="16" t="inlineStr"/>
       <c r="G109" s="16" t="inlineStr">
         <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H109" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H109" s="16" t="inlineStr"/>
       <c r="I109" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J109" s="16" t="inlineStr"/>
-      <c r="K109" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K109" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L109" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -4826,35 +4818,43 @@
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>HOT Roasted Cauliflower → Dinner side</t>
+          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
         </is>
       </c>
       <c r="E110" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="F110" s="16" t="inlineStr"/>
-      <c r="G110" s="16" t="inlineStr"/>
+          <t>80+20 lbs</t>
+        </is>
+      </c>
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G110" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="H110" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J110" s="16" t="inlineStr"/>
-      <c r="K110" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L110" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -4872,258 +4872,277 @@
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
+          <t>HOT Roasted Cauliflower → Dinner side</t>
+        </is>
+      </c>
+      <c r="E111" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F111" s="16" t="inlineStr"/>
+      <c r="G111" s="16" t="inlineStr"/>
+      <c r="H111" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J111" s="16" t="inlineStr"/>
+      <c r="K111" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L111" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr"/>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
           <t>HOT Naan → Dinner</t>
         </is>
       </c>
-      <c r="E111" s="16" t="inlineStr">
+      <c r="E112" s="16" t="inlineStr">
         <is>
           <t>200 pcs</t>
         </is>
       </c>
-      <c r="F111" s="16" t="inlineStr">
+      <c r="F112" s="16" t="inlineStr">
         <is>
           <t>1 each (?)</t>
         </is>
       </c>
-      <c r="G111" s="16" t="inlineStr">
+      <c r="G112" s="16" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="H111" s="16" t="inlineStr">
+      <c r="H112" s="16" t="inlineStr">
         <is>
           <t>2 bags</t>
         </is>
       </c>
-      <c r="I111" s="16" t="inlineStr">
+      <c r="I112" s="16" t="inlineStr">
         <is>
           <t>Purchased; delivered direct to Rex or via van</t>
         </is>
       </c>
-      <c r="J111" s="16" t="inlineStr"/>
-      <c r="K111" s="19" t="inlineStr">
+      <c r="J112" s="16" t="inlineStr"/>
+      <c r="K112" s="19" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L111" s="16" t="inlineStr">
+      <c r="L112" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="inlineStr"/>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="inlineStr">
+        <is>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F113" s="16" t="inlineStr"/>
+      <c r="G113" s="16" t="inlineStr"/>
+      <c r="H113" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J113" s="16" t="inlineStr"/>
+      <c r="K113" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L113" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="inlineStr"/>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F114" s="16" t="inlineStr"/>
+      <c r="G114" s="16" t="inlineStr"/>
+      <c r="H114" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J114" s="16" t="inlineStr"/>
+      <c r="K114" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L114" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>◆  FRIDAY  —  May 22</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: ~1 items</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B114" s="20" t="inlineStr"/>
-      <c r="C114" s="20" t="inlineStr">
+      <c r="B117" s="20" t="inlineStr"/>
+      <c r="C117" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D114" s="20" t="inlineStr">
-        <is>
-          <t>Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="E114" s="20" t="inlineStr"/>
-      <c r="F114" s="20" t="inlineStr"/>
-      <c r="G114" s="20" t="inlineStr"/>
-      <c r="H114" s="20" t="inlineStr"/>
-      <c r="I114" s="20" t="inlineStr">
+      <c r="D117" s="20" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E117" s="20" t="inlineStr"/>
+      <c r="F117" s="20" t="inlineStr"/>
+      <c r="G117" s="20" t="inlineStr"/>
+      <c r="H117" s="20" t="inlineStr"/>
+      <c r="I117" s="20" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-      <c r="J114" s="20" t="inlineStr"/>
-      <c r="K114" s="21" t="inlineStr">
+      <c r="J117" s="20" t="inlineStr"/>
+      <c r="K117" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L114" s="20" t="inlineStr"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="L117" s="20" t="inlineStr"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B116" s="20" t="inlineStr"/>
-      <c r="C116" s="20" t="inlineStr">
+      <c r="B119" s="20" t="inlineStr"/>
+      <c r="C119" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D116" s="20" t="inlineStr">
-        <is>
-          <t>Bean Salad (Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="E116" s="20" t="inlineStr"/>
-      <c r="F116" s="20" t="inlineStr"/>
-      <c r="G116" s="20" t="inlineStr"/>
-      <c r="H116" s="20" t="inlineStr"/>
-      <c r="I116" s="20" t="inlineStr">
+      <c r="D119" s="20" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr"/>
+      <c r="F119" s="20" t="inlineStr"/>
+      <c r="G119" s="20" t="inlineStr"/>
+      <c r="H119" s="20" t="inlineStr"/>
+      <c r="I119" s="20" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="J116" s="20" t="inlineStr"/>
-      <c r="K116" s="21" t="inlineStr">
+      <c r="J119" s="20" t="inlineStr"/>
+      <c r="K119" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L116" s="20" t="inlineStr"/>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
+      <c r="L119" s="20" t="inlineStr"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr"/>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>120 lbs</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr"/>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>Stove top</t>
-        </is>
-      </c>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>180 min</t>
-        </is>
-      </c>
-      <c r="K118" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L118" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr"/>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>Pineapple Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H120" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Oven rice</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K120" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L120" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -5141,155 +5160,108 @@
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Steam Green Beans (Fri Dinner side)</t>
+          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>4 oz</t>
-        </is>
-      </c>
+          <t>120 lbs</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr"/>
       <c r="G121" s="9" t="inlineStr">
         <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>Stove top</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>180 min</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr"/>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Pineapple Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>Frozen; steam at Bloor</t>
-        </is>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K121" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L121" s="9" t="inlineStr">
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven rice</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K123" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L123" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="14" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B122" s="14" t="inlineStr"/>
-      <c r="C122" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D122" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Pork Adobo (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>40 lbs</t>
-        </is>
-      </c>
-      <c r="F122" s="14" t="inlineStr">
-        <is>
-          <t>10 oz</t>
-        </is>
-      </c>
-      <c r="G122" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H122" s="14" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I122" s="14" t="inlineStr"/>
-      <c r="J122" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K122" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L122" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="14" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B123" s="14" t="inlineStr"/>
-      <c r="C123" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D123" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Halal Chicken Adobo (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E123" s="14" t="inlineStr">
-        <is>
-          <t>32 lbs</t>
-        </is>
-      </c>
-      <c r="F123" s="14" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
-      <c r="G123" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H123" s="14" t="inlineStr">
-        <is>
-          <t>1u</t>
-        </is>
-      </c>
-      <c r="I123" s="14" t="inlineStr"/>
-      <c r="J123" s="14" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K123" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L123" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -5307,188 +5279,216 @@
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
+          <t>Steam Green Beans (Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>Frozen; steam at Bloor</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr"/>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Pork Adobo (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>10 oz</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr"/>
+      <c r="J125" s="14" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L125" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr"/>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Halal Chicken Adobo (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="I126" s="14" t="inlineStr"/>
+      <c r="J126" s="14" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L126" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr"/>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
           <t>Roast Adobo Tofu (Fri Dinner — Veg)</t>
         </is>
       </c>
-      <c r="E124" s="9" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>12 pcs</t>
         </is>
       </c>
-      <c r="F124" s="9" t="inlineStr"/>
-      <c r="G124" s="9" t="inlineStr">
+      <c r="F127" s="9" t="inlineStr"/>
+      <c r="G127" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H124" s="9" t="inlineStr">
+      <c r="H127" s="9" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="I124" s="9" t="inlineStr">
+      <c r="I127" s="9" t="inlineStr">
         <is>
           <t>⚠ CONFIRM cook time | Same-day roast at Bloor</t>
         </is>
       </c>
-      <c r="J124" s="9" t="inlineStr">
+      <c r="J127" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K124" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L124" s="9" t="inlineStr">
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L127" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="15" t="inlineStr">
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B126" s="16" t="inlineStr"/>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D126" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E126" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F126" s="16" t="inlineStr"/>
-      <c r="G126" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H126" s="16" t="inlineStr"/>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J126" s="16" t="inlineStr"/>
-      <c r="K126" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L126" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="inlineStr"/>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D127" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
-        </is>
-      </c>
-      <c r="E127" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F127" s="16" t="inlineStr"/>
-      <c r="G127" s="16" t="inlineStr"/>
-      <c r="H127" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="J127" s="16" t="inlineStr"/>
-      <c r="K127" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L127" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr"/>
-      <c r="C128" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>HOT Green Beans → Dinner side</t>
-        </is>
-      </c>
-      <c r="E128" s="16" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="F128" s="16" t="inlineStr"/>
-      <c r="G128" s="16" t="inlineStr"/>
-      <c r="H128" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I128" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J128" s="16" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L128" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -5506,39 +5506,35 @@
       </c>
       <c r="D129" s="16" t="inlineStr">
         <is>
-          <t>HOT Pork Adobo → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E129" s="16" t="inlineStr">
         <is>
-          <t>40 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F129" s="16" t="inlineStr"/>
       <c r="G129" s="16" t="inlineStr">
         <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H129" s="16" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H129" s="16" t="inlineStr"/>
       <c r="I129" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J129" s="16" t="inlineStr"/>
-      <c r="K129" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K129" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L129" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -5556,39 +5552,35 @@
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+          <t>HOT Pineapple Rice → Dinner side</t>
         </is>
       </c>
       <c r="E130" s="16" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F130" s="16" t="inlineStr"/>
-      <c r="G130" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
+      <c r="G130" s="16" t="inlineStr"/>
       <c r="H130" s="16" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J130" s="16" t="inlineStr"/>
-      <c r="K130" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K130" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L130" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
+          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -5606,19 +5598,19 @@
       </c>
       <c r="D131" s="16" t="inlineStr">
         <is>
-          <t>HOT Adobo Tofu → Dinner (Veg)</t>
+          <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
       <c r="E131" s="16" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="F131" s="16" t="inlineStr"/>
       <c r="G131" s="16" t="inlineStr"/>
       <c r="H131" s="16" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="I131" s="16" t="inlineStr">
@@ -5634,335 +5626,331 @@
       </c>
       <c r="L131" s="16" t="inlineStr">
         <is>
+          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr"/>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pork Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="F132" s="16" t="inlineStr"/>
+      <c r="G132" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H132" s="16" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J132" s="16" t="inlineStr"/>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L132" s="16" t="inlineStr">
+        <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr"/>
+      <c r="C133" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D133" s="16" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
+        </is>
+      </c>
+      <c r="E133" s="16" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="F133" s="16" t="inlineStr"/>
+      <c r="G133" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H133" s="16" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J133" s="16" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L133" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr"/>
+      <c r="C134" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>HOT Adobo Tofu → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="F134" s="16" t="inlineStr"/>
+      <c r="G134" s="16" t="inlineStr"/>
+      <c r="H134" s="16" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J134" s="16" t="inlineStr"/>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L134" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>◆  SATURDAY  —  May 23</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr"/>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr"/>
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr"/>
-      <c r="G134" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr"/>
+      <c r="G137" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J134" s="6" t="inlineStr"/>
-      <c r="K134" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L134" s="6" t="inlineStr">
+      <c r="J137" s="6" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr"/>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr"/>
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr"/>
-      <c r="G135" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="H138" s="6" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J135" s="6" t="inlineStr"/>
-      <c r="K135" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L135" s="6" t="inlineStr">
+      <c r="J138" s="6" t="inlineStr"/>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="14" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B137" s="14" t="inlineStr"/>
-      <c r="C137" s="14" t="inlineStr">
+      <c r="B140" s="14" t="inlineStr"/>
+      <c r="C140" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D137" s="14" t="inlineStr">
+      <c r="D140" s="14" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E137" s="14" t="inlineStr">
+      <c r="E140" s="14" t="inlineStr">
         <is>
           <t>80 lbs + 15 lbs</t>
         </is>
       </c>
-      <c r="F137" s="14" t="inlineStr"/>
-      <c r="G137" s="14" t="inlineStr">
+      <c r="F140" s="14" t="inlineStr"/>
+      <c r="G140" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H137" s="14" t="inlineStr"/>
-      <c r="I137" s="14" t="inlineStr">
+      <c r="H140" s="14" t="inlineStr"/>
+      <c r="I140" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J137" s="14" t="inlineStr">
+      <c r="J140" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K137" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L137" s="14" t="inlineStr">
+      <c r="K140" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B139" s="12" t="inlineStr"/>
-      <c r="C139" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D139" s="12" t="inlineStr">
-        <is>
-          <t>Griot Marinade</t>
-        </is>
-      </c>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F139" s="12" t="inlineStr"/>
-      <c r="G139" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="inlineStr"/>
-      <c r="I139" s="12" t="inlineStr">
-        <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
-        </is>
-      </c>
-      <c r="J139" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K139" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="inlineStr"/>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D140" s="12" t="inlineStr">
-        <is>
-          <t>Cut/Marinate Pork Griot</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>30kg raw</t>
-        </is>
-      </c>
-      <c r="F140" s="12" t="inlineStr"/>
-      <c r="G140" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H140" s="12" t="inlineStr">
-        <is>
-          <t>1 bin/2 hotels</t>
-        </is>
-      </c>
-      <c r="I140" s="12" t="inlineStr"/>
-      <c r="J140" s="12" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K140" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L140" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B141" s="12" t="inlineStr"/>
-      <c r="C141" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D141" s="12" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Griot</t>
-        </is>
-      </c>
-      <c r="E141" s="12" t="inlineStr">
-        <is>
-          <t>25kg raw</t>
-        </is>
-      </c>
-      <c r="F141" s="12" t="inlineStr"/>
-      <c r="G141" s="12" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="H141" s="12" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="I141" s="12" t="inlineStr"/>
-      <c r="J141" s="12" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="K141" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L141" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -5980,43 +5968,39 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr"/>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="H142" s="12" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr"/>
       <c r="I142" s="12" t="inlineStr">
         <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+          <t>For Griot Pork/Chicken/Tofu</t>
         </is>
       </c>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K142" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K142" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L142" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -6034,423 +6018,423 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Cut/Marinate Pork Griot</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>30kg raw</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr"/>
       <c r="G143" s="12" t="inlineStr">
         <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>1 bin/2 hotels</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr"/>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K143" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr"/>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Griot</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>25kg raw</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr"/>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr"/>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="K144" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr"/>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr"/>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I145" s="12" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K145" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr"/>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr"/>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H143" s="12" t="inlineStr">
+      <c r="H146" s="12" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I143" s="12" t="inlineStr">
+      <c r="I146" s="12" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
-      <c r="J143" s="12" t="inlineStr">
+      <c r="J146" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K143" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L143" s="12" t="inlineStr">
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L146" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="13" t="inlineStr">
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="9" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr"/>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="B148" s="9" t="inlineStr"/>
+      <c r="C148" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D148" s="9" t="inlineStr">
         <is>
           <t>Carrot Cabbage Fry (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="E148" s="9" t="inlineStr">
         <is>
           <t>3 bins → 2 hotels</t>
         </is>
       </c>
-      <c r="F145" s="9" t="inlineStr"/>
-      <c r="G145" s="9" t="inlineStr">
+      <c r="F148" s="9" t="inlineStr"/>
+      <c r="G148" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H145" s="9" t="inlineStr">
+      <c r="H148" s="9" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I145" s="9" t="inlineStr">
+      <c r="I148" s="9" t="inlineStr">
         <is>
           <t>Stir-fry at LAN; send hot PM</t>
         </is>
       </c>
-      <c r="J145" s="9" t="inlineStr">
+      <c r="J148" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K145" s="14" t="inlineStr">
+      <c r="K148" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L145" s="9" t="inlineStr">
+      <c r="L148" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="14" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B146" s="14" t="inlineStr"/>
-      <c r="C146" s="14" t="inlineStr">
+      <c r="B149" s="14" t="inlineStr"/>
+      <c r="C149" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D146" s="14" t="inlineStr">
+      <c r="D149" s="14" t="inlineStr">
         <is>
           <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E146" s="14" t="inlineStr">
+      <c r="E149" s="14" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="F146" s="14" t="inlineStr"/>
-      <c r="G146" s="14" t="inlineStr">
+      <c r="F149" s="14" t="inlineStr"/>
+      <c r="G149" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H146" s="14" t="inlineStr">
+      <c r="H149" s="14" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I146" s="14" t="inlineStr">
+      <c r="I149" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J146" s="14" t="inlineStr">
+      <c r="J149" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K146" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L146" s="14" t="inlineStr">
+      <c r="K149" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L149" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="9" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr"/>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="B150" s="9" t="inlineStr"/>
+      <c r="C150" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D150" s="9" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E147" s="9" t="inlineStr">
+      <c r="E150" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr"/>
-      <c r="G147" s="9" t="inlineStr"/>
-      <c r="H147" s="9" t="inlineStr">
+      <c r="F150" s="9" t="inlineStr"/>
+      <c r="G150" s="9" t="inlineStr"/>
+      <c r="H150" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I147" s="9" t="inlineStr"/>
-      <c r="J147" s="9" t="inlineStr">
+      <c r="I150" s="9" t="inlineStr"/>
+      <c r="J150" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K147" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L147" s="9" t="inlineStr">
+      <c r="K150" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L150" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="20" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B148" s="20" t="inlineStr"/>
-      <c r="C148" s="20" t="inlineStr">
+      <c r="B151" s="20" t="inlineStr"/>
+      <c r="C151" s="20" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="D148" s="20" t="inlineStr">
+      <c r="D151" s="20" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="E148" s="20" t="inlineStr">
+      <c r="E151" s="20" t="inlineStr">
         <is>
           <t>2 pcs</t>
         </is>
       </c>
-      <c r="F148" s="20" t="inlineStr">
+      <c r="F151" s="20" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="G148" s="20" t="inlineStr">
+      <c r="G151" s="20" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H148" s="20" t="inlineStr">
+      <c r="H151" s="20" t="inlineStr">
         <is>
           <t>4" hotel</t>
         </is>
       </c>
-      <c r="I148" s="20" t="inlineStr">
+      <c r="I151" s="20" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
       </c>
-      <c r="J148" s="20" t="inlineStr">
+      <c r="J151" s="20" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K148" s="14" t="inlineStr">
+      <c r="K151" s="14" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L148" s="20" t="inlineStr">
+      <c r="L151" s="20" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="15" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 10 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="inlineStr"/>
-      <c r="C150" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E150" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F150" s="16" t="inlineStr"/>
-      <c r="G150" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H150" s="16" t="inlineStr"/>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J150" s="16" t="inlineStr"/>
-      <c r="K150" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L150" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B151" s="16" t="inlineStr"/>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D151" s="16" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="E151" s="16" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F151" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G151" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H151" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I151" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J151" s="16" t="inlineStr"/>
-      <c r="K151" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L151" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="inlineStr"/>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="E152" s="16" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="F152" s="16" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="G152" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H152" s="16" t="inlineStr">
-        <is>
-          <t>1 × 4" hotel</t>
-        </is>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J152" s="16" t="inlineStr"/>
-      <c r="K152" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L152" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -6468,39 +6452,35 @@
       </c>
       <c r="D153" s="16" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E153" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F153" s="16" t="inlineStr"/>
       <c r="G153" s="16" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H153" s="16" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr"/>
       <c r="I153" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J153" s="16" t="inlineStr"/>
-      <c r="K153" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K153" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L153" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -6518,19 +6498,27 @@
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="E154" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F154" s="16" t="inlineStr"/>
-      <c r="G154" s="16" t="inlineStr"/>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F154" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G154" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="H154" s="16" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="I154" s="16" t="inlineStr">
@@ -6546,7 +6534,7 @@
       </c>
       <c r="L154" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -6564,37 +6552,187 @@
       </c>
       <c r="D155" s="16" t="inlineStr">
         <is>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>1 × 4" hotel</t>
+        </is>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J155" s="16" t="inlineStr"/>
+      <c r="K155" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L155" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr"/>
+      <c r="C156" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
+        <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F156" s="16" t="inlineStr"/>
+      <c r="G156" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H156" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J156" s="16" t="inlineStr"/>
+      <c r="K156" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L156" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr"/>
+      <c r="C157" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F157" s="16" t="inlineStr"/>
+      <c r="G157" s="16" t="inlineStr"/>
+      <c r="H157" s="16" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J157" s="16" t="inlineStr"/>
+      <c r="K157" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L157" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr"/>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="E155" s="16" t="inlineStr">
+      <c r="E158" s="16" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="F155" s="16" t="inlineStr"/>
-      <c r="G155" s="16" t="inlineStr">
+      <c r="F158" s="16" t="inlineStr"/>
+      <c r="G158" s="16" t="inlineStr">
         <is>
           <t>bus bin/bag</t>
         </is>
       </c>
-      <c r="H155" s="16" t="inlineStr">
+      <c r="H158" s="16" t="inlineStr">
         <is>
           <t>4 items</t>
         </is>
       </c>
-      <c r="I155" s="16" t="inlineStr">
+      <c r="I158" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex fridge</t>
         </is>
       </c>
-      <c r="J155" s="16" t="inlineStr"/>
-      <c r="K155" s="17" t="inlineStr">
+      <c r="J158" s="16" t="inlineStr"/>
+      <c r="K158" s="17" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="L155" s="16" t="inlineStr">
+      <c r="L158" s="16" t="inlineStr">
         <is>
           <t>Produced: LAN day-before</t>
         </is>
@@ -6605,47 +6743,47 @@
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A99:L99"/>
+    <mergeCell ref="A108:L108"/>
+    <mergeCell ref="A128:L128"/>
     <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A133:L133"/>
     <mergeCell ref="A74:L74"/>
-    <mergeCell ref="A149:L149"/>
+    <mergeCell ref="A118:L118"/>
     <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A120:L120"/>
     <mergeCell ref="A136:L136"/>
-    <mergeCell ref="A113:L113"/>
+    <mergeCell ref="A139:L139"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A86:L86"/>
+    <mergeCell ref="A104:L104"/>
     <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="A116:L116"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A141:L141"/>
     <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A144:L144"/>
+    <mergeCell ref="A97:L97"/>
+    <mergeCell ref="A135:L135"/>
+    <mergeCell ref="A122:L122"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="A96:L96"/>
-    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="A100:L100"/>
     <mergeCell ref="A72:L72"/>
-    <mergeCell ref="A112:L112"/>
+    <mergeCell ref="A147:L147"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A63:L63"/>
     <mergeCell ref="A68:L68"/>
+    <mergeCell ref="A152:L152"/>
     <mergeCell ref="A115:L115"/>
-    <mergeCell ref="A117:L117"/>
     <mergeCell ref="A93:L93"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A67:L67"/>
     <mergeCell ref="A59:L59"/>
     <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A92:L92"/>
     <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A138:L138"/>
-    <mergeCell ref="A107:L107"/>
+    <mergeCell ref="A82:L82"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A103:L103"/>
-    <mergeCell ref="A132:L132"/>
-    <mergeCell ref="A119:L119"/>
+    <mergeCell ref="A94:L94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12935,7 +13073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L151"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15852,7 +15990,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr"/>
@@ -15863,7 +16001,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
@@ -15906,7 +16044,7 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr"/>
@@ -15917,12 +16055,12 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>Prep at LAN; send Thu PM</t>
+          <t>Prep at LAN; send Thu PM | ⚠ NO RECIPE</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
@@ -17277,7 +17415,7 @@
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>Cold Egg Salad + Bean Salad → Fri Lunch</t>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
         </is>
       </c>
       <c r="E111" s="16" t="inlineStr">
@@ -17309,149 +17447,149 @@
       </c>
       <c r="L111" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Thursday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr"/>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F112" s="16" t="inlineStr"/>
+      <c r="G112" s="16" t="inlineStr"/>
+      <c r="H112" s="16" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="J112" s="16" t="inlineStr"/>
+      <c r="K112" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L112" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>◆  FRIDAY  —  Jun 5</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: ~1 items</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B114" s="20" t="inlineStr"/>
-      <c r="C114" s="20" t="inlineStr">
+      <c r="B115" s="20" t="inlineStr"/>
+      <c r="C115" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D114" s="20" t="inlineStr">
-        <is>
-          <t>Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="E114" s="20" t="inlineStr"/>
-      <c r="F114" s="20" t="inlineStr"/>
-      <c r="G114" s="20" t="inlineStr"/>
-      <c r="H114" s="20" t="inlineStr"/>
-      <c r="I114" s="20" t="inlineStr">
+      <c r="D115" s="20" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="E115" s="20" t="inlineStr"/>
+      <c r="F115" s="20" t="inlineStr"/>
+      <c r="G115" s="20" t="inlineStr"/>
+      <c r="H115" s="20" t="inlineStr"/>
+      <c r="I115" s="20" t="inlineStr">
         <is>
           <t>Cold salad already at Rex</t>
         </is>
       </c>
-      <c r="J114" s="20" t="inlineStr"/>
-      <c r="K114" s="21" t="inlineStr">
+      <c r="J115" s="20" t="inlineStr"/>
+      <c r="K115" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L114" s="20" t="inlineStr"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="L115" s="20" t="inlineStr"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B116" s="20" t="inlineStr"/>
-      <c r="C116" s="20" t="inlineStr">
+      <c r="B117" s="20" t="inlineStr"/>
+      <c r="C117" s="20" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D116" s="20" t="inlineStr">
-        <is>
-          <t>Bean Salad (Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="E116" s="20" t="inlineStr"/>
-      <c r="F116" s="20" t="inlineStr"/>
-      <c r="G116" s="20" t="inlineStr"/>
-      <c r="H116" s="20" t="inlineStr"/>
-      <c r="I116" s="20" t="inlineStr">
+      <c r="D117" s="20" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="E117" s="20" t="inlineStr"/>
+      <c r="F117" s="20" t="inlineStr"/>
+      <c r="G117" s="20" t="inlineStr"/>
+      <c r="H117" s="20" t="inlineStr"/>
+      <c r="I117" s="20" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="J116" s="20" t="inlineStr"/>
-      <c r="K116" s="21" t="inlineStr">
+      <c r="J117" s="20" t="inlineStr"/>
+      <c r="K117" s="21" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="L116" s="20" t="inlineStr"/>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
+      <c r="L117" s="20" t="inlineStr"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr"/>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr"/>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr"/>
-      <c r="I118" s="9" t="inlineStr"/>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>180 min</t>
-        </is>
-      </c>
-      <c r="K118" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L118" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Sunday Dinner</t>
         </is>
       </c>
     </row>
@@ -17469,93 +17607,85 @@
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
+          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr"/>
       <c r="I119" s="9" t="inlineStr"/>
       <c r="J119" s="9" t="inlineStr">
         <is>
+          <t>180 min</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr"/>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr"/>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="I120" s="9" t="inlineStr"/>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
           <t>120 min</t>
         </is>
       </c>
-      <c r="K119" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L119" s="9" t="inlineStr">
+      <c r="K120" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L120" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="12" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B120" s="12" t="inlineStr"/>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D120" s="12" t="inlineStr">
-        <is>
-          <t>Massaman Curry Paste</t>
-        </is>
-      </c>
-      <c r="E120" s="12" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="F120" s="12" t="inlineStr"/>
-      <c r="G120" s="12" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I120" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
-        </is>
-      </c>
-      <c r="J120" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K120" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L120" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
         </is>
       </c>
     </row>
@@ -17573,96 +17703,100 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Portobello Cheese Melt prep (→ Wk4 Sun Lunch — Veg)</t>
+          <t>Massaman Curry Paste</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr"/>
       <c r="G121" s="12" t="inlineStr">
         <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L121" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr"/>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Portobello Cheese Melt prep (→ Wk4 Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr"/>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H121" s="12" t="inlineStr"/>
-      <c r="I121" s="12" t="inlineStr">
+      <c r="H122" s="12" t="inlineStr"/>
+      <c r="I122" s="12" t="inlineStr">
         <is>
           <t>Prep/slice portobello; hold chilled; cook day-of</t>
         </is>
       </c>
-      <c r="J121" s="12" t="inlineStr">
+      <c r="J122" s="12" t="inlineStr">
         <is>
           <t>??? min</t>
         </is>
       </c>
-      <c r="K121" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L121" s="12" t="inlineStr">
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L122" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="13" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr"/>
-      <c r="C123" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr"/>
-      <c r="G123" s="9" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K123" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L123" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -17680,204 +17814,204 @@
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
+          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
       <c r="G124" s="9" t="inlineStr"/>
       <c r="H124" s="9" t="inlineStr">
         <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr"/>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I124" s="9" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr"/>
+      <c r="G125" s="9" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
         <is>
           <t>Wok/oven</t>
         </is>
       </c>
-      <c r="J124" s="9" t="inlineStr">
+      <c r="J125" s="9" t="inlineStr">
         <is>
           <t>45 min</t>
         </is>
       </c>
-      <c r="K124" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L124" s="9" t="inlineStr">
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L125" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="14" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="14" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B125" s="14" t="inlineStr"/>
-      <c r="C125" s="14" t="inlineStr">
+      <c r="B126" s="14" t="inlineStr"/>
+      <c r="C126" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D125" s="14" t="inlineStr">
+      <c r="D126" s="14" t="inlineStr">
         <is>
           <t>Heat Spring Rolls (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="E125" s="14" t="inlineStr">
+      <c r="E126" s="14" t="inlineStr">
         <is>
           <t>200 pcs</t>
         </is>
       </c>
-      <c r="F125" s="14" t="inlineStr"/>
-      <c r="G125" s="14" t="inlineStr">
+      <c r="F126" s="14" t="inlineStr"/>
+      <c r="G126" s="14" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H125" s="14" t="inlineStr">
+      <c r="H126" s="14" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="I125" s="14" t="inlineStr">
+      <c r="I126" s="14" t="inlineStr">
         <is>
           <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
-      <c r="J125" s="14" t="inlineStr">
+      <c r="J126" s="14" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="K125" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L125" s="14" t="inlineStr">
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L126" s="14" t="inlineStr">
         <is>
           <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr"/>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr"/>
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>Bok Choy (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="E126" s="9" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr"/>
-      <c r="G126" s="9" t="inlineStr">
+      <c r="F127" s="9" t="inlineStr"/>
+      <c r="G127" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H126" s="9" t="inlineStr">
+      <c r="H127" s="9" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="I126" s="9" t="inlineStr">
+      <c r="I127" s="9" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
         </is>
       </c>
-      <c r="J126" s="9" t="inlineStr">
+      <c r="J127" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="K126" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L126" s="9" t="inlineStr">
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L127" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="15" t="inlineStr">
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 8 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr"/>
-      <c r="C128" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="E128" s="16" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="F128" s="16" t="inlineStr"/>
-      <c r="G128" s="16" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H128" s="16" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="I128" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J128" s="16" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L128" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -17895,19 +18029,23 @@
       </c>
       <c r="D129" s="16" t="inlineStr">
         <is>
-          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
         </is>
       </c>
       <c r="E129" s="16" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="F129" s="16" t="inlineStr"/>
-      <c r="G129" s="16" t="inlineStr"/>
+      <c r="G129" s="16" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="H129" s="16" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="I129" s="16" t="inlineStr">
@@ -17941,19 +18079,19 @@
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>HOT Spring Rolls → Dinner side</t>
+          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
         </is>
       </c>
       <c r="E130" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="F130" s="16" t="inlineStr"/>
       <c r="G130" s="16" t="inlineStr"/>
       <c r="H130" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="I130" s="16" t="inlineStr">
@@ -17973,71 +18111,63 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr"/>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="inlineStr">
+        <is>
+          <t>HOT Spring Rolls → Dinner side</t>
+        </is>
+      </c>
+      <c r="E131" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="F131" s="16" t="inlineStr"/>
+      <c r="G131" s="16" t="inlineStr"/>
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J131" s="16" t="inlineStr"/>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L131" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>◆  SATURDAY  —  Jun 6</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 2.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr"/>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J133" s="6" t="inlineStr"/>
-      <c r="K133" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L133" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Production</t>
         </is>
       </c>
     </row>
@@ -18055,17 +18185,17 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+          <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>6 oz</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -18075,7 +18205,7 @@
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
@@ -18095,125 +18225,125 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr"/>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr"/>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Friday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="14" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B136" s="14" t="inlineStr"/>
-      <c r="C136" s="14" t="inlineStr">
+      <c r="B137" s="14" t="inlineStr"/>
+      <c r="C137" s="14" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="D136" s="14" t="inlineStr">
+      <c r="D137" s="14" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="E136" s="14" t="inlineStr">
+      <c r="E137" s="14" t="inlineStr">
         <is>
           <t>92 lbs (80+12)</t>
         </is>
       </c>
-      <c r="F136" s="14" t="inlineStr">
+      <c r="F137" s="14" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="G136" s="14" t="inlineStr">
+      <c r="G137" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H136" s="14" t="inlineStr"/>
-      <c r="I136" s="14" t="inlineStr">
+      <c r="H137" s="14" t="inlineStr"/>
+      <c r="I137" s="14" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="J136" s="14" t="inlineStr">
+      <c r="J137" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K136" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L136" s="14" t="inlineStr">
+      <c r="K137" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L137" s="14" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
         <is>
           <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B138" s="12" t="inlineStr"/>
-      <c r="C138" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D138" s="12" t="inlineStr">
-        <is>
-          <t>Cut/Season Tandoori Pork</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="F138" s="12" t="inlineStr"/>
-      <c r="G138" s="12" t="inlineStr">
-        <is>
-          <t>hotels</t>
-        </is>
-      </c>
-      <c r="H138" s="12" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="I138" s="12" t="inlineStr">
-        <is>
-          <t>Season w/Vindaloo Dry Spice Mix</t>
-        </is>
-      </c>
-      <c r="J138" s="12" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K138" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L138" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -18231,26 +18361,30 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Tandoori Marinade</t>
+          <t>Cut/Season Tandoori Pork</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr"/>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>hotels</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I139" s="12" t="inlineStr"/>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>Season w/Vindaloo Dry Spice Mix</t>
+        </is>
+      </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
           <t>60 min</t>
@@ -18263,7 +18397,7 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>Serves: Tandoori Production Wk. 4 Monday</t>
+          <t>Serves: Wk. 4 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -18281,29 +18415,29 @@
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
+          <t>Tandoori Marinade</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr"/>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>bins</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>3 bins (6u)</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="I140" s="12" t="inlineStr"/>
       <c r="J140" s="12" t="inlineStr">
         <is>
-          <t>90 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="K140" s="10" t="inlineStr">
@@ -18313,7 +18447,7 @@
       </c>
       <c r="L140" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
+          <t>Serves: Tandoori Production Wk. 4 Monday</t>
         </is>
       </c>
     </row>
@@ -18331,43 +18465,39 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr"/>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
+          <t>bins</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>4 items</t>
-        </is>
-      </c>
-      <c r="I141" s="12" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
-        </is>
-      </c>
+          <t>3 bins (6u)</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr"/>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="K141" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K141" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
         </is>
       </c>
     </row>
@@ -18385,20 +18515,28 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>3 bins + 1 bag</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr"/>
-      <c r="G142" s="12" t="inlineStr"/>
-      <c r="H142" s="12" t="inlineStr"/>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
       <c r="I142" s="12" t="inlineStr">
         <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
       <c r="J142" s="12" t="inlineStr">
@@ -18431,211 +18569,211 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr"/>
+      <c r="G143" s="12" t="inlineStr"/>
+      <c r="H143" s="12" t="inlineStr"/>
+      <c r="I143" s="12" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="K143" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr"/>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
           <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E144" s="12" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="F143" s="12" t="inlineStr"/>
-      <c r="G143" s="12" t="inlineStr">
+      <c r="F144" s="12" t="inlineStr"/>
+      <c r="G144" s="12" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H143" s="12" t="inlineStr">
+      <c r="H144" s="12" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="I143" s="12" t="inlineStr">
+      <c r="I144" s="12" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
-      <c r="J143" s="12" t="inlineStr">
+      <c r="J144" s="12" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K143" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L143" s="12" t="inlineStr">
+      <c r="K144" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L144" s="12" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="9" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr"/>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="B145" s="9" t="inlineStr"/>
+      <c r="C145" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D144" s="9" t="inlineStr">
+      <c r="D145" s="9" t="inlineStr">
         <is>
           <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
         </is>
       </c>
-      <c r="E144" s="9" t="inlineStr">
+      <c r="E145" s="9" t="inlineStr">
         <is>
           <t>110lbs</t>
         </is>
       </c>
-      <c r="F144" s="9" t="inlineStr">
+      <c r="F145" s="9" t="inlineStr">
         <is>
           <t>12 oz</t>
         </is>
       </c>
-      <c r="G144" s="9" t="inlineStr">
+      <c r="G145" s="9" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H144" s="9" t="inlineStr">
+      <c r="H145" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I144" s="9" t="inlineStr">
+      <c r="I145" s="9" t="inlineStr">
         <is>
           <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
         </is>
       </c>
-      <c r="J144" s="9" t="inlineStr">
+      <c r="J145" s="9" t="inlineStr">
         <is>
           <t>320 min</t>
         </is>
       </c>
-      <c r="K144" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L144" s="9" t="inlineStr">
+      <c r="K145" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="13" t="inlineStr">
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="13" t="inlineStr">
         <is>
           <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr"/>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="B147" s="9" t="inlineStr"/>
+      <c r="C147" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D146" s="9" t="inlineStr">
+      <c r="D147" s="9" t="inlineStr">
         <is>
           <t>Potato Wedges (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="E146" s="9" t="inlineStr">
+      <c r="E147" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F146" s="9" t="inlineStr"/>
-      <c r="G146" s="9" t="inlineStr"/>
-      <c r="H146" s="9" t="inlineStr">
+      <c r="F147" s="9" t="inlineStr"/>
+      <c r="G147" s="9" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I146" s="9" t="inlineStr">
+      <c r="I147" s="9" t="inlineStr">
         <is>
           <t>Purchased frozen; oven</t>
         </is>
       </c>
-      <c r="J146" s="9" t="inlineStr">
+      <c r="J147" s="9" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K146" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L146" s="9" t="inlineStr">
+      <c r="K147" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L147" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="15" t="inlineStr">
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
         <is>
           <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 4.5 HOTELS (hot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="inlineStr"/>
-      <c r="C148" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D148" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="E148" s="16" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="F148" s="16" t="inlineStr"/>
-      <c r="G148" s="16" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H148" s="16" t="inlineStr"/>
-      <c r="I148" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="J148" s="16" t="inlineStr"/>
-      <c r="K148" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L148" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -18653,7 +18791,7 @@
       </c>
       <c r="D149" s="16" t="inlineStr">
         <is>
-          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="E149" s="16" t="inlineStr">
@@ -18664,28 +18802,24 @@
       <c r="F149" s="16" t="inlineStr"/>
       <c r="G149" s="16" t="inlineStr">
         <is>
-          <t>boxes</t>
-        </is>
-      </c>
-      <c r="H149" s="16" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr"/>
       <c r="I149" s="16" t="inlineStr">
         <is>
-          <t>Vendor → Rex | Driver collects ordered pizza</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="J149" s="16" t="inlineStr"/>
-      <c r="K149" s="7" t="inlineStr">
-        <is>
-          <t>Vendor</t>
+      <c r="K149" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="L149" s="16" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Saturday Dinner</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -18703,39 +18837,39 @@
       </c>
       <c r="D150" s="16" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
       <c r="E150" s="16" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="F150" s="16" t="inlineStr"/>
       <c r="G150" s="16" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
+          <t>boxes</t>
         </is>
       </c>
       <c r="H150" s="16" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>order</t>
         </is>
       </c>
       <c r="I150" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex fridge</t>
+          <t>Vendor → Rex | Driver collects ordered pizza</t>
         </is>
       </c>
       <c r="J150" s="16" t="inlineStr"/>
-      <c r="K150" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K150" s="7" t="inlineStr">
+        <is>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="L150" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
+          <t>Serves: Wk. 3 Saturday Dinner</t>
         </is>
       </c>
     </row>
@@ -18753,41 +18887,91 @@
       </c>
       <c r="D151" s="16" t="inlineStr">
         <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="F151" s="16" t="inlineStr"/>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="H151" s="16" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="J151" s="16" t="inlineStr"/>
+      <c r="K151" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L151" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr"/>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="E151" s="16" t="inlineStr">
+      <c r="E152" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="F151" s="16" t="inlineStr">
+      <c r="F152" s="16" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="G151" s="16" t="inlineStr">
+      <c r="G152" s="16" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H151" s="16" t="inlineStr">
+      <c r="H152" s="16" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I151" s="16" t="inlineStr">
+      <c r="I152" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J151" s="16" t="inlineStr"/>
-      <c r="K151" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L151" s="16" t="inlineStr">
+      <c r="J152" s="16" t="inlineStr"/>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L152" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Dinner (same day)</t>
         </is>
@@ -18798,45 +18982,45 @@
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A90:L90"/>
-    <mergeCell ref="A137:L137"/>
+    <mergeCell ref="A128:L128"/>
     <mergeCell ref="A46:L46"/>
     <mergeCell ref="A75:L75"/>
+    <mergeCell ref="A133:L133"/>
     <mergeCell ref="A80:L80"/>
-    <mergeCell ref="A145:L145"/>
+    <mergeCell ref="A118:L118"/>
+    <mergeCell ref="A136:L136"/>
     <mergeCell ref="A57:L57"/>
     <mergeCell ref="A113:L113"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A116:L116"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A97:L97"/>
-    <mergeCell ref="A135:L135"/>
     <mergeCell ref="A106:L106"/>
-    <mergeCell ref="A122:L122"/>
     <mergeCell ref="A91:L91"/>
-    <mergeCell ref="A131:L131"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A62:L62"/>
     <mergeCell ref="A100:L100"/>
-    <mergeCell ref="A147:L147"/>
     <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A112:L112"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A68:L68"/>
     <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A115:L115"/>
-    <mergeCell ref="A117:L117"/>
-    <mergeCell ref="A127:L127"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A114:L114"/>
     <mergeCell ref="A83:L83"/>
+    <mergeCell ref="A148:L148"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A73:L73"/>
     <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A138:L138"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A94:L94"/>
     <mergeCell ref="A132:L132"/>
     <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A123:L123"/>
+    <mergeCell ref="A146:L146"/>
     <mergeCell ref="A69:L69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -3579,48 +3579,56 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr"/>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>Egg Salad Mix (→ Fri Lunch — make at LAN)</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr"/>
-      <c r="G79" s="12" t="inlineStr"/>
-      <c r="H79" s="12" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="I79" s="12" t="inlineStr"/>
-      <c r="J79" s="12" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K79" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L79" s="12" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Lunch</t>
+      <c r="B79" s="9" t="inlineStr"/>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Cook Pork Adobo (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr"/>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>Oven/Combi; cool; vac bag</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>120 min</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3646,12 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Cook Pork Adobo (→ Fri Dinner)</t>
+          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>40 lbs cooked</t>
+          <t>32 lbs cooked</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -3654,7 +3662,7 @@
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>1.5u</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
@@ -3664,7 +3672,7 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>120 min</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="K80" s="10" t="inlineStr">
@@ -3678,233 +3686,225 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>32 lbs cooked</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>165 pcs</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr"/>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>90 min</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Wednesday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr"/>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr"/>
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>1u</t>
-        </is>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Oven/Combi; cool; vac bag</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="inlineStr">
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>Reheat bagged batch</t>
+        </is>
+      </c>
+      <c r="J83" s="14" t="inlineStr">
         <is>
           <t>60 min</t>
         </is>
       </c>
-      <c r="K81" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>🌙  DINNER — Items cooked / heated for Dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L83" s="14" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Monday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr"/>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>165 pcs</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr"/>
-      <c r="G83" s="9" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Herbed Couscous (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="K83" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L83" s="9" t="inlineStr">
+      <c r="I84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K84" s="14" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 12.5 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B84" s="14" t="inlineStr"/>
-      <c r="C84" s="14" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D84" s="14" t="inlineStr">
-        <is>
-          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="F84" s="14" t="inlineStr"/>
-      <c r="G84" s="14" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="H84" s="14" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="I84" s="14" t="inlineStr">
-        <is>
-          <t>Reheat bagged batch</t>
-        </is>
-      </c>
-      <c r="J84" s="14" t="inlineStr">
-        <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="K84" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L84" s="14" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Monday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr"/>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>Herbed Couscous (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr"/>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="K85" s="14" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="15" t="inlineStr">
-        <is>
-          <t>▼  SEND PM — Evening van dispatch  |  VAN LOAD: 12.5 HOTELS (hot)</t>
+      <c r="B86" s="16" t="inlineStr"/>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr"/>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="H86" s="16" t="inlineStr"/>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="J86" s="16" t="inlineStr"/>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L86" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -3922,35 +3922,39 @@
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Pick up Baked Rolls at GC</t>
+          <t>HOT Shakshuka Sauce → Dinner</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
-          <t>pickup</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr"/>
       <c r="G87" s="16" t="inlineStr">
         <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="H87" s="16" t="inlineStr"/>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="H87" s="16" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
-          <t>GC → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J87" s="16" t="inlineStr"/>
-      <c r="K87" s="18" t="inlineStr">
-        <is>
-          <t>GC</t>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L87" s="16" t="inlineStr">
         <is>
-          <t>N/A — logistics</t>
+          <t>Produced: pre-loaded batch (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -3968,39 +3972,35 @@
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>HOT Shakshuka Sauce → Dinner</t>
+          <t>HOT Herbed Couscous → Dinner side</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr"/>
-      <c r="G88" s="16" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
+      <c r="G88" s="16" t="inlineStr"/>
       <c r="H88" s="16" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="J88" s="16" t="inlineStr"/>
-      <c r="K88" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="K88" s="17" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="L88" s="16" t="inlineStr">
         <is>
-          <t>Produced: pre-loaded batch (prev. cycle)</t>
+          <t>Produced: Wk. 1 Wednesday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
@@ -4018,35 +4018,39 @@
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>HOT Herbed Couscous → Dinner side</t>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>40 lbs</t>
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr"/>
-      <c r="G89" s="16" t="inlineStr"/>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="J89" s="16" t="inlineStr"/>
-      <c r="K89" s="17" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="L89" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 1 Tuesday Production</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4068,12 @@
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Cold Pork Vindaloo → Rex fridge</t>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>40 lbs</t>
+          <t>32 lbs</t>
         </is>
       </c>
       <c r="F90" s="16" t="inlineStr"/>
@@ -4080,7 +4084,7 @@
       </c>
       <c r="H90" s="16" t="inlineStr">
         <is>
-          <t>1.5u</t>
+          <t>1.0u</t>
         </is>
       </c>
       <c r="I90" s="16" t="inlineStr">
@@ -4114,23 +4118,23 @@
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+          <t>HOT Shakshuka Chicken Legs → Dinner</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>165 pcs</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr"/>
       <c r="G91" s="16" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="H91" s="16" t="inlineStr">
         <is>
-          <t>1.0u</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
@@ -4146,71 +4150,71 @@
       </c>
       <c r="L91" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Tuesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="inlineStr"/>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>HOT Shakshuka Chicken Legs → Dinner</t>
-        </is>
-      </c>
-      <c r="E92" s="16" t="inlineStr">
-        <is>
-          <t>165 pcs</t>
-        </is>
-      </c>
-      <c r="F92" s="16" t="inlineStr"/>
-      <c r="G92" s="16" t="inlineStr">
+          <t>Produced: Wk. 1 Wednesday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>◆  THURSDAY  —  May 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 4 HOTELS (hot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Burgers → Lunch</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>185 pcs</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H92" s="16" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="J92" s="16" t="inlineStr"/>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L92" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>◆  THURSDAY  —  May 21</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>▲  SEND AM — Morning van dispatch  |  VAN LOAD: 4 HOTELS (hot)</t>
+      <c r="J94" s="6" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -4228,12 +4232,12 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>HOT Halal Chicken Burgers → Lunch</t>
+          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>185 pcs</t>
+          <t>20 pcs</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -4242,11 +4246,7 @@
           <t>hotel</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+      <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -4264,56 +4264,60 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr"/>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr"/>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr"/>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>185 pcs</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr"/>
+      <c r="G97" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr"/>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="J96" s="6" t="inlineStr"/>
-      <c r="K96" s="7" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L96" s="6" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>☀  LUNCH — Items cooked / heated for Lunch service</t>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr"/>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Thursday Lunch</t>
         </is>
       </c>
     </row>
@@ -4331,96 +4335,92 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
+          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>185 pcs</t>
+          <t>30 pcs</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
+      <c r="G98" s="9" t="inlineStr"/>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="I98" s="9" t="inlineStr"/>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>Pan fry; send hot AM</t>
+        </is>
+      </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr"/>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Egg Salad Mix (→ Fri Lunch — make at LAN)</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr"/>
+      <c r="G100" s="12" t="inlineStr"/>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr"/>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="K98" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Thursday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr"/>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr"/>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>Pan fry; send hot AM</t>
-        </is>
-      </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="K99" s="10" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="L99" s="9" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>⚙  PRODUCTION — Advance prep, long cooks, bagging</t>
+      <c r="K100" s="10" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Lunch</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L113" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production (LAN)</t>
+          <t>Produced: Wk. 1 Thursday Production (Bloor)</t>
         </is>
       </c>
     </row>
@@ -6745,6 +6745,7 @@
     <mergeCell ref="A41:L41"/>
     <mergeCell ref="A108:L108"/>
     <mergeCell ref="A128:L128"/>
+    <mergeCell ref="A99:L99"/>
     <mergeCell ref="A37:L37"/>
     <mergeCell ref="A74:L74"/>
     <mergeCell ref="A118:L118"/>
@@ -6753,20 +6754,20 @@
     <mergeCell ref="A136:L136"/>
     <mergeCell ref="A139:L139"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A86:L86"/>
     <mergeCell ref="A104:L104"/>
     <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A116:L116"/>
+    <mergeCell ref="A85:L85"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A116:L116"/>
     <mergeCell ref="A141:L141"/>
     <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A97:L97"/>
     <mergeCell ref="A135:L135"/>
     <mergeCell ref="A122:L122"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A100:L100"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="A96:L96"/>
     <mergeCell ref="A72:L72"/>
     <mergeCell ref="A147:L147"/>
     <mergeCell ref="A19:L19"/>
@@ -6779,11 +6780,10 @@
     <mergeCell ref="A67:L67"/>
     <mergeCell ref="A59:L59"/>
     <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A92:L92"/>
     <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A82:L82"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A94:L94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/01_Production_Schedule_generated.xlsx
+++ b/outputs/01_Production_Schedule_generated.xlsx
@@ -18288,10 +18288,14 @@
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>Vegan portion pulled before chicken added; shares cook time</t>
-        </is>
-      </c>
-      <c r="J123" s="9" t="inlineStr"/>
+          <t>Vegan portion pulled before chicken added; shares cook time with Chicken Chili</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
           <t>Bloor</t>
